--- a/data/processed/best_areas.xlsx
+++ b/data/processed/best_areas.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>190.6217512521918</v>
+        <v>139.9036629603248</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -499,23 +499,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>H=4.0 | C=45.6 | D=53.6 | P=-6.8 | A=42.7 | R=3.0</t>
+          <t>H=7.5 | C=36.7 | D=49.9 | P=-17.4 | A=38.4 | R=3.0</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4.010735790387009</v>
+        <v>7.503206542983218</v>
       </c>
       <c r="F2" t="n">
-        <v>45.58284658064783</v>
+        <v>36.68067306449589</v>
       </c>
       <c r="G2" t="n">
-        <v>53.62584208498384</v>
+        <v>49.85956986768631</v>
       </c>
       <c r="H2" t="n">
-        <v>6.794887859985394</v>
+        <v>17.44131900930777</v>
       </c>
       <c r="I2" t="n">
-        <v>42.67565920110568</v>
+        <v>38.40721037917233</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -529,164 +529,164 @@
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>103.2194244560187</v>
+        <v>94.04344947516543</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C000002</t>
+          <t>C000004</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>186.0888549081963</v>
+        <v>117.8175890825609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>H=4.5 | C=33.2 | D=58.8 | P=-3.8 | A=41.2 | R=3.0</t>
+          <t>H=10.3 | C=36.8 | D=35.7 | P=-17.1 | A=31.9 | R=2.0</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.535727766943937</v>
+        <v>10.32873884306982</v>
       </c>
       <c r="F3" t="n">
-        <v>33.20269677282788</v>
+        <v>36.83947469090556</v>
       </c>
       <c r="G3" t="n">
-        <v>58.81245450648284</v>
+        <v>35.7050629008124</v>
       </c>
       <c r="H3" t="n">
-        <v>3.811959310504598</v>
+        <v>17.1047816897122</v>
       </c>
       <c r="I3" t="n">
-        <v>41.22974747200805</v>
+        <v>31.85381282121969</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>96.55087904625466</v>
+        <v>82.87327643478778</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C000009</t>
+          <t>C000020</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>160.5795433068414</v>
+        <v>89.26482171618197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>H=10.3 | C=36.8 | D=35.7 | P=-2.9 | A=31.9 | R=2.0</t>
+          <t>H=10.4 | C=18.8 | D=28.1 | P=-9.3 | A=22.0 | R=3.5</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.32873884306982</v>
+        <v>10.3956318121241</v>
       </c>
       <c r="F4" t="n">
-        <v>36.83947469090556</v>
+        <v>18.76646241735192</v>
       </c>
       <c r="G4" t="n">
-        <v>35.7050629008124</v>
+        <v>28.10762345171247</v>
       </c>
       <c r="H4" t="n">
-        <v>2.850796948285367</v>
+        <v>9.276268032075912</v>
       </c>
       <c r="I4" t="n">
-        <v>31.85381282121969</v>
+        <v>22.04190450032756</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>82.87327643478778</v>
+        <v>57.26971768118848</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C000019</t>
+          <t>C000032</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>139.2885219085633</v>
+        <v>73.34808106146353</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>H=0.0 | C=37.7 | D=33.9 | P=-2.4 | A=29.5 | R=3.0</t>
+          <t>H=5.0 | C=10.4 | D=20.5 | P=-0.0 | A=14.5 | R=2.0</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4.95442446784087</v>
       </c>
       <c r="F5" t="n">
-        <v>37.72890948156196</v>
+        <v>10.42168495838445</v>
       </c>
       <c r="G5" t="n">
-        <v>33.88636586813228</v>
+        <v>20.4711702289119</v>
       </c>
       <c r="H5" t="n">
-        <v>2.397992466761294</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>29.5194860945868</v>
+        <v>14.53521751189091</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>71.61527534969424</v>
+        <v>35.84727965513722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C000026</t>
+          <t>C000051</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115.289150251315</v>
+        <v>54.77858950325049</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -695,47 +695,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>H=12.9 | C=23.0 | D=25.5 | P=-3.4 | A=22.6 | R=3.5</t>
+          <t>H=0.0 | C=10.7 | D=22.1 | P=-4.2 | A=14.6 | R=3.0</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12.8898839611771</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>22.97068876133435</v>
+        <v>10.67810828029281</v>
       </c>
       <c r="G6" t="n">
-        <v>25.53093434298983</v>
+        <v>22.0746630259522</v>
       </c>
       <c r="H6" t="n">
-        <v>3.366977207189278</v>
+        <v>4.162207734404523</v>
       </c>
       <c r="I6" t="n">
-        <v>22.57067741880255</v>
+        <v>14.59670093974037</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>61.39150706550129</v>
+        <v>32.75277130624501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C000044</t>
+          <t>C000059</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.80464749880993</v>
+        <v>52.53881524064655</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -744,47 +744,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>H=12.3 | C=11.2 | D=25.9 | P=-0.7 | A=18.7 | R=2.0</t>
+          <t>H=6.7 | C=7.8 | D=18.0 | P=-4.7 | A=12.7 | R=3.5</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12.34697120079487</v>
+        <v>6.747676714883866</v>
       </c>
       <c r="F7" t="n">
-        <v>11.15557025691236</v>
+        <v>7.845538347346629</v>
       </c>
       <c r="G7" t="n">
-        <v>25.88835262854116</v>
+        <v>17.98573221872826</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6830645001191938</v>
+        <v>4.747448385233445</v>
       </c>
       <c r="I7" t="n">
-        <v>18.72052826670718</v>
+        <v>12.73265834429365</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>49.39089408624839</v>
+        <v>32.57894728095876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C000059</t>
+          <t>C000060</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85.91946680758646</v>
+        <v>52.38062365021003</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -793,23 +793,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>H=9.0 | C=24.1 | D=10.9 | P=-1.3 | A=15.0 | R=3.0</t>
+          <t>H=0.0 | C=18.5 | D=13.1 | P=-4.1 | A=12.7 | R=3.0</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9.04002360795341</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>24.10292321796681</v>
+        <v>18.50476759991403</v>
       </c>
       <c r="G8" t="n">
-        <v>10.86045501992304</v>
+        <v>13.10700375925079</v>
       </c>
       <c r="H8" t="n">
-        <v>1.294819156387006</v>
+        <v>4.138364947581984</v>
       </c>
       <c r="I8" t="n">
-        <v>14.97120585060936</v>
+        <v>12.7217577462634</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -823,17 +823,17 @@
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>44.00340184584327</v>
+        <v>31.61177135916482</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C000070</t>
+          <t>C000071</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73.34808106146353</v>
+        <v>49.78102545754624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -842,23 +842,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>H=5.0 | C=10.4 | D=20.5 | P=-0.0 | A=14.5 | R=2.0</t>
+          <t>H=5.5 | C=4.6 | D=18.5 | P=-2.9 | A=11.7 | R=2.0</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.95442446784087</v>
+        <v>5.488450747524911</v>
       </c>
       <c r="F9" t="n">
-        <v>10.42168495838445</v>
+        <v>4.638795203613305</v>
       </c>
       <c r="G9" t="n">
-        <v>20.4711702289119</v>
+        <v>18.47659404170868</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2.932194972048503</v>
       </c>
       <c r="I9" t="n">
-        <v>14.53521751189091</v>
+        <v>11.69930387997959</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -872,7 +872,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>35.84727965513722</v>
+        <v>28.60383999284689</v>
       </c>
     </row>
     <row r="10">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65.27257341293031</v>
+        <v>48.45999198339934</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -891,23 +891,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>H=0.0 | C=19.1 | D=14.0 | P=-0.9 | A=13.4 | R=3.5</t>
+          <t>H=1.3 | C=17.8 | D=9.3 | P=-3.2 | A=10.8 | R=3.5</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1.290032651072631</v>
       </c>
       <c r="F10" t="n">
-        <v>19.11826406984395</v>
+        <v>17.79715424324383</v>
       </c>
       <c r="G10" t="n">
-        <v>14.03497875366133</v>
+        <v>9.259417406821518</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9076455469193707</v>
+        <v>3.220308836059012</v>
       </c>
       <c r="I10" t="n">
-        <v>13.39024406677865</v>
+        <v>10.77709889300415</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
@@ -921,66 +921,66 @@
         <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>33.15324282350528</v>
+        <v>28.34660430113798</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C000078</t>
+          <t>C000114</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64.40743620373016</v>
+        <v>37.88281142082977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>H=6.7 | C=7.8 | D=18.0 | P=-0.8 | A=12.7 | R=3.5</t>
+          <t>H=14.4 | C=1.2 | D=3.1 | P=-0.0 | A=4.3 | R=2.0</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.747676714883866</v>
+        <v>14.39515752672992</v>
       </c>
       <c r="F11" t="n">
-        <v>7.845538347346629</v>
+        <v>1.168460452173742</v>
       </c>
       <c r="G11" t="n">
-        <v>17.98573221872826</v>
+        <v>3.061808531302996</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7912413975389075</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>12.73265834429365</v>
+        <v>4.319584004164399</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>32.57894728095876</v>
+        <v>18.62542651020666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C000082</t>
+          <t>C000143</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62.72653601916499</v>
+        <v>32.16910378665238</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>H=0.0 | C=18.5 | D=13.1 | P=-0.7 | A=12.7 | R=3.0</t>
+          <t>H=4.2 | C=7.5 | D=4.0 | P=-0.0 | A=5.2 | R=3.0</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4.205758233853527</v>
       </c>
       <c r="F12" t="n">
-        <v>18.50476759991403</v>
+        <v>7.489198797553329</v>
       </c>
       <c r="G12" t="n">
-        <v>13.10700375925079</v>
+        <v>3.980221362612684</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6897274912636639</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>12.7217577462634</v>
+        <v>5.187469986133039</v>
       </c>
       <c r="J12" t="n">
         <v>3</v>
@@ -1019,17 +1019,17 @@
         <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>31.61177135916482</v>
+        <v>15.67517839401954</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C000091</t>
+          <t>C000154</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>57.21725029641395</v>
+        <v>30.41392610673741</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1038,96 +1038,96 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>H=5.7 | C=12.9 | D=12.0 | P=-1.8 | A=11.3 | R=3.0</t>
+          <t>H=0.0 | C=16.8 | D=2.7 | P=-3.2 | A=6.9 | R=2.0</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.72125619898368</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>12.89029857112477</v>
+        <v>16.83420964225634</v>
       </c>
       <c r="G13" t="n">
-        <v>12.03943347302312</v>
+        <v>2.65724136837855</v>
       </c>
       <c r="H13" t="n">
-        <v>1.837242917506968</v>
+        <v>3.154326101453278</v>
       </c>
       <c r="I13" t="n">
-        <v>11.2700256267171</v>
+        <v>6.940023898274722</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>30.65098824313157</v>
+        <v>19.49145101063489</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C000092</t>
+          <t>C000155</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>57.11151288766749</v>
+        <v>30.35344114708541</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H=5.5 | C=4.6 | D=18.5 | P=-0.5 | A=11.7 | R=2.0</t>
+          <t>H=6.9 | C=6.1 | D=1.8 | P=-0.0 | A=4.1 | R=3.0</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.488450747524911</v>
+        <v>6.938993980343114</v>
       </c>
       <c r="F14" t="n">
-        <v>4.638795203613305</v>
+        <v>6.106033776932642</v>
       </c>
       <c r="G14" t="n">
-        <v>18.47659404170868</v>
+        <v>1.777659157868501</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4886991620080839</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>11.69930387997959</v>
+        <v>4.080673167968984</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>28.60383999284689</v>
+        <v>14.82268691514426</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C000096</t>
+          <t>C000161</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56.51076407354687</v>
+        <v>29.78502792383085</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1136,23 +1136,23 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>H=1.3 | C=17.8 | D=9.3 | P=-0.5 | A=10.8 | R=3.5</t>
+          <t>H=0.0 | C=14.5 | D=0.0 | P=-0.0 | A=4.8 | R=3.5</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.290032651072631</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>17.79715424324383</v>
+        <v>14.47624324122829</v>
       </c>
       <c r="G15" t="n">
-        <v>9.259417406821518</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5367181393431686</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>10.77709889300415</v>
+        <v>4.825414413742761</v>
       </c>
       <c r="J15" t="n">
         <v>3.5</v>
@@ -1166,115 +1166,115 @@
         <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>28.34660430113798</v>
+        <v>14.47624324122829</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C000101</t>
+          <t>C000165</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54.52153049300044</v>
+        <v>29.65337749634204</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=27.9 | P=-3.0 | A=14.9 | R=3.0</t>
+          <t>H=12.3 | C=0.0 | D=2.3 | P=-0.0 | A=3.2 | R=2.0</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>12.29483911743335</v>
       </c>
       <c r="F16" t="n">
-        <v>2.894869422722564</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>27.94478357691869</v>
+        <v>2.272578183504773</v>
       </c>
       <c r="H16" t="n">
-        <v>2.983836777517363</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>14.9373482627002</v>
+        <v>3.185428944657945</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>30.83965299964126</v>
+        <v>14.56741730093812</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C000105</t>
+          <t>C000179</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53.37917799294036</v>
+        <v>28.31910562328143</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>H=0.9 | C=10.9 | D=14.2 | P=-0.0 | A=10.9 | R=3.5</t>
+          <t>H=10.7 | C=2.7 | D=0.4 | P=-0.0 | A=2.9 | R=3.0</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8564191511931554</v>
+        <v>10.73502665302223</v>
       </c>
       <c r="F17" t="n">
-        <v>10.9043488242049</v>
+        <v>2.744008625141222</v>
       </c>
       <c r="G17" t="n">
-        <v>14.20970248560205</v>
+        <v>0.3856834155607017</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>10.88237070940152</v>
+        <v>2.896682358331131</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>25.9704704610001</v>
+        <v>13.86471869372416</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C000120</t>
+          <t>C000195</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.00524926643362</v>
+        <v>27.18593988812859</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1283,219 +1283,219 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>H=0.0 | C=22.7 | D=2.9 | P=-1.4 | A=9.0 | R=2.0</t>
+          <t>H=0.0 | C=10.3 | D=2.8 | P=-0.0 | A=4.9 | R=3.5</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>22.691529828359</v>
+        <v>10.33562517301334</v>
       </c>
       <c r="G18" t="n">
-        <v>2.869802173221797</v>
+        <v>2.83910668439096</v>
       </c>
       <c r="H18" t="n">
-        <v>1.405763057667011</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>8.998744362730564</v>
+        <v>4.864761733199926</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>25.5613320015808</v>
+        <v>13.1747318574043</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C000151</t>
+          <t>C000208</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>40.4909938936286</v>
+        <v>26.55330852804834</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>H=17.1 | C=3.2 | D=2.4 | P=-1.9 | A=5.1 | R=3.0</t>
+          <t>H=0.0 | C=13.0 | D=0.0 | P=-0.0 | A=4.3 | R=2.0</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>17.05126716104604</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3.187231034298396</v>
+        <v>12.96064353838443</v>
       </c>
       <c r="G19" t="n">
-        <v>2.425250604006678</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.882731685256003</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5.116913506943812</v>
+        <v>4.320214512794809</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>22.66374879935111</v>
+        <v>12.96064353838443</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C000154</t>
+          <t>C000210</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>39.96176770770386</v>
+        <v>26.47328980232562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>H=11.5 | C=5.7 | D=5.0 | P=-1.8 | A=6.3 | R=3.5</t>
+          <t>H=0.0 | C=7.5 | D=5.4 | P=-0.0 | A=5.2 | R=2.0</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11.49874588567654</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5.665547634402373</v>
+        <v>7.512356792514868</v>
       </c>
       <c r="G20" t="n">
-        <v>5.033028302640711</v>
+        <v>5.364958206932711</v>
       </c>
       <c r="H20" t="n">
-        <v>1.805008235147375</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>6.321487677067238</v>
+        <v>5.186598034304645</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>22.19732182271963</v>
+        <v>12.87731499944758</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C000166</t>
+          <t>C000231</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>37.88281142082977</v>
+        <v>25.14163866808258</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>H=14.4 | C=1.2 | D=3.1 | P=-0.0 | A=4.3 | R=2.0</t>
+          <t>H=0.0 | C=8.6 | D=3.6 | P=-0.0 | A=4.7 | R=3.0</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>14.39515752672992</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.168460452173742</v>
+        <v>8.618143666160218</v>
       </c>
       <c r="G21" t="n">
-        <v>3.061808531302996</v>
+        <v>3.569795063523645</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4.319584004164399</v>
+        <v>4.657612087148562</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>18.62542651020666</v>
+        <v>12.18793872968386</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C000173</t>
+          <t>C000235</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35.56833270373856</v>
+        <v>24.61170556575886</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>H=2.1 | C=9.6 | D=7.9 | P=-1.6 | A=7.5 | R=3.0</t>
+          <t>H=0.0 | C=6.3 | D=7.0 | P=-1.0 | A=5.6 | R=3.0</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.066058328024093</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>9.609881432976753</v>
+        <v>6.303320442942572</v>
       </c>
       <c r="G22" t="n">
-        <v>7.918084264705474</v>
+        <v>7.046935017731888</v>
       </c>
       <c r="H22" t="n">
-        <v>1.556794415825214</v>
+        <v>0.9837542626360252</v>
       </c>
       <c r="I22" t="n">
-        <v>7.506678998015669</v>
+        <v>5.624574323180135</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
@@ -1509,42 +1509,42 @@
         <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>19.59402402570632</v>
+        <v>13.35025546067446</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C000177</t>
+          <t>C000237</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35.08479557288076</v>
+        <v>24.51732104456848</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>H=0.9 | C=10.7 | D=5.7 | P=-0.1 | A=6.6 | R=3.0</t>
+          <t>H=10.9 | C=0.0 | D=1.1 | P=-0.0 | A=2.4 | R=3.0</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8625006549112778</v>
+        <v>10.87807738630281</v>
       </c>
       <c r="F23" t="n">
-        <v>10.67050215670293</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>5.744428894334872</v>
+        <v>1.112129259605435</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1424492332909197</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>6.572798608553627</v>
+        <v>2.369077527519853</v>
       </c>
       <c r="J23" t="n">
         <v>3</v>
@@ -1558,42 +1558,42 @@
         <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>17.27743170594908</v>
+        <v>11.99020664590825</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C000178</t>
+          <t>C000287</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>35.06809485213633</v>
+        <v>21.66563377348075</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>H=7.9 | C=5.3 | D=7.0 | P=-2.1 | A=6.6 | R=3.0</t>
+          <t>H=5.0 | C=6.3 | D=0.5 | P=-0.9 | A=3.2 | R=3.0</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7.928726719546557</v>
+        <v>4.968067659166701</v>
       </c>
       <c r="F24" t="n">
-        <v>5.276476196864767</v>
+        <v>6.320706845348123</v>
       </c>
       <c r="G24" t="n">
-        <v>6.990898033904711</v>
+        <v>0.5494580125681127</v>
       </c>
       <c r="H24" t="n">
-        <v>2.093893311804078</v>
+        <v>0.8772651723815277</v>
       </c>
       <c r="I24" t="n">
-        <v>6.575728869165038</v>
+        <v>3.209642564594548</v>
       </c>
       <c r="J24" t="n">
         <v>3</v>
@@ -1607,66 +1607,66 @@
         <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>20.19610095031603</v>
+        <v>11.83823251708294</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C000182</t>
+          <t>C000304</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>34.11417657245203</v>
+        <v>20.40697076865442</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>H=0.0 | C=12.7 | D=6.4 | P=-1.8 | A=7.5 | R=3.5</t>
+          <t>H=5.9 | C=5.3 | D=0.0 | P=-0.9 | A=2.8 | R=3.0</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>5.911861988325854</v>
       </c>
       <c r="F25" t="n">
-        <v>12.73994674953407</v>
+        <v>5.311549128188136</v>
       </c>
       <c r="G25" t="n">
-        <v>6.413818251991927</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.762903078283563</v>
+        <v>0.8718113783728645</v>
       </c>
       <c r="I25" t="n">
-        <v>7.453558042507319</v>
+        <v>2.755826707450354</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>19.15376500152599</v>
+        <v>11.22341111651399</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C000209</t>
+          <t>C000332</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.16910378665238</v>
+        <v>18.54098772350057</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1675,170 +1675,170 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>H=4.2 | C=7.5 | D=4.0 | P=-0.0 | A=5.2 | R=3.0</t>
+          <t>H=0.0 | C=4.6 | D=4.4 | P=-0.0 | A=3.7 | R=3.5</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4.205758233853527</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>7.489198797553329</v>
+        <v>4.558718100428397</v>
       </c>
       <c r="G26" t="n">
-        <v>3.980221362612684</v>
+        <v>4.351997196404634</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>5.187469986133039</v>
+        <v>3.695571298345116</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
-        <v>15.67517839401954</v>
+        <v>8.910715296833031</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C000220</t>
+          <t>C000335</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.0135118946347</v>
+        <v>18.47197316485219</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>H=0.0 | C=9.9 | D=5.2 | P=-0.0 | A=5.9 | R=2.0</t>
+          <t>H=0.0 | C=2.9 | D=6.0 | P=-0.0 | A=4.0 | R=3.0</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>9.938611727983428</v>
+        <v>2.917634677831475</v>
       </c>
       <c r="G27" t="n">
-        <v>5.173171405399215</v>
+        <v>5.970463082891799</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>5.899456278694084</v>
+        <v>3.957776434056391</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>15.11178313338264</v>
+        <v>8.888097760723273</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C000221</t>
+          <t>C000336</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>30.94517449088815</v>
+        <v>18.4703689085442</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.0 | D=13.3 | P=-0.2 | A=7.3 | R=3.5</t>
+          <t>H=0.0 | C=9.5 | D=7.9 | P=-5.8 | A=7.1 | R=3.0</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1.959191011164711</v>
+        <v>9.508691587422472</v>
       </c>
       <c r="G28" t="n">
-        <v>13.26885796383338</v>
+        <v>7.889633812927335</v>
       </c>
       <c r="H28" t="n">
-        <v>0.196557574779513</v>
+        <v>5.779239989683065</v>
       </c>
       <c r="I28" t="n">
-        <v>7.287492652304929</v>
+        <v>7.114380768937825</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>15.22804897499809</v>
+        <v>17.39832540034981</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C000224</t>
+          <t>C000340</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30.71696239900768</v>
+        <v>18.32922278082053</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>H=13.4 | C=4.3 | D=1.8 | P=-3.0 | A=4.6 | R=3.5</t>
+          <t>H=0.0 | C=6.8 | D=2.0 | P=-0.0 | A=3.3 | R=3.5</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>13.37767314184953</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>4.277583736483633</v>
+        <v>6.828422784890696</v>
       </c>
       <c r="G29" t="n">
-        <v>1.795335530475587</v>
+        <v>1.997445423516802</v>
       </c>
       <c r="H29" t="n">
-        <v>2.996512179571294</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4.553141201040592</v>
+        <v>3.2748636400553</v>
       </c>
       <c r="J29" t="n">
         <v>3.5</v>
@@ -1852,17 +1852,17 @@
         <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>19.45059240880875</v>
+        <v>8.825868208407497</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C000232</t>
+          <t>C000348</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29.87318871685729</v>
+        <v>17.78779347681746</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1871,23 +1871,23 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>H=17.6 | C=0.0 | D=0.0 | P=-1.9 | A=2.9 | R=2.0</t>
+          <t>H=5.8 | C=2.9 | D=0.0 | P=-0.0 | A=1.9 | R=2.0</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>17.61071811422378</v>
+        <v>5.828603238273392</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2.86890669490137</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.947253160053559</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2.935119685703964</v>
+        <v>1.927736104679355</v>
       </c>
       <c r="J30" t="n">
         <v>2</v>
@@ -1901,42 +1901,42 @@
         <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>17.61071811422378</v>
+        <v>8.697509933174763</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C000233</t>
+          <t>C000359</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29.78690466377413</v>
+        <v>17.37305216081182</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>H=0.0 | C=13.3 | D=3.3 | P=-1.4 | A=6.1 | R=3.0</t>
+          <t>H=5.4 | C=3.0 | D=0.0 | P=-0.0 | A=1.9 | R=3.0</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>5.437333420947287</v>
       </c>
       <c r="F31" t="n">
-        <v>13.28084830990025</v>
+        <v>3.00381791568924</v>
       </c>
       <c r="G31" t="n">
-        <v>3.258585053510446</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.399195419795375</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>6.05624196338864</v>
+        <v>1.907494875387628</v>
       </c>
       <c r="J31" t="n">
         <v>3</v>
@@ -1950,33 +1950,33 @@
         <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>16.53943336341069</v>
+        <v>8.441151336636528</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C000234</t>
+          <t>C000373</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.78502792383085</v>
+        <v>16.50154086997915</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>H=0.0 | C=14.5 | D=0.0 | P=-0.0 | A=4.8 | R=3.5</t>
+          <t>H=5.3 | C=2.8 | D=0.0 | P=-0.0 | A=1.8 | R=2.0</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>5.260475422682626</v>
       </c>
       <c r="F32" t="n">
-        <v>14.47624324122829</v>
+        <v>2.799794475853701</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1985,56 +1985,56 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4.825414413742761</v>
+        <v>1.810010729065005</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>14.47624324122829</v>
+        <v>8.060269898536326</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C000236</t>
+          <t>C000374</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.67080423965606</v>
+        <v>16.42582573909884</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.8 | D=8.3 | P=-0.5 | A=6.4 | R=3.0</t>
+          <t>H=7.5 | C=3.9 | D=0.0 | P=-2.3 | A=2.5 | R=3.0</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>7.521288256284354</v>
       </c>
       <c r="F33" t="n">
-        <v>6.843680729381008</v>
+        <v>3.879753391496605</v>
       </c>
       <c r="G33" t="n">
-        <v>8.336535767153649</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5448594109167689</v>
+        <v>2.310312491261457</v>
       </c>
       <c r="I33" t="n">
-        <v>6.449494793370493</v>
+        <v>2.546799173212927</v>
       </c>
       <c r="J33" t="n">
         <v>3</v>
@@ -2048,42 +2048,42 @@
         <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>15.18021649653466</v>
+        <v>11.40104164778096</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C000237</t>
+          <t>C000375</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29.65337749634204</v>
+        <v>16.41970327459077</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>H=12.3 | C=0.0 | D=2.3 | P=-0.0 | A=3.2 | R=2.0</t>
+          <t>H=0.0 | C=5.2 | D=2.7 | P=-0.0 | A=3.1 | R=2.0</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>12.29483911743335</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5.20929074266048</v>
       </c>
       <c r="G34" t="n">
-        <v>2.272578183504773</v>
+        <v>2.745111592446077</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3.185428944657945</v>
+        <v>3.108986043776532</v>
       </c>
       <c r="J34" t="n">
         <v>2</v>
@@ -2097,17 +2097,17 @@
         <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>14.56741730093812</v>
+        <v>7.954402335106558</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C000255</t>
+          <t>C000378</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.31910562328143</v>
+        <v>16.31618536804281</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2116,23 +2116,23 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>H=10.7 | C=2.7 | D=0.4 | P=-0.0 | A=2.9 | R=3.0</t>
+          <t>H=5.4 | C=2.5 | D=0.0 | P=-0.0 | A=1.7 | R=3.0</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10.73502665302223</v>
+        <v>5.44073944244955</v>
       </c>
       <c r="F35" t="n">
-        <v>2.744008625141222</v>
+        <v>2.480669258575189</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3856834155607017</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2.896682358331131</v>
+        <v>1.733679659933321</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
@@ -2146,164 +2146,164 @@
         <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>13.86471869372416</v>
+        <v>7.921408701024738</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C000256</t>
+          <t>C000384</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.31599347229689</v>
+        <v>16.17813450811647</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>H=0.0 | C=9.3 | D=6.2 | P=-1.2 | A=6.2 | R=3.5</t>
+          <t>H=5.7 | C=2.2 | D=0.0 | P=-0.0 | A=1.7 | R=2.0</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>5.74908309956597</v>
       </c>
       <c r="F36" t="n">
-        <v>9.293787933061594</v>
+        <v>2.15613947081562</v>
       </c>
       <c r="G36" t="n">
-        <v>6.202845329523841</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.215736083484076</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>6.199351975782452</v>
+        <v>1.676893673532868</v>
       </c>
       <c r="J36" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>15.49663326258544</v>
+        <v>7.905222570381591</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C000269</t>
+          <t>C000400</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.45414082223904</v>
+        <v>15.81064129333414</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>H=0.0 | C=7.9 | D=5.8 | P=-0.2 | A=5.5 | R=2.0</t>
+          <t>H=4.9 | C=1.2 | D=1.6 | P=-0.0 | A=2.0 | R=3.5</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>4.850292848271179</v>
       </c>
       <c r="F37" t="n">
-        <v>7.87757381501067</v>
+        <v>1.162045182363996</v>
       </c>
       <c r="G37" t="n">
-        <v>5.797239897095484</v>
+        <v>1.617752282201856</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2159781302205788</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>5.524477886884632</v>
+        <v>2.00460667660079</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M37" t="n">
-        <v>13.67481371210615</v>
+        <v>7.630090312837032</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C000275</t>
+          <t>C000431</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.18593988812859</v>
+        <v>14.98406744396993</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>H=0.0 | C=10.3 | D=2.8 | P=-0.0 | A=4.9 | R=3.5</t>
+          <t>H=0.0 | C=2.6 | D=4.5 | P=-0.0 | A=3.2 | R=3.0</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>10.33562517301334</v>
+        <v>2.641167798158019</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83910668439096</v>
+        <v>4.543264839535915</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>4.864761733199926</v>
+        <v>3.152021685820631</v>
       </c>
       <c r="J38" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>13.1747318574043</v>
+        <v>7.184432637693934</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C000284</t>
+          <t>C000436</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26.83402955021101</v>
+        <v>14.88667615276281</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2312,23 +2312,23 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>H=5.9 | C=5.6 | D=1.6 | P=-0.0 | A=3.6 | R=3.0</t>
+          <t>H=13.9 | C=3.4 | D=1.9 | P=-8.1 | A=4.4 | R=3.0</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5.918118379367022</v>
+        <v>13.85548391651788</v>
       </c>
       <c r="F39" t="n">
-        <v>5.568349679355453</v>
+        <v>3.4155944537692</v>
       </c>
       <c r="G39" t="n">
-        <v>1.598461692909637</v>
+        <v>1.948527878092495</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>8.098246872767302</v>
       </c>
       <c r="I39" t="n">
-        <v>3.641700469467807</v>
+        <v>4.422042743055628</v>
       </c>
       <c r="J39" t="n">
         <v>3</v>
@@ -2342,17 +2342,17 @@
         <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>13.08492975163211</v>
+        <v>19.21960624837957</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C000293</t>
+          <t>C000441</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26.55330852804834</v>
+        <v>14.76387106472946</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2361,47 +2361,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>H=0.0 | C=13.0 | D=0.0 | P=-0.0 | A=4.3 | R=2.0</t>
+          <t>H=0.0 | C=5.2 | D=1.9 | P=-0.0 | A=2.7 | R=3.5</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>12.96064353838443</v>
+        <v>5.174152023405216</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1.899070870149035</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>4.320214512794809</v>
+        <v>2.674252776209589</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M40" t="n">
-        <v>12.96064353838443</v>
+        <v>7.07322289355425</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C000319</t>
+          <t>C000442</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25.47329289874901</v>
+        <v>14.6813859299164</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2410,23 +2410,23 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>H=10.2 | C=3.7 | D=0.0 | P=-0.9 | A=2.9 | R=2.0</t>
+          <t>H=5.4 | C=0.0 | D=1.8 | P=-0.0 | A=1.8 | R=2.0</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10.23535253588912</v>
+        <v>5.388515065030845</v>
       </c>
       <c r="F41" t="n">
-        <v>3.661746263817668</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.763193763628065</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9378507061299934</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2.926474177254076</v>
+        <v>1.77968272598584</v>
       </c>
       <c r="J41" t="n">
         <v>2</v>
@@ -2440,66 +2440,66 @@
         <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>13.89709879970679</v>
+        <v>7.15170882865891</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C000327</t>
+          <t>C000444</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25.14163866808258</v>
+        <v>14.59307223835925</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>H=0.0 | C=8.6 | D=3.6 | P=-0.0 | A=4.7 | R=3.0</t>
+          <t>H=0.0 | C=2.9 | D=4.2 | P=-0.0 | A=3.0 | R=2.0</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>8.618143666160218</v>
+        <v>2.884034236431071</v>
       </c>
       <c r="G42" t="n">
-        <v>3.569795063523645</v>
+        <v>4.160424044365566</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>4.657612087148562</v>
+        <v>3.041556767659807</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>12.18793872968386</v>
+        <v>7.044458280796637</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C000337</t>
+          <t>C000447</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24.51732104456848</v>
+        <v>14.55249223969727</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2508,72 +2508,72 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>H=10.9 | C=0.0 | D=1.1 | P=-0.0 | A=2.4 | R=3.0</t>
+          <t>H=7.1 | C=0.0 | D=0.0 | P=-0.0 | A=1.2 | R=2.0</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10.87807738630281</v>
+        <v>7.116938300676331</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.112129259605435</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>2.369077527519853</v>
+        <v>1.186156383446055</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>11.99020664590825</v>
+        <v>7.116938300676331</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C000360</t>
+          <t>C000470</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23.65870120292893</v>
+        <v>13.79945890552916</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.0 | D=8.4 | P=-0.0 | A=5.2 | R=3.0</t>
+          <t>H=5.6 | C=1.1 | D=0.0 | P=-0.0 | A=1.3 | R=3.0</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>5.62972871780407</v>
       </c>
       <c r="F44" t="n">
-        <v>2.991529793876747</v>
+        <v>1.055494749815221</v>
       </c>
       <c r="G44" t="n">
-        <v>8.427279978233926</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>5.210816587075879</v>
+        <v>1.290119702905752</v>
       </c>
       <c r="J44" t="n">
         <v>3</v>
@@ -2587,66 +2587,66 @@
         <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>11.41880977211067</v>
+        <v>6.685223467619291</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C000365</t>
+          <t>C000486</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>23.39208838916966</v>
+        <v>13.50156286301008</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>H=1.3 | C=7.3 | D=2.6 | P=-0.0 | A=4.0 | R=3.5</t>
+          <t>H=0.0 | C=2.6 | D=5.8 | P=-1.2 | A=3.7 | R=2.0</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.347116613412998</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>7.330353120071823</v>
+        <v>2.575962790423339</v>
       </c>
       <c r="G45" t="n">
-        <v>2.644074085190606</v>
+        <v>5.751932056392683</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1.242562953263016</v>
       </c>
       <c r="I45" t="n">
-        <v>3.990007518188078</v>
+        <v>3.734620291670788</v>
       </c>
       <c r="J45" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>11.32154381867543</v>
+        <v>8.327894846816022</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C000366</t>
+          <t>C000501</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23.32770226358961</v>
+        <v>13.16244521566322</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2655,23 +2655,23 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>H=4.8 | C=4.7 | D=2.0 | P=-0.0 | A=3.3 | R=2.0</t>
+          <t>H=3.8 | C=2.6 | D=0.0 | P=-0.0 | A=1.5 | R=2.0</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4.751404269157518</v>
+        <v>3.805604668152633</v>
       </c>
       <c r="F46" t="n">
-        <v>4.681731258569999</v>
+        <v>2.600561869617414</v>
       </c>
       <c r="G46" t="n">
-        <v>1.963991916274611</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3.334473755853558</v>
+        <v>1.501121401231244</v>
       </c>
       <c r="J46" t="n">
         <v>2</v>
@@ -2685,91 +2685,91 @@
         <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>11.39712744400213</v>
+        <v>6.406166537770048</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C000367</t>
+          <t>C000512</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.30126462408094</v>
+        <v>12.94358592811864</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>H=3.3 | C=5.8 | D=7.2 | P=-3.4 | A=6.1 | R=3.5</t>
+          <t>H=6.3 | C=0.0 | D=0.0 | P=-0.0 | A=1.1 | R=2.0</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3.279199862438197</v>
+        <v>6.319133518075361</v>
       </c>
       <c r="F47" t="n">
-        <v>5.797133313552486</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>7.173860778249615</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>3.385235810490398</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>6.065841470715336</v>
+        <v>1.053188919679227</v>
       </c>
       <c r="J47" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>16.2501939542403</v>
+        <v>6.319133518075361</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C000374</t>
+          <t>C000525</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>23.0468057468277</v>
+        <v>12.67036808344561</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>H=8.7 | C=3.4 | D=0.0 | P=-0.6 | A=2.6 | R=3.0</t>
+          <t>H=0.0 | C=3.5 | D=2.6 | P=-0.0 | A=2.5 | R=3.0</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8.669799490382481</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>3.436334024766553</v>
+        <v>3.458027088474403</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2.60441284725902</v>
       </c>
       <c r="H48" t="n">
-        <v>0.574834136378542</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2.590411256652598</v>
+        <v>2.454882119787645</v>
       </c>
       <c r="J48" t="n">
         <v>3</v>
@@ -2783,115 +2783,115 @@
         <v>3</v>
       </c>
       <c r="M48" t="n">
-        <v>12.10613351514903</v>
+        <v>6.062439935733424</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C000386</t>
+          <t>C000535</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>22.74009514736496</v>
+        <v>12.4189483577034</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>H=5.7 | C=5.7 | D=0.0 | P=-0.2 | A=2.8 | R=3.0</t>
+          <t>H=6.0 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.5</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.690923588866131</v>
+        <v>5.984602491423172</v>
       </c>
       <c r="F49" t="n">
-        <v>5.691560857511753</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2031470557074349</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>2.84567421731494</v>
+        <v>0.9974337485705287</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>11.38248444637788</v>
+        <v>5.984602491423172</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C000421</t>
+          <t>C000548</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>21.54942196917226</v>
+        <v>12.19696930611751</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>H=2.6 | C=5.8 | D=2.6 | P=-0.4 | A=3.7 | R=2.0</t>
+          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.615922729591706</v>
+        <v>5.899323622868189</v>
       </c>
       <c r="F50" t="n">
-        <v>5.791286921188151</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>2.617407138272108</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3557745251260244</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>3.675119664464055</v>
+        <v>0.9832206038113648</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>11.02461678905197</v>
+        <v>5.899323622868189</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C000422</t>
+          <t>C000549</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>21.53563208013511</v>
+        <v>12.19684901270042</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2900,72 +2900,72 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>H=5.1 | C=3.6 | D=4.7 | P=-2.0 | A=4.4 | R=3.0</t>
+          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.131118382741906</v>
+        <v>5.94885075009938</v>
       </c>
       <c r="F51" t="n">
-        <v>3.610072575756656</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>4.704276509658633</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.032123691299934</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>4.410682177205186</v>
+        <v>0.9914751250165634</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>13.44546746815719</v>
+        <v>5.94885075009938</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C000445</t>
+          <t>C000556</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>21.02802283310387</v>
+        <v>12.10020673847659</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.7 | D=5.5 | P=-0.0 | A=4.3 | R=2.0</t>
+          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>5.900928961228063</v>
       </c>
       <c r="F52" t="n">
-        <v>4.720198632751612</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>5.478188103988093</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>4.312493596244584</v>
+        <v>0.9834881602046772</v>
       </c>
       <c r="J52" t="n">
         <v>2</v>
@@ -2979,42 +2979,42 @@
         <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>10.1983867367397</v>
+        <v>5.900928961228063</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C000461</t>
+          <t>C000559</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>20.32624734084814</v>
+        <v>12.07083942018262</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.9 | D=6.7 | P=-1.9 | A=5.3 | R=3.0</t>
+          <t>H=5.8 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>5.836779877776503</v>
       </c>
       <c r="F53" t="n">
-        <v>5.899692843456029</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>6.706406168896692</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.905975806805779</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>5.319767365600356</v>
+        <v>0.9727966462960839</v>
       </c>
       <c r="J53" t="n">
         <v>3</v>
@@ -3028,17 +3028,17 @@
         <v>3</v>
       </c>
       <c r="M53" t="n">
-        <v>12.60609901235272</v>
+        <v>5.836779877776503</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C000487</t>
+          <t>C000571</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>19.59666437739208</v>
+        <v>11.92500971982725</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3047,23 +3047,23 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.9 | D=4.6 | P=-0.0 | A=3.9 | R=3.5</t>
+          <t>H=0.0 | C=5.7 | D=0.0 | P=-0.0 | A=1.9 | R=3.5</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>4.867765445399894</v>
+        <v>5.692627731062584</v>
       </c>
       <c r="G54" t="n">
-        <v>4.560426652884045</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>3.902801808241987</v>
+        <v>1.897542577020861</v>
       </c>
       <c r="J54" t="n">
         <v>3.5</v>
@@ -3077,42 +3077,42 @@
         <v>4</v>
       </c>
       <c r="M54" t="n">
-        <v>9.42819209828394</v>
+        <v>5.692627731062584</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C000506</t>
+          <t>C000575</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>18.47197316485219</v>
+        <v>11.89391447958141</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=6.0 | P=-0.0 | A=4.0 | R=3.0</t>
+          <t>H=4.5 | C=0.0 | D=1.2 | P=-0.0 | A=1.4 | R=3.0</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>4.528969473397168</v>
       </c>
       <c r="F55" t="n">
-        <v>2.917634677831475</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>5.970463082891799</v>
+        <v>1.200240345478271</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>3.957776434056391</v>
+        <v>1.35494841830533</v>
       </c>
       <c r="J55" t="n">
         <v>3</v>
@@ -3126,42 +3126,42 @@
         <v>3</v>
       </c>
       <c r="M55" t="n">
-        <v>8.888097760723273</v>
+        <v>5.729209818875439</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C000512</t>
+          <t>C000578</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>18.415312824685</v>
+        <v>11.83760519345153</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>H=1.8 | C=4.7 | D=2.4 | P=-0.0 | A=3.1 | R=3.0</t>
+          <t>H=0.0 | C=2.4 | D=3.3 | P=-0.0 | A=2.4 | R=3.0</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.811551046669753</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>4.654784784835195</v>
+        <v>2.382385358841616</v>
       </c>
       <c r="G56" t="n">
-        <v>2.43770202507452</v>
+        <v>3.265083722182235</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>3.072371115260617</v>
+        <v>2.426670314038323</v>
       </c>
       <c r="J56" t="n">
         <v>3</v>
@@ -3175,91 +3175,91 @@
         <v>3</v>
       </c>
       <c r="M56" t="n">
-        <v>8.904037856579468</v>
+        <v>5.647469081023851</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C000515</t>
+          <t>C000601</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>18.32922278082053</v>
+        <v>11.5213346838246</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.8 | D=2.0 | P=-0.0 | A=3.3 | R=3.5</t>
+          <t>H=5.6 | C=0.0 | D=0.0 | P=-0.0 | A=0.9 | R=3.0</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>5.564298190326248</v>
       </c>
       <c r="F57" t="n">
-        <v>6.828422784890696</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>1.997445423516802</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>3.2748636400553</v>
+        <v>0.9273830317210414</v>
       </c>
       <c r="J57" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M57" t="n">
-        <v>8.825868208407497</v>
+        <v>5.564298190326248</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C000518</t>
+          <t>C000610</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>18.22460969617751</v>
+        <v>11.4055323067991</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.4 | D=3.3 | P=-0.6 | A=3.8 | R=2.0</t>
+          <t>H=10.2 | C=3.7 | D=0.0 | P=-5.6 | A=2.9 | R=2.0</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>10.23535253588912</v>
       </c>
       <c r="F58" t="n">
-        <v>6.416210399663416</v>
+        <v>3.661746263817668</v>
       </c>
       <c r="G58" t="n">
-        <v>3.341731102511008</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.624077847761888</v>
+        <v>5.62710423677996</v>
       </c>
       <c r="I58" t="n">
-        <v>3.809602351143309</v>
+        <v>2.926474177254076</v>
       </c>
       <c r="J58" t="n">
         <v>2</v>
@@ -3273,66 +3273,66 @@
         <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>9.757941502174424</v>
+        <v>13.89709879970679</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C000530</t>
+          <t>C000615</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>17.78779347681746</v>
+        <v>11.31550142288359</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>H=5.8 | C=2.9 | D=0.0 | P=-0.0 | A=1.9 | R=2.0</t>
+          <t>H=0.0 | C=6.9 | D=0.0 | P=-1.0 | A=2.3 | R=3.0</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5.828603238273392</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>2.86890669490137</v>
+        <v>6.915401198305339</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1.01527144900131</v>
       </c>
       <c r="I59" t="n">
-        <v>1.927736104679355</v>
+        <v>2.305133732768446</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M59" t="n">
-        <v>8.697509933174763</v>
+        <v>6.915401198305339</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C000533</t>
+          <t>C000621</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>17.73264686731064</v>
+        <v>11.28080399030465</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3341,23 +3341,23 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>H=0.0 | C=8.8 | D=1.8 | P=-1.4 | A=3.9 | R=2.0</t>
+          <t>H=0.0 | C=3.8 | D=1.6 | P=-0.0 | A=2.1 | R=2.0</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>8.806665372464053</v>
+        <v>3.825468315911813</v>
       </c>
       <c r="G60" t="n">
-        <v>1.84204772272664</v>
+        <v>1.610903291683232</v>
       </c>
       <c r="H60" t="n">
-        <v>1.383479073874183</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>3.856578985518005</v>
+        <v>2.080607751145554</v>
       </c>
       <c r="J60" t="n">
         <v>2</v>
@@ -3371,66 +3371,66 @@
         <v>2</v>
       </c>
       <c r="M60" t="n">
-        <v>10.64871309519069</v>
+        <v>5.436371607595046</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C000535</t>
+          <t>C000634</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>17.61996588179715</v>
+        <v>11.09731279919482</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>H=9.9 | C=0.0 | D=0.0 | P=-0.9 | A=1.7 | R=3.5</t>
+          <t>H=0.0 | C=5.4 | D=0.0 | P=-0.0 | A=1.8 | R=2.0</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>9.935506270492084</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>5.359334163538437</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9222128101206288</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1.655917711748681</v>
+        <v>1.786444721179479</v>
       </c>
       <c r="J61" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>9.935506270492084</v>
+        <v>5.359334163538437</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C000543</t>
+          <t>C000636</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>17.39385832882905</v>
+        <v>11.06580893172652</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3439,14 +3439,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>H=0.0 | C=8.5 | D=0.0 | P=-0.0 | A=2.8 | R=2.0</t>
+          <t>H=0.0 | C=5.3 | D=0.0 | P=-0.0 | A=1.8 | R=3.0</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>8.455995899424126</v>
+        <v>5.294660130357306</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3455,31 +3455,31 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2.818665299808043</v>
+        <v>1.764886710119102</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M62" t="n">
-        <v>8.455995899424126</v>
+        <v>5.294660130357306</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C000544</t>
+          <t>C000665</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>17.37305216081182</v>
+        <v>10.75390753275266</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3488,14 +3488,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>H=5.4 | C=3.0 | D=0.0 | P=-0.0 | A=1.9 | R=3.0</t>
+          <t>H=5.2 | C=0.0 | D=0.0 | P=-0.0 | A=0.9 | R=2.0</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5.437333420947287</v>
+        <v>5.233342578224462</v>
       </c>
       <c r="F63" t="n">
-        <v>3.00381791568924</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3504,105 +3504,105 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>1.907494875387628</v>
+        <v>0.8722237630374104</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
-        <v>8.441151336636528</v>
+        <v>5.233342578224462</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C000553</t>
+          <t>C000668</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>17.02793349970533</v>
+        <v>10.71938941581399</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>H=6.3 | C=2.2 | D=1.2 | P=-1.0 | A=2.4 | R=3.0</t>
+          <t>H=0.0 | C=5.1 | D=0.0 | P=-0.0 | A=1.7 | R=3.5</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6.307560590934778</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>2.206768992726267</v>
+        <v>5.099699712695404</v>
       </c>
       <c r="G64" t="n">
-        <v>1.171262559940401</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9601662972559033</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>2.372481042701419</v>
+        <v>1.699899904231801</v>
       </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M64" t="n">
-        <v>9.685592143601447</v>
+        <v>5.099699712695404</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C000554</t>
+          <t>C000693</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>16.99018155819507</v>
+        <v>10.46730168377295</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>H=0.0 | C=0.9 | D=9.9 | P=-1.8 | A=5.2 | R=3.0</t>
+          <t>H=0.0 | C=6.2 | D=0.0 | P=-0.8 | A=2.1 | R=3.0</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9082648219273907</v>
+        <v>6.237103010418305</v>
       </c>
       <c r="G65" t="n">
-        <v>9.883621531278193</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1.806015906281419</v>
+        <v>0.8382692569147558</v>
       </c>
       <c r="I65" t="n">
-        <v>5.24456570628156</v>
+        <v>2.079034336806101</v>
       </c>
       <c r="J65" t="n">
         <v>3</v>
@@ -3616,164 +3616,164 @@
         <v>3</v>
       </c>
       <c r="M65" t="n">
-        <v>10.79188635320558</v>
+        <v>6.237103010418305</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C000560</t>
+          <t>C000716</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>16.60797024616761</v>
+        <v>10.28176721062322</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.6 | D=5.8 | P=-0.2 | A=3.7 | R=2.0</t>
+          <t>H=0.0 | C=3.0 | D=1.9 | P=-0.0 | A=2.0 | R=3.0</t>
         </is>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>2.575962790423339</v>
+        <v>2.952950685399849</v>
       </c>
       <c r="G66" t="n">
-        <v>5.751932056392683</v>
+        <v>1.940211780639116</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2070938255438359</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>3.734620291670788</v>
+        <v>1.954422785452841</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M66" t="n">
-        <v>8.327894846816022</v>
+        <v>4.893162466038965</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C000565</t>
+          <t>C000734</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>16.50154086997915</v>
+        <v>10.00108796174218</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>H=5.3 | C=2.8 | D=0.0 | P=-0.0 | A=1.8 | R=2.0</t>
+          <t>H=0.0 | C=2.8 | D=1.9 | P=-0.0 | A=1.9 | R=3.0</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5.260475422682626</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>2.799794475853701</v>
+        <v>2.827951706319173</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1.927277801086113</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1.810010729065005</v>
+        <v>1.906289469316114</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>8.060269898536326</v>
+        <v>4.755229507405287</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C000566</t>
+          <t>C000761</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>16.48572350813675</v>
+        <v>9.625495042231302</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>H=0.0 | C=0.0 | D=9.3 | P=-1.0 | A=4.7 | R=3.5</t>
+          <t>H=0.0 | C=4.6 | D=0.0 | P=-0.0 | A=1.5 | R=2.0</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>4.635489365031789</v>
       </c>
       <c r="G68" t="n">
-        <v>9.30590853933848</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.9804629991690461</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>4.65295426966924</v>
+        <v>1.545163121677263</v>
       </c>
       <c r="J68" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>9.30590853933848</v>
+        <v>4.635489365031789</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C000568</t>
+          <t>C000778</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>16.41970327459077</v>
+        <v>9.425271785204528</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3782,112 +3782,112 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.2 | D=2.7 | P=-0.0 | A=3.1 | R=2.0</t>
+          <t>H=0.0 | C=4.5 | D=0.0 | P=-0.0 | A=1.5 | R=3.5</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>5.20929074266048</v>
+        <v>4.463248418953047</v>
       </c>
       <c r="G69" t="n">
-        <v>2.745111592446077</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>3.108986043776532</v>
+        <v>1.487749472984349</v>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M69" t="n">
-        <v>7.954402335106558</v>
+        <v>4.463248418953047</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C000571</t>
+          <t>C000811</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>16.32842763473408</v>
+        <v>9.09215250078045</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>H=5.5 | C=0.0 | D=3.8 | P=-1.0 | A=2.8 | R=3.0</t>
+          <t>H=0.0 | C=4.4 | D=0.0 | P=-0.0 | A=1.5 | R=2.0</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5.54053973404824</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>4.373189754482189</v>
       </c>
       <c r="G70" t="n">
-        <v>3.77259576442984</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9596051597814594</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>2.80972117122296</v>
+        <v>1.45772991816073</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>9.313135498478079</v>
+        <v>4.373189754482189</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C000572</t>
+          <t>C000812</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>16.31618536804281</v>
+        <v>9.043081382307493</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>H=5.4 | C=2.5 | D=0.0 | P=-0.0 | A=1.7 | R=3.0</t>
+          <t>H=0.0 | C=4.3 | D=0.0 | P=-0.0 | A=1.4 | R=3.0</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5.44073944244955</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>2.480669258575189</v>
+        <v>4.299876089659422</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1.733679659933321</v>
+        <v>1.433292029886474</v>
       </c>
       <c r="J71" t="n">
         <v>3</v>
@@ -3910,140 +3910,140 @@
         <v>3</v>
       </c>
       <c r="M71" t="n">
-        <v>7.921408701024738</v>
+        <v>4.299876089659422</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C000579</t>
+          <t>C000846</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>16.17813450811647</v>
+        <v>8.733486528088097</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>H=5.7 | C=2.2 | D=0.0 | P=-0.0 | A=1.7 | R=2.0</t>
+          <t>H=0.0 | C=2.7 | D=1.4 | P=-0.0 | A=1.6 | R=3.0</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5.74908309956597</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>2.15613947081562</v>
+        <v>2.737857030764379</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1.398297836845784</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1.676893673532868</v>
+        <v>1.611767928677685</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>7.905222570381591</v>
+        <v>4.136154867610164</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C000600</t>
+          <t>C000850</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>15.81064129333414</v>
+        <v>8.705932181602464</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>H=4.9 | C=1.2 | D=1.6 | P=-0.0 | A=2.0 | R=3.5</t>
+          <t>H=0.0 | C=4.2 | D=0.0 | P=-0.0 | A=1.4 | R=2.0</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.850292848271179</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>1.162045182363996</v>
+        <v>4.183245335214327</v>
       </c>
       <c r="G73" t="n">
-        <v>1.617752282201856</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>2.00460667660079</v>
+        <v>1.394415111738109</v>
       </c>
       <c r="J73" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>7.630090312837032</v>
+        <v>4.183245335214327</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C000606</t>
+          <t>C000851</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>15.72896932895364</v>
+        <v>8.703729783135666</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>H=1.2 | C=2.7 | D=3.8 | P=-0.0 | A=3.0 | R=2.0</t>
+          <t>H=4.2 | C=0.0 | D=0.0 | P=-0.0 | A=0.7 | R=2.0</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1.158488702213862</v>
+        <v>4.216725512298678</v>
       </c>
       <c r="F74" t="n">
-        <v>2.686607176822308</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>3.770690660138368</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>2.973962506045598</v>
+        <v>0.7027875853831129</v>
       </c>
       <c r="J74" t="n">
         <v>2</v>
@@ -4057,42 +4057,42 @@
         <v>2</v>
       </c>
       <c r="M74" t="n">
-        <v>7.615786539174539</v>
+        <v>4.216725512298678</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C000607</t>
+          <t>C000861</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>15.69022000047718</v>
+        <v>8.617137835054999</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.2 | D=3.3 | P=-0.0 | A=3.1 | R=3.5</t>
+          <t>H=4.1 | C=0.0 | D=0.0 | P=-0.0 | A=0.7 | R=3.5</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>4.099407190936363</v>
       </c>
       <c r="F75" t="n">
-        <v>4.231763823857031</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>3.285674906651002</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>3.053425394611178</v>
+        <v>0.6832345318227271</v>
       </c>
       <c r="J75" t="n">
         <v>3.5</v>
@@ -4106,189 +4106,189 @@
         <v>4</v>
       </c>
       <c r="M75" t="n">
-        <v>7.517438730508032</v>
+        <v>4.099407190936363</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C000613</t>
+          <t>C000901</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15.60569411954249</v>
+        <v>8.199824476958087</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>H=4.5 | C=1.9 | D=1.7 | P=-0.4 | A=2.3 | R=3.0</t>
+          <t>H=0.0 | C=3.9 | D=0.0 | P=-0.0 | A=1.3 | R=3.5</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4.503849073887534</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>1.931134245971533</v>
+        <v>3.860569414897419</v>
       </c>
       <c r="G76" t="n">
-        <v>1.719145988921847</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.4093190300764241</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2.253925922099357</v>
+        <v>1.286856471632473</v>
       </c>
       <c r="J76" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M76" t="n">
-        <v>8.154129308780913</v>
+        <v>3.860569414897419</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C000618</t>
+          <t>C000911</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>15.44847553544829</v>
+        <v>8.083234670820534</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>H=0.0 | C=0.7 | D=6.6 | P=-0.0 | A=3.6 | R=3.5</t>
+          <t>H=0.0 | C=3.8 | D=0.0 | P=-0.0 | A=1.3 | R=3.0</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7428713297310472</v>
+        <v>3.827820329911738</v>
       </c>
       <c r="G77" t="n">
-        <v>6.628278291867558</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>3.561762922510795</v>
+        <v>1.275940109970579</v>
       </c>
       <c r="J77" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M77" t="n">
-        <v>7.371149621598605</v>
+        <v>3.827820329911738</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C000633</t>
+          <t>C000918</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>15.22772739508422</v>
+        <v>8.024684789096783</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.3 | D=1.6 | P=-0.4 | A=2.9 | R=3.0</t>
+          <t>H=0.0 | C=1.9 | D=1.9 | P=-0.0 | A=1.6 | R=3.5</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>6.333522103226265</v>
+        <v>1.864966596162784</v>
       </c>
       <c r="G78" t="n">
-        <v>1.614654780320099</v>
+        <v>1.893944411495507</v>
       </c>
       <c r="H78" t="n">
-        <v>0.4201588381551292</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>2.918501424568805</v>
+        <v>1.568627737802015</v>
       </c>
       <c r="J78" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M78" t="n">
-        <v>7.948176883546364</v>
+        <v>3.758911007658291</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C000636</t>
+          <t>C000923</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>15.14300395346061</v>
+        <v>7.970356856189654</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.4 | D=5.3 | P=-1.7 | A=4.1 | R=3.0</t>
+          <t>H=0.0 | C=3.8 | D=0.0 | P=-0.0 | A=1.3 | R=3.0</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>4.417952581680571</v>
+        <v>3.772306650585076</v>
       </c>
       <c r="G79" t="n">
-        <v>5.289894599924521</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>1.661483408600607</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>4.117598160522451</v>
+        <v>1.257435550195025</v>
       </c>
       <c r="J79" t="n">
         <v>3</v>
@@ -4302,42 +4302,42 @@
         <v>3</v>
       </c>
       <c r="M79" t="n">
-        <v>9.707847181605093</v>
+        <v>3.772306650585076</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C000642</t>
+          <t>C000944</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>14.98406744396993</v>
+        <v>7.80832753055957</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.6 | D=4.5 | P=-0.0 | A=3.2 | R=3.0</t>
+          <t>H=0.0 | C=3.7 | D=0.0 | P=-0.0 | A=1.2 | R=3.0</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>2.641167798158019</v>
+        <v>3.69262009699651</v>
       </c>
       <c r="G80" t="n">
-        <v>4.543264839535915</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>3.152021685820631</v>
+        <v>1.230873365665503</v>
       </c>
       <c r="J80" t="n">
         <v>3</v>
@@ -4351,91 +4351,91 @@
         <v>3</v>
       </c>
       <c r="M80" t="n">
-        <v>7.184432637693934</v>
+        <v>3.69262009699651</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C000645</t>
+          <t>C000973</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>14.89756093439275</v>
+        <v>7.513827925063221</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>H=0.8 | C=4.4 | D=1.9 | P=-0.0 | A=2.6 | R=3.5</t>
+          <t>H=0.0 | C=0.0 | D=3.5 | P=-0.0 | A=1.8 | R=3.0</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8378481678454439</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>4.411657315832509</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1.896356383924392</v>
+        <v>3.518940451250351</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>2.558371991880606</v>
+        <v>1.759470225625176</v>
       </c>
       <c r="J81" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M81" t="n">
-        <v>7.145861867602344</v>
+        <v>3.518940451250351</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C000651</t>
+          <t>C000998</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>14.78588789452298</v>
+        <v>7.311229723353519</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>H=5.7 | C=2.9 | D=0.0 | P=-1.0 | A=1.9 | R=2.0</t>
+          <t>H=0.0 | C=3.5 | D=0.0 | P=-0.0 | A=1.2 | R=2.0</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5.721305405365494</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>2.924839287530153</v>
+        <v>3.49732609345255</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9664170747584707</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>1.928497330070967</v>
+        <v>1.165775364484184</v>
       </c>
       <c r="J82" t="n">
         <v>2</v>
@@ -4449,42 +4449,42 @@
         <v>2</v>
       </c>
       <c r="M82" t="n">
-        <v>8.646144692895646</v>
+        <v>3.49732609345255</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C000652</t>
+          <t>C001013</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>14.76649107835405</v>
+        <v>7.147407283745667</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>H=5.9 | C=1.3 | D=0.0 | P=-0.0 | A=1.4 | R=2.0</t>
+          <t>H=0.0 | C=2.9 | D=0.5 | P=-0.0 | A=1.2 | R=2.0</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5.946306353309759</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>1.266281934022641</v>
+        <v>2.936381335558953</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>0.4764708462320955</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1.413145036892507</v>
+        <v>1.217029201635699</v>
       </c>
       <c r="J83" t="n">
         <v>2</v>
@@ -4498,91 +4498,91 @@
         <v>2</v>
       </c>
       <c r="M83" t="n">
-        <v>7.2125882873324</v>
+        <v>3.412852181791048</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C000660</t>
+          <t>C001023</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>14.6813859299164</v>
+        <v>7.066111653949901</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>H=5.4 | C=0.0 | D=1.8 | P=-0.0 | A=1.8 | R=2.0</t>
+          <t>H=2.3 | C=0.0 | D=1.0 | P=-0.0 | A=0.9 | R=3.5</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5.388515065030845</v>
+        <v>2.341859880898093</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1.763193763628065</v>
+        <v>0.9723711678725593</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>1.77968272598584</v>
+        <v>0.8764955640859617</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M84" t="n">
-        <v>7.15170882865891</v>
+        <v>3.314231048770652</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C000665</t>
+          <t>C001036</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>14.59307223835925</v>
+        <v>6.924815656613203</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=4.2 | P=-0.0 | A=3.0 | R=2.0</t>
+          <t>H=0.0 | C=3.3 | D=0.0 | P=-0.0 | A=1.1 | R=2.0</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>2.884034236431071</v>
+        <v>3.307286388498296</v>
       </c>
       <c r="G85" t="n">
-        <v>4.160424044365566</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>3.041556767659807</v>
+        <v>1.102428796166099</v>
       </c>
       <c r="J85" t="n">
         <v>2</v>
@@ -4596,140 +4596,140 @@
         <v>2</v>
       </c>
       <c r="M85" t="n">
-        <v>7.044458280796637</v>
+        <v>3.307286388498296</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C000669</t>
+          <t>C001063</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>14.55249223969727</v>
+        <v>6.72245155385994</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>H=7.1 | C=0.0 | D=0.0 | P=-0.0 | A=1.2 | R=2.0</t>
+          <t>H=0.0 | C=0.0 | D=3.1 | P=-0.0 | A=1.6 | R=3.0</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>7.116938300676331</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>3.132903197004849</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1.186156383446055</v>
+        <v>1.566451598502424</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M86" t="n">
-        <v>7.116938300676331</v>
+        <v>3.132903197004849</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C000680</t>
+          <t>C001083</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>14.38340963405767</v>
+        <v>6.445954548197911</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>H=2.7 | C=1.7 | D=2.5 | P=-0.0 | A=2.3 | R=3.0</t>
+          <t>H=3.1 | C=0.0 | D=0.0 | P=-0.0 | A=0.5 | R=2.0</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2.734712249215978</v>
+        <v>3.097167544560947</v>
       </c>
       <c r="F87" t="n">
-        <v>1.666025221842117</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>2.527230234338119</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>2.274742232652428</v>
+        <v>0.5161945907601578</v>
       </c>
       <c r="J87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M87" t="n">
-        <v>6.927967705396214</v>
+        <v>3.097167544560947</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C000692</t>
+          <t>C001103</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>14.21907066205051</v>
+        <v>6.272547807805161</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>H=5.5 | C=0.7 | D=1.9 | P=-0.8 | A=2.1 | R=3.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5.544291787941484</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6534682877090318</v>
+        <v>2.937318594002538</v>
       </c>
       <c r="G88" t="n">
-        <v>1.903445908752385</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.8309002471940794</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>2.09359434826945</v>
+        <v>0.9791061980008461</v>
       </c>
       <c r="J88" t="n">
         <v>3</v>
@@ -4743,17 +4743,17 @@
         <v>3</v>
       </c>
       <c r="M88" t="n">
-        <v>8.101205984402901</v>
+        <v>2.937318594002538</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C000699</t>
+          <t>C001105</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>14.02179814421483</v>
+        <v>6.26193764844994</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4762,96 +4762,96 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>H=1.5 | C=3.1 | D=2.3 | P=-0.1 | A=2.4 | R=3.0</t>
+          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.547325912902204</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>3.06590878367104</v>
+        <v>2.981280810713085</v>
       </c>
       <c r="G89" t="n">
-        <v>2.331189165396169</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1371982542215158</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>2.445451829405465</v>
+        <v>0.993760270237695</v>
       </c>
       <c r="J89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M89" t="n">
-        <v>6.944423861969413</v>
+        <v>2.981280810713085</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C000711</t>
+          <t>C001107</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>13.85580930271118</v>
+        <v>6.252125132700542</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>H=5.7 | C=0.6 | D=1.8 | P=-0.9 | A=2.1 | R=2.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5.736013654522957</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6055076167163521</v>
+        <v>2.927274655426496</v>
       </c>
       <c r="G90" t="n">
-        <v>1.797532318362557</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.942652769069979</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>2.056604307173889</v>
+        <v>0.9757582184754987</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>8.139053589601865</v>
+        <v>2.927274655426496</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C000712</t>
+          <t>C001108</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>13.85368004538687</v>
+        <v>6.24441894686862</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4860,63 +4860,63 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.9 | D=0.0 | P=-0.2 | A=2.3 | R=3.0</t>
+          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>6.915401198305339</v>
+        <v>2.972665055837026</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1692119081668849</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>2.305133732768446</v>
+        <v>0.9908883519456754</v>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>6.915401198305339</v>
+        <v>2.972665055837026</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C000713</t>
+          <t>C001113</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>13.79945890552916</v>
+        <v>6.223732527693402</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>H=5.6 | C=1.1 | D=0.0 | P=-0.0 | A=1.3 | R=3.0</t>
+          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5.62972871780407</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>1.055494749815221</v>
+        <v>2.962491407062329</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -4925,56 +4925,56 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1.290119702905752</v>
+        <v>0.9874971356874429</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>6.685223467619291</v>
+        <v>2.962491407062329</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C000721</t>
+          <t>C001119</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>13.6660936072784</v>
+        <v>6.201073430803066</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.6 | D=4.0 | P=-0.7 | A=3.2 | R=3.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>3.605377395636738</v>
+        <v>2.902167261050689</v>
       </c>
       <c r="G93" t="n">
-        <v>3.99824559619111</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.7204146342360243</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>3.200915263307802</v>
+        <v>0.9673890870168962</v>
       </c>
       <c r="J93" t="n">
         <v>3</v>
@@ -4988,42 +4988,42 @@
         <v>3</v>
       </c>
       <c r="M93" t="n">
-        <v>7.603622991827848</v>
+        <v>2.902167261050689</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C000728</t>
+          <t>C001125</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13.52070362903862</v>
+        <v>6.14691969457726</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>H=4.6 | C=0.0 | D=1.9 | P=-0.0 | A=1.7 | R=3.5</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.5</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4.641930563591517</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>2.850944112087177</v>
       </c>
       <c r="G94" t="n">
-        <v>1.858281459737751</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>1.702795823800795</v>
+        <v>0.9503147040290592</v>
       </c>
       <c r="J94" t="n">
         <v>3.5</v>
@@ -5037,17 +5037,17 @@
         <v>4</v>
       </c>
       <c r="M94" t="n">
-        <v>6.500212023329269</v>
+        <v>2.850944112087177</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C000734</t>
+          <t>C001132</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>13.38969857349016</v>
+        <v>6.111408888303061</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -5056,72 +5056,72 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.9 | D=3.1 | P=-0.4 | A=2.9 | R=3.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
         </is>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>3.881631369700499</v>
+        <v>2.907250272935932</v>
       </c>
       <c r="G95" t="n">
-        <v>3.129223271169638</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0.4059531947106504</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>2.858488758818318</v>
+        <v>0.9690834243119771</v>
       </c>
       <c r="J95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>7.010854640870137</v>
+        <v>2.907250272935932</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C000740</t>
+          <t>C001133</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>13.28265843432246</v>
+        <v>6.107434725714692</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>H=2.4 | C=4.0 | D=0.7 | P=-0.5 | A=2.1 | R=3.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2.419159812851364</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>4.025842159608742</v>
+        <v>2.856115438876078</v>
       </c>
       <c r="G96" t="n">
-        <v>0.6977347781186738</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.5040719582029481</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>2.094008077737478</v>
+        <v>0.9520384796253594</v>
       </c>
       <c r="J96" t="n">
         <v>3</v>
@@ -5135,42 +5135,42 @@
         <v>3</v>
       </c>
       <c r="M96" t="n">
-        <v>7.14273675057878</v>
+        <v>2.856115438876078</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C000748</t>
+          <t>C001141</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.12444619484244</v>
+        <v>6.070292466579317</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>H=4.4 | C=2.2 | D=0.0 | P=-0.2 | A=1.5 | R=3.0</t>
+          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=3.0</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4.365611028448806</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>2.234343965794827</v>
+        <v>2.837848754055402</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1742340365484885</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>1.47238316000641</v>
+        <v>0.9459495846851339</v>
       </c>
       <c r="J97" t="n">
         <v>3</v>
@@ -5184,42 +5184,42 @@
         <v>3</v>
       </c>
       <c r="M97" t="n">
-        <v>6.599954994243634</v>
+        <v>2.837848754055402</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C000774</t>
+          <t>C001145</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>12.82641822141435</v>
+        <v>6.042931198203846</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>H=0.0 | C=1.2 | D=5.0 | P=-0.0 | A=2.9 | R=2.0</t>
+          <t>H=2.9 | C=0.0 | D=0.0 | P=-0.0 | A=0.5 | R=2.0</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>2.897321255307693</v>
       </c>
       <c r="F98" t="n">
-        <v>1.171501081534105</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>4.997251718192685</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>2.889126219607711</v>
+        <v>0.4828868758846154</v>
       </c>
       <c r="J98" t="n">
         <v>2</v>
@@ -5233,17 +5233,17 @@
         <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>6.16875279972679</v>
+        <v>2.897321255307693</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C000777</t>
+          <t>C001152</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>12.75372519176578</v>
+        <v>6.008807926813411</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5252,47 +5252,47 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.6 | D=1.8 | P=-0.8 | A=2.7 | R=3.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
         </is>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>5.578349909591425</v>
+        <v>2.856790783678727</v>
       </c>
       <c r="G99" t="n">
-        <v>1.774397691944847</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.8421449642967941</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>2.746648815836232</v>
+        <v>0.9522635945595755</v>
       </c>
       <c r="J99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M99" t="n">
-        <v>7.352747601536271</v>
+        <v>2.856790783678727</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C000779</t>
+          <t>C001165</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>12.67036808344561</v>
+        <v>5.951500176645296</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5301,47 +5301,47 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.5 | D=2.6 | P=-0.0 | A=2.5 | R=3.0</t>
+          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=2.0</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>3.458027088474403</v>
+        <v>2.828606644251785</v>
       </c>
       <c r="G100" t="n">
-        <v>2.60441284725902</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>2.454882119787645</v>
+        <v>0.9428688814172617</v>
       </c>
       <c r="J100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M100" t="n">
-        <v>6.062439935733424</v>
+        <v>2.828606644251785</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C000785</t>
+          <t>C001166</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>12.56297482605984</v>
+        <v>5.947784333824027</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5350,37 +5350,37 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.2 | D=0.0 | P=-0.1 | A=2.1 | R=3.0</t>
+          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=2.0</t>
         </is>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>6.237103010418305</v>
+        <v>2.826779180569194</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0.139711542819126</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>2.079034336806101</v>
+        <v>0.9422597268563979</v>
       </c>
       <c r="J101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M101" t="n">
-        <v>6.237103010418305</v>
+        <v>2.826779180569194</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/best_areas.xlsx
+++ b/data/processed/best_areas.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,71 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>candidate_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>final_score</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>main_reason</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>score_breakdown</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>hospital_score</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>clinic_score</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>doctor_score</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>competition_score</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>accessibility_score</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>road_score</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>population_score</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>road_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>road_weight</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>prescription_score</t>
         </is>
@@ -486,664 +508,742 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C000001</t>
+          <t>C005049</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139.9036629603248</v>
+        <v>152.2458335984106</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>H=7.5 | C=36.7 | D=49.9 | P=-17.4 | A=38.4 | R=3.0</t>
+          <t>H=7.5 | C=36.7 | D=49.9 | P=-17.4 | A=38.4 | R=3.0 | Pop=60.2 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7.503206542983218</v>
+        <v>7.503206542971671</v>
       </c>
       <c r="F2" t="n">
-        <v>36.68067306449589</v>
+        <v>36.68067306449847</v>
       </c>
       <c r="G2" t="n">
-        <v>49.85956986768631</v>
+        <v>49.85956986769806</v>
       </c>
       <c r="H2" t="n">
-        <v>17.44131900930777</v>
+        <v>17.44131900928699</v>
       </c>
       <c r="I2" t="n">
-        <v>38.40721037917233</v>
+        <v>38.40721037917714</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>4.114056879339158</v>
+      </c>
+      <c r="L2" t="n">
+        <v>60.19447326660156</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="n">
-        <v>94.04344947516543</v>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>94.04344947516819</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C000004</t>
+          <t>C010144</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>117.8175890825609</v>
+        <v>131.1203934800488</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>H=10.3 | C=36.8 | D=35.7 | P=-17.1 | A=31.9 | R=2.0</t>
+          <t>H=10.3 | C=36.8 | D=35.7 | P=-17.1 | A=31.9 | R=2.0 | Pop=83.3 | PopScore=4.4</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.32873884306982</v>
+        <v>10.32873884313252</v>
       </c>
       <c r="F3" t="n">
-        <v>36.83947469090556</v>
+        <v>36.8394746908071</v>
       </c>
       <c r="G3" t="n">
-        <v>35.7050629008124</v>
+        <v>35.70506290083514</v>
       </c>
       <c r="H3" t="n">
-        <v>17.1047816897122</v>
+        <v>17.10478168980269</v>
       </c>
       <c r="I3" t="n">
-        <v>31.85381282121969</v>
+        <v>31.85381282120869</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>4.434268132595471</v>
+      </c>
+      <c r="L3" t="n">
+        <v>83.29041290283203</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>82.87327643478778</v>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>82.87327643477477</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C000020</t>
+          <t>C003823</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89.26482171618197</v>
+        <v>100.9989823833701</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>H=10.4 | C=18.8 | D=28.1 | P=-9.3 | A=22.0 | R=3.5</t>
+          <t>H=12.3 | C=11.2 | D=25.9 | P=-4.1 | A=18.7 | R=2.0 | Pop=62.2 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.3956318121241</v>
+        <v>12.34697120073556</v>
       </c>
       <c r="F4" t="n">
-        <v>18.76646241735192</v>
+        <v>11.1555702568467</v>
       </c>
       <c r="G4" t="n">
-        <v>28.10762345171247</v>
+        <v>25.88835262833924</v>
       </c>
       <c r="H4" t="n">
-        <v>9.276268032075912</v>
+        <v>4.098387000678795</v>
       </c>
       <c r="I4" t="n">
-        <v>22.04190450032756</v>
+        <v>18.72052826657445</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.146767462302017</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>57.26971768118848</v>
+        <v>62.22927856445312</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>49.3908940859215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C000032</t>
+          <t>C003450</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.34808106146353</v>
+        <v>86.7803814946822</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>H=5.0 | C=10.4 | D=20.5 | P=-0.0 | A=14.5 | R=2.0</t>
+          <t>H=5.0 | C=10.4 | D=20.5 | P=-0.0 | A=14.5 | R=2.0 | Pop=87.0 | PopScore=4.5</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.95442446784087</v>
+        <v>4.954424467859699</v>
       </c>
       <c r="F5" t="n">
-        <v>10.42168495838445</v>
+        <v>10.42168495840273</v>
       </c>
       <c r="G5" t="n">
-        <v>20.4711702289119</v>
+        <v>20.47117022892906</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>14.53521751189091</v>
+        <v>14.53521751190872</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>4.477433477702784</v>
+      </c>
+      <c r="L5" t="n">
+        <v>87.00850677490234</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>35.84727965513722</v>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>35.84727965519149</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C000051</t>
+          <t>C005034</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54.77858950325049</v>
+        <v>78.24311694896231</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>H=0.0 | C=10.7 | D=22.1 | P=-4.2 | A=14.6 | R=3.0</t>
+          <t>H=9.0 | C=24.1 | D=10.9 | P=-7.8 | A=15.0 | R=3.0 | Pop=49.2 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>9.040023607965294</v>
       </c>
       <c r="F6" t="n">
-        <v>10.67810828029281</v>
+        <v>24.10292321794611</v>
       </c>
       <c r="G6" t="n">
-        <v>22.0746630259522</v>
+        <v>10.86045501989848</v>
       </c>
       <c r="H6" t="n">
-        <v>4.162207734404523</v>
+        <v>7.768914938306009</v>
       </c>
       <c r="I6" t="n">
-        <v>14.59670093974037</v>
+        <v>14.97120585059217</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>3.915312495733783</v>
+      </c>
+      <c r="L6" t="n">
+        <v>49.16474533081055</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>32.75277130624501</v>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>44.00340184580989</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C000059</t>
+          <t>C000178</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52.53881524064655</v>
+        <v>66.46850909104536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>H=6.7 | C=7.8 | D=18.0 | P=-4.7 | A=12.7 | R=3.5</t>
+          <t>H=0.0 | C=10.7 | D=22.1 | P=-4.2 | A=14.6 | R=3.0 | Pop=48.2 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.747676714883866</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>7.845538347346629</v>
+        <v>10.67810828022539</v>
       </c>
       <c r="G7" t="n">
-        <v>17.98573221872826</v>
+        <v>22.07466302594043</v>
       </c>
       <c r="H7" t="n">
-        <v>4.747448385233445</v>
+        <v>4.162207734391663</v>
       </c>
       <c r="I7" t="n">
-        <v>12.73265834429365</v>
+        <v>14.59670093971202</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.896639862639165</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>32.57894728095876</v>
+        <v>48.23672866821289</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>32.75277130616583</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C000060</t>
+          <t>C012630</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.38062365021003</v>
+        <v>63.85241373373253</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>H=0.0 | C=18.5 | D=13.1 | P=-4.1 | A=12.7 | R=3.0</t>
+          <t>H=0.0 | C=18.5 | D=13.1 | P=-4.1 | A=12.7 | R=3.0 | Pop=44.8 | PopScore=3.8</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>18.50476759991403</v>
+        <v>18.50476759986521</v>
       </c>
       <c r="G8" t="n">
-        <v>13.10700375925079</v>
+        <v>13.10700375921821</v>
       </c>
       <c r="H8" t="n">
-        <v>4.138364947581984</v>
+        <v>4.138364947558304</v>
       </c>
       <c r="I8" t="n">
-        <v>12.7217577462634</v>
+        <v>12.72175774623084</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>3.823930027872508</v>
+      </c>
+      <c r="L8" t="n">
+        <v>44.78378677368164</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>31.61177135916482</v>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>31.61177135908342</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C000071</t>
+          <t>C013600</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49.78102545754624</v>
+        <v>62.40361758297414</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>H=5.5 | C=4.6 | D=18.5 | P=-2.9 | A=11.7 | R=2.0</t>
+          <t>H=5.5 | C=4.6 | D=18.5 | P=-2.9 | A=11.7 | R=2.0 | Pop=66.2 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.488450747524911</v>
+        <v>5.488450747519946</v>
       </c>
       <c r="F9" t="n">
-        <v>4.638795203613305</v>
+        <v>4.638795203608812</v>
       </c>
       <c r="G9" t="n">
-        <v>18.47659404170868</v>
+        <v>18.47659404171509</v>
       </c>
       <c r="H9" t="n">
-        <v>2.932194972048503</v>
+        <v>2.932194972044189</v>
       </c>
       <c r="I9" t="n">
-        <v>11.69930387997959</v>
+        <v>11.69930387998047</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>4.207530708473655</v>
+      </c>
+      <c r="L9" t="n">
+        <v>66.19042205810547</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>28.60383999284689</v>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>28.60383999284384</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C000075</t>
+          <t>C005080</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.45999198339934</v>
+        <v>61.49789215471246</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>H=1.3 | C=17.8 | D=9.3 | P=-3.2 | A=10.8 | R=3.5</t>
+          <t>H=6.7 | C=7.8 | D=18.0 | P=-4.7 | A=12.7 | R=3.5 | Pop=18.8 | PopScore=3.0</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.290032651072631</v>
+        <v>6.747676714883866</v>
       </c>
       <c r="F10" t="n">
-        <v>17.79715424324383</v>
+        <v>7.845538347346629</v>
       </c>
       <c r="G10" t="n">
-        <v>9.259417406821518</v>
+        <v>17.98573221872826</v>
       </c>
       <c r="H10" t="n">
-        <v>3.220308836059012</v>
+        <v>4.747448385233445</v>
       </c>
       <c r="I10" t="n">
-        <v>10.77709889300415</v>
+        <v>12.73265834429365</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>2.986358971355304</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.81340980529785</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
-        <v>28.34660430113798</v>
+      <c r="O10" t="n">
+        <v>32.57894728095876</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C000114</t>
+          <t>C009766</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37.88281142082977</v>
+        <v>60.10875235362665</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>H=14.4 | C=1.2 | D=3.1 | P=-0.0 | A=4.3 | R=2.0</t>
+          <t>H=1.3 | C=17.8 | D=9.3 | P=-3.2 | A=10.8 | R=3.5 | Pop=47.6 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.39515752672992</v>
+        <v>1.290032651072631</v>
       </c>
       <c r="F11" t="n">
-        <v>1.168460452173742</v>
+        <v>17.79715424324383</v>
       </c>
       <c r="G11" t="n">
-        <v>3.061808531302996</v>
+        <v>9.259417406821518</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3.220308836059012</v>
       </c>
       <c r="I11" t="n">
-        <v>4.319584004164399</v>
+        <v>10.77709889300415</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.882920123409102</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>18.62542651020666</v>
+        <v>47.56582641601562</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>28.34660430113798</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C000143</t>
+          <t>C009195</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.16910378665238</v>
+        <v>50.37479796641327</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>H=4.2 | C=7.5 | D=4.0 | P=-0.0 | A=5.2 | R=3.0</t>
+          <t>H=14.4 | C=1.2 | D=3.1 | P=-0.0 | A=4.3 | R=2.0 | Pop=63.3 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.205758233853527</v>
+        <v>14.39515752672992</v>
       </c>
       <c r="F12" t="n">
-        <v>7.489198797553329</v>
+        <v>1.168460452173742</v>
       </c>
       <c r="G12" t="n">
-        <v>3.980221362612684</v>
+        <v>3.061808531302996</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>5.187469986133039</v>
+        <v>4.319584004164399</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.1639955151945</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>15.67517839401954</v>
+        <v>63.32803344726562</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>18.62542651020666</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C000154</t>
+          <t>C009017</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.41392610673741</v>
+        <v>44.18725442655661</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>H=0.0 | C=16.8 | D=2.7 | P=-3.2 | A=6.9 | R=2.0</t>
+          <t>H=5.7 | C=6.3 | D=3.7 | P=-0.0 | A=4.9 | R=3.0 | Pop=55.0 | PopScore=4.0</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>5.691455119737899</v>
       </c>
       <c r="F13" t="n">
-        <v>16.83420964225634</v>
+        <v>6.31422922481618</v>
       </c>
       <c r="G13" t="n">
-        <v>2.65724136837855</v>
+        <v>3.655275884914199</v>
       </c>
       <c r="H13" t="n">
-        <v>3.154326101453278</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6.940023898274722</v>
+        <v>4.880956870685476</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.025746093517168</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>19.49145101063489</v>
+        <v>55.02209091186523</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>15.66096022946828</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C000155</t>
+          <t>C003467</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.35344114708541</v>
+        <v>43.7469618622326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H=6.9 | C=6.1 | D=1.8 | P=-0.0 | A=4.1 | R=3.0</t>
+          <t>H=0.0 | C=16.8 | D=2.7 | P=-3.2 | A=6.9 | R=2.0 | Pop=84.1 | PopScore=4.4</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.938993980343114</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>6.106033776932642</v>
+        <v>16.83420964215612</v>
       </c>
       <c r="G14" t="n">
-        <v>1.777659157868501</v>
+        <v>2.657241368377704</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3.154326101402702</v>
       </c>
       <c r="I14" t="n">
-        <v>4.080673167968984</v>
+        <v>6.940023898240892</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.444345251849656</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>14.82268691514426</v>
+        <v>84.14411163330078</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>19.49145101053382</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C000161</t>
+          <t>C009261</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.78502792383085</v>
+        <v>41.7204279748848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>H=0.0 | C=14.5 | D=0.0 | P=-0.0 | A=4.8 | R=3.5</t>
+          <t>H=0.0 | C=14.5 | D=0.0 | P=-0.0 | A=4.8 | R=3.5 | Pop=52.6 | PopScore=4.0</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>14.47624324122829</v>
+        <v>14.47159564706446</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1152,481 +1252,541 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4.825414413742761</v>
+        <v>4.823865215688155</v>
       </c>
       <c r="J15" t="n">
         <v>3.5</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>3.981616719729017</v>
+      </c>
+      <c r="L15" t="n">
+        <v>52.6036262512207</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>4</v>
       </c>
-      <c r="M15" t="n">
-        <v>14.47624324122829</v>
+      <c r="O15" t="n">
+        <v>14.47159564706446</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C000165</t>
+          <t>C013577</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29.65337749634204</v>
+        <v>40.38279149254797</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>H=12.3 | C=0.0 | D=2.3 | P=-0.0 | A=3.2 | R=2.0</t>
+          <t>H=0.0 | C=8.6 | D=4.3 | P=-0.0 | A=5.0 | R=2.0 | Pop=103.2 | PopScore=4.6</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.29483911743335</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>8.603859148010979</v>
       </c>
       <c r="G16" t="n">
-        <v>2.272578183504773</v>
+        <v>4.268245621894352</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3.185428944657945</v>
+        <v>5.002075860284169</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>4.646124788902965</v>
+      </c>
+      <c r="L16" t="n">
+        <v>103.1804809570312</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>14.56741730093812</v>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>12.87210476990533</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C000179</t>
+          <t>C012479</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.31910562328143</v>
+        <v>40.15870530732162</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>H=10.7 | C=2.7 | D=0.4 | P=-0.0 | A=2.9 | R=3.0</t>
+          <t>H=10.7 | C=2.7 | D=0.4 | P=-0.0 | A=2.9 | R=3.0 | Pop=50.8 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10.73502665302223</v>
+        <v>10.73502665301193</v>
       </c>
       <c r="F17" t="n">
-        <v>2.744008625141222</v>
+        <v>2.744008625134775</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3856834155607017</v>
+        <v>0.3856834155569375</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2.896682358331131</v>
+        <v>2.896682358325382</v>
       </c>
       <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>3.946533228027264</v>
+      </c>
+      <c r="L17" t="n">
+        <v>50.75563049316406</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" t="n">
-        <v>13.86471869372416</v>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>13.86471869370364</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C000195</t>
+          <t>C013500</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27.18593988812859</v>
+        <v>39.04295225583963</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>H=0.0 | C=10.3 | D=2.8 | P=-0.0 | A=4.9 | R=3.5</t>
+          <t>H=0.0 | C=13.0 | D=0.0 | P=-0.0 | A=4.3 | R=2.0 | Pop=63.3 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>10.33562517301334</v>
+        <v>12.96064353834643</v>
       </c>
       <c r="G18" t="n">
-        <v>2.83910668439096</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4.864761733199926</v>
+        <v>4.320214512782144</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.163214575956184</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>13.1747318574043</v>
+        <v>63.27781677246094</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>12.96064353834643</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C000208</t>
+          <t>C013491</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.55330852804834</v>
+        <v>38.43194566476656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>H=0.0 | C=13.0 | D=0.0 | P=-0.0 | A=4.3 | R=2.0</t>
+          <t>H=12.3 | C=0.0 | D=2.3 | P=-0.0 | A=3.2 | R=2.0 | Pop=17.7 | PopScore=2.9</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>12.29483911743335</v>
       </c>
       <c r="F19" t="n">
-        <v>12.96064353838443</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.272578183504773</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4.320214512794809</v>
+        <v>3.185428944657945</v>
       </c>
       <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>2.926189389474839</v>
+      </c>
+      <c r="L19" t="n">
+        <v>17.65640258789062</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>12.96064353838443</v>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>14.56741730093812</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C000210</t>
+          <t>C010110</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.47328980232562</v>
+        <v>37.85652144781051</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>H=0.0 | C=7.5 | D=5.4 | P=-0.0 | A=5.2 | R=2.0</t>
+          <t>H=0.0 | C=7.5 | D=5.4 | P=-0.0 | A=5.2 | R=2.0 | Pop=43.5 | PopScore=3.8</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>7.512356792514868</v>
+        <v>7.512356792524591</v>
       </c>
       <c r="G20" t="n">
-        <v>5.364958206932711</v>
+        <v>5.364958206938954</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>5.186598034304645</v>
+        <v>5.186598034311007</v>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>3.794410548484106</v>
+      </c>
+      <c r="L20" t="n">
+        <v>43.4520263671875</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>12.87731499944758</v>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>12.87731499946354</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C000231</t>
+          <t>C008162</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.14163866808258</v>
+        <v>37.75578826447685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>H=0.0 | C=8.6 | D=3.6 | P=-0.0 | A=4.7 | R=3.0</t>
+          <t>H=0.0 | C=8.6 | D=3.6 | P=-0.0 | A=4.7 | R=3.0 | Pop=66.0 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>8.618143666160218</v>
+        <v>8.618143666159648</v>
       </c>
       <c r="G21" t="n">
-        <v>3.569795063523645</v>
+        <v>3.569795063522354</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4.657612087148562</v>
+        <v>4.657612087147726</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>4.204716532132689</v>
+      </c>
+      <c r="L21" t="n">
+        <v>66.00160217285156</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>3</v>
-      </c>
-      <c r="M21" t="n">
-        <v>12.18793872968386</v>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>12.187938729682</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C000235</t>
+          <t>C010638</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24.61170556575886</v>
+        <v>35.12727087790941</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.3 | D=7.0 | P=-1.0 | A=5.6 | R=3.0</t>
+          <t>H=0.0 | C=6.3 | D=7.0 | P=-1.0 | A=5.6 | R=3.0 | Pop=32.3 | PopScore=3.5</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>6.303320442942572</v>
+        <v>6.303320442934357</v>
       </c>
       <c r="G22" t="n">
-        <v>7.046935017731888</v>
+        <v>7.046935017718495</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9837542626360252</v>
+        <v>0.9837542626313882</v>
       </c>
       <c r="I22" t="n">
-        <v>5.624574323180135</v>
+        <v>5.6245743231707</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>3.5051884373936</v>
+      </c>
+      <c r="L22" t="n">
+        <v>32.28771591186523</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>13.35025546067446</v>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>13.35025546065285</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C000237</t>
+          <t>C001412</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24.51732104456848</v>
+        <v>34.055939319896</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>H=10.9 | C=0.0 | D=1.1 | P=-0.0 | A=2.4 | R=3.0</t>
+          <t>H=10.9 | C=0.0 | D=1.1 | P=-0.0 | A=2.4 | R=3.0 | Pop=23.0 | PopScore=3.2</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10.87807738630281</v>
+        <v>10.87807738632181</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.112129259605435</v>
+        <v>1.112129259612113</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2.369077527519853</v>
+        <v>2.369077527526358</v>
       </c>
       <c r="J23" t="n">
         <v>3</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="n">
+        <v>3.17953942509184</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.03568077087402</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>3</v>
-      </c>
-      <c r="M23" t="n">
-        <v>11.99020664590825</v>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>11.99020664593392</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C000287</t>
+          <t>C000101</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21.66563377348075</v>
+        <v>31.4313370246224</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>H=5.0 | C=6.3 | D=0.5 | P=-0.9 | A=3.2 | R=3.0</t>
+          <t>H=3.3 | C=5.2 | D=2.6 | P=-1.2 | A=3.6 | R=3.0 | Pop=56.7 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.968067659166701</v>
+        <v>3.315526071977458</v>
       </c>
       <c r="F24" t="n">
-        <v>6.320706845348123</v>
+        <v>5.176321890113948</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5494580125681127</v>
+        <v>2.590899787289793</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8772651723815277</v>
+        <v>1.185713203315138</v>
       </c>
       <c r="I24" t="n">
-        <v>3.209642564594548</v>
+        <v>3.57347820234579</v>
       </c>
       <c r="J24" t="n">
         <v>3</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>4.055211105190279</v>
+      </c>
+      <c r="L24" t="n">
+        <v>56.69734191894531</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>11.83823251708294</v>
+      <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>11.0827477493812</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C000304</t>
+          <t>C002152</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.40697076865442</v>
+        <v>30.87656602088459</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>H=5.9 | C=5.3 | D=0.0 | P=-0.9 | A=2.8 | R=3.0</t>
+          <t>H=5.9 | C=5.3 | D=0.0 | P=-0.9 | A=2.8 | R=3.0 | Pop=31.8 | PopScore=3.5</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1647,287 +1807,323 @@
       <c r="J25" t="n">
         <v>3</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>3.489865084076724</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.78152465820312</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>3</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="n">
         <v>11.22341111651399</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C000332</t>
+          <t>C007153</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.54098772350057</v>
+        <v>30.63719787594754</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.6 | D=4.4 | P=-0.0 | A=3.7 | R=3.5</t>
+          <t>H=5.8 | C=2.9 | D=0.0 | P=-0.0 | A=1.9 | R=2.0 | Pop=71.5 | PopScore=4.3</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>5.828603238305402</v>
       </c>
       <c r="F26" t="n">
-        <v>4.558718100428397</v>
+        <v>2.868906694920994</v>
       </c>
       <c r="G26" t="n">
-        <v>4.351997196404634</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3.695571298345116</v>
+        <v>1.927736104691232</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.283134799675208</v>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
-      </c>
-      <c r="M26" t="n">
-        <v>8.910715296833031</v>
+        <v>71.46725463867188</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>8.697509933226396</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C000335</t>
+          <t>C001072</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18.47197316485219</v>
+        <v>30.10904728890866</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=6.0 | P=-0.0 | A=4.0 | R=3.0</t>
+          <t>H=0.0 | C=2.9 | D=6.0 | P=-0.0 | A=4.0 | R=3.0 | Pop=47.4 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>2.917634677831475</v>
+        <v>2.917634677837338</v>
       </c>
       <c r="G27" t="n">
-        <v>5.970463082891799</v>
+        <v>5.970463082891105</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3.957776434056391</v>
+        <v>3.957776434057998</v>
       </c>
       <c r="J27" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>3.879024708015324</v>
+      </c>
+      <c r="L27" t="n">
+        <v>47.37701034545898</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L27" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" t="n">
-        <v>8.888097760723273</v>
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>8.888097760728444</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C000336</t>
+          <t>C007949</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18.4703689085442</v>
+        <v>29.65182963281506</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>H=0.0 | C=9.5 | D=7.9 | P=-5.8 | A=7.1 | R=3.0</t>
+          <t>H=5.4 | C=3.0 | D=0.0 | P=-0.0 | A=1.9 | R=3.0 | Pop=58.9 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>5.437333420948989</v>
       </c>
       <c r="F28" t="n">
-        <v>9.508691587422472</v>
+        <v>3.003817915615222</v>
       </c>
       <c r="G28" t="n">
-        <v>7.889633812927335</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>5.779239989683065</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>7.114380768937825</v>
+        <v>1.907494875363239</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="n">
+        <v>4.092925824050106</v>
+      </c>
+      <c r="L28" t="n">
+        <v>58.91493606567383</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>3</v>
-      </c>
-      <c r="M28" t="n">
-        <v>17.39832540034981</v>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>8.441151336564211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C000340</t>
+          <t>C000329</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18.32922278082053</v>
+        <v>29.37567315045393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.8 | D=2.0 | P=-0.0 | A=3.3 | R=3.5</t>
+          <t>H=0.0 | C=9.5 | D=7.9 | P=-5.8 | A=7.1 | R=3.0 | Pop=36.9 | PopScore=3.6</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>6.828422784890696</v>
+        <v>9.508691587425922</v>
       </c>
       <c r="G29" t="n">
-        <v>1.997445423516802</v>
+        <v>7.889633812909215</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>5.779239989659096</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2748636400553</v>
+        <v>7.114380768929914</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.635101413955985</v>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
-      </c>
-      <c r="M29" t="n">
-        <v>8.825868208407497</v>
+        <v>36.90569686889648</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>17.39832540033514</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C000348</t>
+          <t>C000083</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.78779347681746</v>
+        <v>29.33345828406825</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>H=5.8 | C=2.9 | D=0.0 | P=-0.0 | A=1.9 | R=2.0</t>
+          <t>H=0.0 | C=4.6 | D=3.9 | P=-0.0 | A=3.5 | R=3.5 | Pop=46.8 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5.828603238273392</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>2.86890669490137</v>
+        <v>4.620588592704674</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3.896417821776707</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1.927736104679355</v>
+        <v>3.488405108456578</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.866868314753275</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
-      </c>
-      <c r="M30" t="n">
-        <v>8.697509933174763</v>
+        <v>46.79248046875</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>8.517006414481381</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C000359</t>
+          <t>C010348</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17.37305216081182</v>
+        <v>29.15867748541768</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>H=5.4 | C=3.0 | D=0.0 | P=-0.0 | A=1.9 | R=3.0</t>
+          <t>H=5.7 | C=2.2 | D=0.0 | P=-0.0 | A=1.7 | R=2.0 | Pop=74.7 | PopScore=4.3</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5.437333420947287</v>
+        <v>5.749083099575197</v>
       </c>
       <c r="F31" t="n">
-        <v>3.00381791568924</v>
+        <v>2.156139470819884</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1936,243 +2132,273 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1.907494875387628</v>
+        <v>1.676893673535828</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.326847659091311</v>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
-      </c>
-      <c r="M31" t="n">
-        <v>8.441151336636528</v>
+        <v>74.70526123046875</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>7.905222570395081</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C000373</t>
+          <t>C002135</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.50154086997915</v>
+        <v>28.97982846590996</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>H=5.3 | C=2.8 | D=0.0 | P=-0.0 | A=1.8 | R=2.0</t>
+          <t>H=0.0 | C=6.8 | D=2.0 | P=-0.0 | A=3.3 | R=3.5 | Pop=33.8 | PopScore=3.6</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5.260475422682626</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>2.799794475853701</v>
+        <v>6.828422784918054</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.99744542351781</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1.810010729065005</v>
+        <v>3.274863640064924</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.550201895010578</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>8.060269898536326</v>
+        <v>33.82034683227539</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>8.825868208435864</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C000374</t>
+          <t>C000421</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16.42582573909884</v>
+        <v>28.20786679371711</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>H=7.5 | C=3.9 | D=0.0 | P=-2.3 | A=2.5 | R=3.0</t>
+          <t>H=0.0 | C=5.2 | D=2.7 | P=-0.0 | A=3.1 | R=2.0 | Pop=49.9 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>7.521288256284354</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>3.879753391496605</v>
+        <v>5.209290742673871</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2.745111592456297</v>
       </c>
       <c r="H33" t="n">
-        <v>2.310312491261457</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2.546799173212927</v>
+        <v>3.108986043786105</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.929387839692722</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
-      </c>
-      <c r="M33" t="n">
-        <v>11.40104164778096</v>
+        <v>49.87582397460938</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>7.954402335130167</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C000375</t>
+          <t>C004536</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16.41970327459077</v>
+        <v>27.8723351666621</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.2 | D=2.7 | P=-0.0 | A=3.1 | R=2.0</t>
+          <t>H=0.0 | C=2.9 | D=4.2 | P=-0.0 | A=3.0 | R=2.0 | Pop=82.6 | PopScore=4.4</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>5.20929074266048</v>
+        <v>2.884034236427663</v>
       </c>
       <c r="G34" t="n">
-        <v>2.745111592446077</v>
+        <v>4.160424044356455</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3.108986043776532</v>
+        <v>3.041556767654115</v>
       </c>
       <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>4.426420976109486</v>
+      </c>
+      <c r="L34" t="n">
+        <v>82.63156127929688</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>7.954402335106558</v>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>7.044458280784118</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C000378</t>
+          <t>C008680</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.31618536804281</v>
+        <v>27.14040499478731</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>H=5.4 | C=2.5 | D=0.0 | P=-0.0 | A=1.7 | R=3.0</t>
+          <t>H=5.4 | C=0.0 | D=1.8 | P=-0.0 | A=1.8 | R=2.0 | Pop=62.6 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.44073944244955</v>
+        <v>5.388515065028164</v>
       </c>
       <c r="F35" t="n">
-        <v>2.480669258575189</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.76319376362805</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1.733679659933321</v>
+        <v>1.779682725985386</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.153006354958781</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>7.921408701024738</v>
+        <v>62.62499237060547</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>7.151708828656214</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C000384</t>
+          <t>C002731</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16.17813450811647</v>
+        <v>26.91899341031226</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>H=5.7 | C=2.2 | D=0.0 | P=-0.0 | A=1.7 | R=2.0</t>
+          <t>H=5.4 | C=2.5 | D=0.0 | P=-0.0 | A=1.7 | R=3.0 | Pop=33.3 | PopScore=3.5</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.74908309956597</v>
+        <v>5.440739442429406</v>
       </c>
       <c r="F36" t="n">
-        <v>2.15613947081562</v>
+        <v>2.480669258590382</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2181,338 +2407,380 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1.676893673532868</v>
+        <v>1.733679659935028</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.534269347426393</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>7.905222570381591</v>
+        <v>33.26996612548828</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>7.921408701019788</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C000400</t>
+          <t>C003481</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.81064129333414</v>
+        <v>26.35352653782149</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>H=4.9 | C=1.2 | D=1.6 | P=-0.0 | A=2.0 | R=3.5</t>
+          <t>H=3.8 | C=2.6 | D=0.0 | P=-0.0 | A=1.5 | R=2.0 | Pop=80.2 | PopScore=4.4</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4.850292848271179</v>
+        <v>3.805604668166855</v>
       </c>
       <c r="F37" t="n">
-        <v>1.162045182363996</v>
+        <v>2.600561869615027</v>
       </c>
       <c r="G37" t="n">
-        <v>1.617752282201856</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2.00460667660079</v>
+        <v>1.501121401232818</v>
       </c>
       <c r="J37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.39702710737815</v>
       </c>
       <c r="L37" t="n">
-        <v>4</v>
-      </c>
-      <c r="M37" t="n">
-        <v>7.630090312837032</v>
+        <v>80.20908355712891</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>6.406166537781882</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C000431</t>
+          <t>C003128</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14.98406744396993</v>
+        <v>26.18591276209523</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.6 | D=4.5 | P=-0.0 | A=3.2 | R=3.0</t>
+          <t>H=7.0 | C=2.0 | D=0.0 | P=-1.7 | A=1.8 | R=2.0 | Pop=76.5 | PopScore=4.3</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>6.989004499737087</v>
       </c>
       <c r="F38" t="n">
-        <v>2.641167798158019</v>
+        <v>1.964123331075413</v>
       </c>
       <c r="G38" t="n">
-        <v>4.543264839535915</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1.717308862274173</v>
       </c>
       <c r="I38" t="n">
-        <v>3.152021685820631</v>
+        <v>1.819541860314652</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.349876500420431</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
-      </c>
-      <c r="M38" t="n">
-        <v>7.184432637693934</v>
+        <v>76.46889495849609</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>8.9531278308125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C000436</t>
+          <t>C008633</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>14.88667615276281</v>
+        <v>26.14907113066759</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>H=13.9 | C=3.4 | D=1.9 | P=-8.1 | A=4.4 | R=3.0</t>
+          <t>H=11.5 | C=5.7 | D=5.0 | P=-10.8 | A=6.3 | R=3.5 | Pop=82.2 | PopScore=4.4</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>13.85548391651788</v>
+        <v>11.49874588567654</v>
       </c>
       <c r="F39" t="n">
-        <v>3.4155944537692</v>
+        <v>5.665547634402373</v>
       </c>
       <c r="G39" t="n">
-        <v>1.948527878092495</v>
+        <v>5.033028302640711</v>
       </c>
       <c r="H39" t="n">
-        <v>8.098246872767302</v>
+        <v>10.83004941088425</v>
       </c>
       <c r="I39" t="n">
-        <v>4.422042743055628</v>
+        <v>6.321487677067238</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.420808983391451</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
-      </c>
-      <c r="M39" t="n">
-        <v>19.21960624837957</v>
+        <v>82.16353607177734</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>22.19732182271963</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C000441</t>
+          <t>C007221</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>14.76387106472946</v>
+        <v>25.64789447840737</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.2 | D=1.9 | P=-0.0 | A=2.7 | R=3.5</t>
+          <t>H=5.6 | C=1.1 | D=0.0 | P=-0.0 | A=1.3 | R=3.0 | Pop=50.9 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>5.629728717812311</v>
       </c>
       <c r="F40" t="n">
-        <v>5.174152023405216</v>
+        <v>1.055494749806664</v>
       </c>
       <c r="G40" t="n">
-        <v>1.899070870149035</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>2.674252776209589</v>
+        <v>1.290119702904273</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.949478524292997</v>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
-      </c>
-      <c r="M40" t="n">
-        <v>7.07322289355425</v>
+        <v>50.90829086303711</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>6.685223467618975</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C000442</t>
+          <t>C001365</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>14.6813859299164</v>
+        <v>25.54091485555339</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>H=5.4 | C=0.0 | D=1.8 | P=-0.0 | A=1.8 | R=2.0</t>
+          <t>H=0.0 | C=2.6 | D=5.8 | P=-1.2 | A=3.7 | R=2.0 | Pop=54.3 | PopScore=4.0</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5.388515065030845</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2.575962790427726</v>
       </c>
       <c r="G41" t="n">
-        <v>1.763193763628065</v>
+        <v>5.751932056380634</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1.242562953267371</v>
       </c>
       <c r="I41" t="n">
-        <v>1.77968272598584</v>
+        <v>3.734620291666225</v>
       </c>
       <c r="J41" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" t="n">
+        <v>4.013117330857386</v>
+      </c>
+      <c r="L41" t="n">
+        <v>54.31904983520508</v>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>2</v>
-      </c>
-      <c r="M41" t="n">
-        <v>7.15170882865891</v>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>8.327894846808359</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C000444</t>
+          <t>C005092</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>14.59307223835925</v>
+        <v>25.42354864388941</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=4.2 | P=-0.0 | A=3.0 | R=2.0</t>
+          <t>H=0.0 | C=2.6 | D=4.5 | P=-0.0 | A=3.2 | R=3.0 | Pop=31.5 | PopScore=3.5</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>2.884034236431071</v>
+        <v>2.641167798163308</v>
       </c>
       <c r="G42" t="n">
-        <v>4.160424044365566</v>
+        <v>4.543264839553295</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>3.041556767659807</v>
+        <v>3.152021685831083</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.479827066624365</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
-      </c>
-      <c r="M42" t="n">
-        <v>7.044458280796637</v>
+        <v>31.45410919189453</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>3</v>
+      </c>
+      <c r="O42" t="n">
+        <v>7.184432637716602</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C000447</t>
+          <t>C009257</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14.55249223969727</v>
+        <v>24.26506128832253</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>H=7.1 | C=0.0 | D=0.0 | P=-0.0 | A=1.2 | R=2.0</t>
+          <t>H=6.0 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.5 | Pop=50.9 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7.116938300676331</v>
+        <v>5.984602491423172</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2524,47 +2792,53 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1.186156383446055</v>
+        <v>0.9974337485705287</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.948704310206379</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
-      </c>
-      <c r="M43" t="n">
-        <v>7.116938300676331</v>
+        <v>50.86811828613281</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>4</v>
+      </c>
+      <c r="O43" t="n">
+        <v>5.984602491423172</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C000470</t>
+          <t>C001844</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13.79945890552916</v>
+        <v>24.16957077621892</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>H=5.6 | C=1.1 | D=0.0 | P=-0.0 | A=1.3 | R=3.0</t>
+          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.0 | Pop=53.1 | PopScore=4.0</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5.62972871780407</v>
+        <v>5.899323622863868</v>
       </c>
       <c r="F44" t="n">
-        <v>1.055494749815221</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2573,96 +2847,108 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1.290119702905752</v>
+        <v>0.9832206038106447</v>
       </c>
       <c r="J44" t="n">
         <v>3</v>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" t="n">
+        <v>3.990867156703372</v>
+      </c>
+      <c r="L44" t="n">
+        <v>53.10178375244141</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L44" t="n">
-        <v>3</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.685223467619291</v>
+      <c r="N44" t="n">
+        <v>3</v>
+      </c>
+      <c r="O44" t="n">
+        <v>5.899323622863868</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C000486</t>
+          <t>C004637</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13.50156286301008</v>
+        <v>24.06804466045589</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.6 | D=5.8 | P=-1.2 | A=3.7 | R=2.0</t>
+          <t>H=5.3 | C=2.8 | D=0.0 | P=-0.0 | A=1.8 | R=2.0 | Pop=11.5 | PopScore=2.5</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>5.260475422682626</v>
       </c>
       <c r="F45" t="n">
-        <v>2.575962790423339</v>
+        <v>2.799794475853701</v>
       </c>
       <c r="G45" t="n">
-        <v>5.751932056392683</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.242562953263016</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3.734620291670788</v>
+        <v>1.810010729065005</v>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" t="n">
+        <v>2.522167930158913</v>
+      </c>
+      <c r="L45" t="n">
+        <v>11.45557022094727</v>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L45" t="n">
-        <v>2</v>
-      </c>
-      <c r="M45" t="n">
-        <v>8.327894846816022</v>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>8.060269898536326</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C000501</t>
+          <t>C003004</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13.16244521566322</v>
+        <v>24.0373812770499</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>H=3.8 | C=2.6 | D=0.0 | P=-0.0 | A=1.5 | R=2.0</t>
+          <t>H=5.0 | C=0.0 | D=0.0 | P=-0.0 | A=0.8 | R=2.0 | Pop=94.7 | PopScore=4.6</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3.805604668152633</v>
+        <v>5.035189989905803</v>
       </c>
       <c r="F46" t="n">
-        <v>2.600561869617414</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2671,338 +2957,380 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1.501121401231244</v>
+        <v>0.8391983316509672</v>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" t="n">
+        <v>4.561027154691065</v>
+      </c>
+      <c r="L46" t="n">
+        <v>94.68170928955078</v>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>6.406166537770048</v>
+      <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>5.035189989905803</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C000512</t>
+          <t>C002290</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>12.94358592811864</v>
+        <v>23.85058866755243</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>H=6.3 | C=0.0 | D=0.0 | P=-0.0 | A=1.1 | R=2.0</t>
+          <t>H=0.0 | C=2.4 | D=3.3 | P=-0.0 | A=2.4 | R=3.0 | Pop=53.8 | PopScore=4.0</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.319133518075361</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2.382385358840881</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3.265083722163237</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1.053188919679227</v>
+        <v>2.426670314028578</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4.004327824713779</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>6.319133518075361</v>
+        <v>53.83495330810547</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>3</v>
+      </c>
+      <c r="O47" t="n">
+        <v>5.647469081004117</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C000525</t>
+          <t>C011052</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>12.67036808344561</v>
+        <v>23.68187370117195</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.5 | D=2.6 | P=-0.0 | A=2.5 | R=3.0</t>
+          <t>H=0.0 | C=3.5 | D=2.6 | P=-0.0 | A=2.5 | R=3.0 | Pop=38.3 | PopScore=3.7</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>3.458027088474403</v>
+        <v>3.458027088468519</v>
       </c>
       <c r="G48" t="n">
-        <v>2.60441284725902</v>
+        <v>2.604412847246794</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2.454882119787645</v>
+        <v>2.45488211977957</v>
       </c>
       <c r="J48" t="n">
         <v>3</v>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" t="n">
+        <v>3.67050187258779</v>
+      </c>
+      <c r="L48" t="n">
+        <v>38.27161026000977</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>3</v>
-      </c>
-      <c r="M48" t="n">
-        <v>6.062439935733424</v>
+      <c r="N48" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" t="n">
+        <v>6.062439935715313</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C000535</t>
+          <t>C003341</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>12.4189483577034</v>
+        <v>23.52437939709079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>H=6.0 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.5</t>
+          <t>H=4.5 | C=0.0 | D=1.2 | P=-0.0 | A=1.4 | R=3.0 | Pop=47.3 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.984602491423172</v>
+        <v>4.528969473397168</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1.200240345478271</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9974337485705287</v>
+        <v>1.35494841830533</v>
       </c>
       <c r="J49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.876821639169793</v>
       </c>
       <c r="L49" t="n">
-        <v>4</v>
-      </c>
-      <c r="M49" t="n">
-        <v>5.984602491423172</v>
+        <v>47.27054977416992</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" t="n">
+        <v>5.729209818875439</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C000548</t>
+          <t>C002755</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>12.19696930611751</v>
+        <v>23.50898397344857</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
+          <t>H=0.0 | C=5.2 | D=1.9 | P=-0.0 | A=2.7 | R=3.5 | Pop=17.4 | PopScore=2.9</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.899323622868189</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>5.174152023412173</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1.899070870149719</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9832206038113648</v>
+        <v>2.674252776212251</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.915037636234521</v>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M50" t="n">
-        <v>5.899323622868189</v>
+        <v>17.44950675964355</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>4</v>
+      </c>
+      <c r="O50" t="n">
+        <v>7.073222893561892</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C000549</t>
+          <t>C003442</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12.19684901270042</v>
+        <v>23.24090432065266</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
+          <t>H=0.0 | C=3.8 | D=1.6 | P=-0.0 | A=2.1 | R=2.0 | Pop=52.9 | PopScore=4.0</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.94885075009938</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>3.825468315911813</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1.610903291683232</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0.9914751250165634</v>
+        <v>2.080607751145554</v>
       </c>
       <c r="J51" t="n">
         <v>2</v>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" t="n">
+        <v>3.986700110116005</v>
+      </c>
+      <c r="L51" t="n">
+        <v>52.87680816650391</v>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L51" t="n">
-        <v>2</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.94885075009938</v>
+      <c r="N51" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" t="n">
+        <v>5.436371607595046</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C000556</t>
+          <t>C009010</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.10020673847659</v>
+        <v>22.53229744459433</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
+          <t>H=5.9 | C=2.8 | D=1.0 | P=-2.9 | A=2.4 | R=3.0 | Pop=42.2 | PopScore=3.8</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5.900928961228063</v>
+        <v>5.872794764559936</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>2.821195878400136</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.9625694323122199</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>2.872300050025061</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9834881602046772</v>
+        <v>2.400482469716144</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.765343065717771</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
-      </c>
-      <c r="M52" t="n">
-        <v>5.900928961228063</v>
+        <v>42.17851638793945</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>3</v>
+      </c>
+      <c r="O52" t="n">
+        <v>9.656560075272292</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C000559</t>
+          <t>C002094</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12.07083942018262</v>
+        <v>22.37678567494557</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>H=5.8 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
+          <t>H=5.6 | C=0.0 | D=0.0 | P=-0.0 | A=0.9 | R=3.0 | Pop=36.3 | PopScore=3.6</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.836779877776503</v>
+        <v>5.564298190349531</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3014,194 +3342,218 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9727966462960839</v>
+        <v>0.9273830317249219</v>
       </c>
       <c r="J53" t="n">
         <v>3</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" t="n">
+        <v>3.618483663691339</v>
+      </c>
+      <c r="L53" t="n">
+        <v>36.2809944152832</v>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>3</v>
-      </c>
-      <c r="M53" t="n">
-        <v>5.836779877776503</v>
+      <c r="N53" t="n">
+        <v>3</v>
+      </c>
+      <c r="O53" t="n">
+        <v>5.564298190349531</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C000571</t>
+          <t>C000343</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>11.92500971982725</v>
+        <v>22.2490314377594</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.7 | D=0.0 | P=-0.0 | A=1.9 | R=3.5</t>
+          <t>H=0.0 | C=2.8 | D=1.9 | P=-0.0 | A=1.9 | R=3.0 | Pop=58.3 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>5.692627731062584</v>
+        <v>2.827951706315079</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1.927277801086707</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>1.897542577020861</v>
+        <v>1.906289469315047</v>
       </c>
       <c r="J54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4.08264782534144</v>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
-      </c>
-      <c r="M54" t="n">
-        <v>5.692627731062584</v>
+        <v>58.30228424072266</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>3</v>
+      </c>
+      <c r="O54" t="n">
+        <v>4.755229507401785</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C000575</t>
+          <t>C007721</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>11.89391447958141</v>
+        <v>22.1539080011263</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>H=4.5 | C=0.0 | D=1.2 | P=-0.0 | A=1.4 | R=3.0</t>
+          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=26.6 | PopScore=3.3</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.528969473397168</v>
+        <v>5.948850750096658</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>1.200240345478271</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1.35494841830533</v>
+        <v>0.9914751250161097</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.319019662810459</v>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
-      </c>
-      <c r="M55" t="n">
-        <v>5.729209818875439</v>
+        <v>26.63324737548828</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>5.948850750096658</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C000578</t>
+          <t>C007183</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>11.83760519345153</v>
+        <v>22.11685937659464</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.4 | D=3.3 | P=-0.0 | A=2.4 | R=3.0</t>
+          <t>H=8.8 | C=4.4 | D=0.0 | P=-5.4 | A=2.9 | R=2.0 | Pop=43.0 | PopScore=3.8</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>8.807818466339167</v>
       </c>
       <c r="F56" t="n">
-        <v>2.382385358841616</v>
+        <v>4.398655339369084</v>
       </c>
       <c r="G56" t="n">
-        <v>3.265083722182235</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>5.379780117041485</v>
       </c>
       <c r="I56" t="n">
-        <v>2.426670314038323</v>
+        <v>2.934188190846223</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.783277765739326</v>
       </c>
       <c r="L56" t="n">
-        <v>3</v>
-      </c>
-      <c r="M56" t="n">
-        <v>5.647469081023851</v>
+        <v>42.95989608764648</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>13.20647380570825</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C000601</t>
+          <t>C001396</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11.5213346838246</v>
+        <v>22.04791017006726</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>H=5.6 | C=0.0 | D=0.0 | P=-0.0 | A=0.9 | R=3.0</t>
+          <t>H=0.0 | C=4.1 | D=0.0 | P=-0.0 | A=1.4 | R=3.5 | Pop=83.5 | PopScore=4.4</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.564298190326248</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>4.125158569732197</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -3210,194 +3562,218 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9273830317210414</v>
+        <v>1.375052856577399</v>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.436695914981709</v>
       </c>
       <c r="L57" t="n">
-        <v>3</v>
-      </c>
-      <c r="M57" t="n">
-        <v>5.564298190326248</v>
+        <v>83.49530029296875</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>4</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4.125158569732197</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C000610</t>
+          <t>C012690</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>11.4055323067991</v>
+        <v>21.94506651243444</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>H=10.2 | C=3.7 | D=0.0 | P=-5.6 | A=2.9 | R=2.0</t>
+          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=25.6 | PopScore=3.3</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>10.23535253588912</v>
+        <v>5.900928961236548</v>
       </c>
       <c r="F58" t="n">
-        <v>3.661746263817668</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>5.62710423677996</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>2.926474177254076</v>
+        <v>0.9834881602060913</v>
       </c>
       <c r="J58" t="n">
         <v>2</v>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" t="n">
+        <v>3.281619924646912</v>
+      </c>
+      <c r="L58" t="n">
+        <v>25.61885833740234</v>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L58" t="n">
-        <v>2</v>
-      </c>
-      <c r="M58" t="n">
-        <v>13.89709879970679</v>
+      <c r="N58" t="n">
+        <v>2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>5.900928961236548</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C000615</t>
+          <t>C005441</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11.31550142288359</v>
+        <v>21.56129082276006</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.9 | D=0.0 | P=-1.0 | A=2.3 | R=3.0</t>
+          <t>H=0.0 | C=6.2 | D=0.0 | P=-0.8 | A=2.1 | R=3.0 | Pop=39.4 | PopScore=3.7</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>6.915401198305339</v>
+        <v>6.237103010416181</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.01527144900131</v>
+        <v>0.8382692569111241</v>
       </c>
       <c r="I59" t="n">
-        <v>2.305133732768446</v>
+        <v>2.079034336805393</v>
       </c>
       <c r="J59" t="n">
         <v>3</v>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" t="n">
+        <v>3.697996379660176</v>
+      </c>
+      <c r="L59" t="n">
+        <v>39.3663444519043</v>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L59" t="n">
-        <v>3</v>
-      </c>
-      <c r="M59" t="n">
-        <v>6.915401198305339</v>
+      <c r="N59" t="n">
+        <v>3</v>
+      </c>
+      <c r="O59" t="n">
+        <v>6.237103010416181</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C000621</t>
+          <t>C009739</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>11.28080399030465</v>
+        <v>21.56025747531795</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.8 | D=1.6 | P=-0.0 | A=2.1 | R=2.0</t>
+          <t>H=0.0 | C=5.1 | D=0.0 | P=-0.0 | A=1.7 | R=3.5 | Pop=36.1 | PopScore=3.6</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>3.825468315911813</v>
+        <v>5.099699712694632</v>
       </c>
       <c r="G60" t="n">
-        <v>1.610903291683232</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>2.080607751145554</v>
+        <v>1.699899904231544</v>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.613622686501845</v>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
-      </c>
-      <c r="M60" t="n">
-        <v>5.436371607595046</v>
+        <v>36.10021209716797</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>5.099699712694632</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C000634</t>
+          <t>C013807</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>11.09731279919482</v>
+        <v>21.48117995204782</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.4 | D=0.0 | P=-0.0 | A=1.8 | R=2.0</t>
+          <t>H=4.2 | C=0.0 | D=0.0 | P=-0.0 | A=0.7 | R=2.0 | Pop=69.7 | PopScore=4.3</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>4.216725512315009</v>
       </c>
       <c r="F61" t="n">
-        <v>5.359334163538437</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -3406,47 +3782,53 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1.786444721179479</v>
+        <v>0.7027875853858349</v>
       </c>
       <c r="J61" t="n">
         <v>2</v>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" t="n">
+        <v>4.259150056293074</v>
+      </c>
+      <c r="L61" t="n">
+        <v>69.74982452392578</v>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L61" t="n">
-        <v>2</v>
-      </c>
-      <c r="M61" t="n">
-        <v>5.359334163538437</v>
+      <c r="N61" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" t="n">
+        <v>4.216725512315009</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C000636</t>
+          <t>C012566</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>11.06580893172652</v>
+        <v>21.44384181314243</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.3 | D=0.0 | P=-0.0 | A=1.8 | R=3.0</t>
+          <t>H=0.0 | C=4.1 | D=0.0 | P=-0.0 | A=1.4 | R=2.0 | Pop=71.8 | PopScore=4.3</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>5.294660130357306</v>
+        <v>4.12119091552514</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3455,47 +3837,53 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1.764886710119102</v>
+        <v>1.373730305175047</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4.288028983858216</v>
       </c>
       <c r="L62" t="n">
-        <v>3</v>
-      </c>
-      <c r="M62" t="n">
-        <v>5.294660130357306</v>
+        <v>71.82279205322266</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4.12119091552514</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C000665</t>
+          <t>C013790</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10.75390753275266</v>
+        <v>21.41611221830132</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>H=5.2 | C=0.0 | D=0.0 | P=-0.0 | A=0.9 | R=2.0</t>
+          <t>H=0.0 | C=4.3 | D=0.0 | P=-0.0 | A=1.4 | R=3.0 | Pop=60.8 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5.233342578224462</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>4.299876089662234</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3504,47 +3892,53 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8722237630374104</v>
+        <v>1.433292029887411</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.124343611996036</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
-      </c>
-      <c r="M63" t="n">
-        <v>5.233342578224462</v>
+        <v>60.82721328735352</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>3</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4.299876089662234</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C000668</t>
+          <t>C002499</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10.71938941581399</v>
+        <v>21.29013829482704</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.1 | D=0.0 | P=-0.0 | A=1.7 | R=3.5</t>
+          <t>H=0.0 | C=5.0 | D=0.0 | P=-0.0 | A=1.7 | R=2.0 | Pop=36.2 | PopScore=3.6</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>5.099699712695404</v>
+        <v>5.035759858469539</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3553,194 +3947,218 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1.699899904231801</v>
+        <v>1.678586619489846</v>
       </c>
       <c r="J64" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.616919971979658</v>
       </c>
       <c r="L64" t="n">
-        <v>4</v>
-      </c>
-      <c r="M64" t="n">
-        <v>5.099699712695404</v>
+        <v>36.22274398803711</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>2</v>
+      </c>
+      <c r="O64" t="n">
+        <v>5.035759858469539</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C000693</t>
+          <t>C003285</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>10.46730168377295</v>
+        <v>21.22307224184321</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.2 | D=0.0 | P=-0.8 | A=2.1 | R=3.0</t>
+          <t>H=0.0 | C=4.6 | D=0.0 | P=-0.0 | A=1.5 | R=2.0 | Pop=46.7 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>6.237103010418305</v>
+        <v>4.635489365046799</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8382692569147558</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>2.079034336806101</v>
+        <v>1.545163121682266</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3.865859066527126</v>
       </c>
       <c r="L65" t="n">
-        <v>3</v>
-      </c>
-      <c r="M65" t="n">
-        <v>6.237103010418305</v>
+        <v>46.74427032470703</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4.635489365046799</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C000716</t>
+          <t>C002329</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>10.28176721062322</v>
+        <v>21.10405973537998</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.0 | D=1.9 | P=-0.0 | A=2.0 | R=3.0</t>
+          <t>H=5.0 | C=0.0 | D=0.0 | P=-0.0 | A=0.8 | R=3.0 | Pop=34.8 | PopScore=3.6</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>4.995391982898593</v>
       </c>
       <c r="F66" t="n">
-        <v>2.952950685399849</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>1.940211780639116</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1.954422785452841</v>
+        <v>0.8325653304830989</v>
       </c>
       <c r="J66" t="n">
         <v>3</v>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" t="n">
+        <v>3.576673078844827</v>
+      </c>
+      <c r="L66" t="n">
+        <v>34.75439071655273</v>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L66" t="n">
-        <v>3</v>
-      </c>
-      <c r="M66" t="n">
-        <v>4.893162466038965</v>
+      <c r="N66" t="n">
+        <v>3</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4.995391982898593</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C000734</t>
+          <t>C004503</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>10.00108796174218</v>
+        <v>20.95503331833453</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.8 | D=1.9 | P=-0.0 | A=1.9 | R=3.0</t>
+          <t>H=0.0 | C=2.5 | D=1.4 | P=-0.0 | A=1.6 | R=3.0 | Pop=65.1 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>2.827951706319173</v>
+        <v>2.530708245784684</v>
       </c>
       <c r="G67" t="n">
-        <v>1.927277801086113</v>
+        <v>1.431681474416512</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1.906289469316114</v>
+        <v>1.559410152469817</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K67" t="n">
+        <v>4.191437620895052</v>
+      </c>
+      <c r="L67" t="n">
+        <v>65.11777496337891</v>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L67" t="n">
-        <v>3</v>
-      </c>
-      <c r="M67" t="n">
-        <v>4.755229507405287</v>
+      <c r="N67" t="n">
+        <v>3</v>
+      </c>
+      <c r="O67" t="n">
+        <v>3.962389720201196</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C000761</t>
+          <t>C000457</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>9.625495042231302</v>
+        <v>20.81542103854036</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.6 | D=0.0 | P=-0.0 | A=1.5 | R=2.0</t>
+          <t>H=0.0 | C=4.4 | D=0.0 | P=-0.0 | A=1.5 | R=2.0 | Pop=48.8 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>4.635489365031789</v>
+        <v>4.373189754483641</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3749,96 +4167,108 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1.545163121677263</v>
+        <v>1.457729918161214</v>
       </c>
       <c r="J68" t="n">
         <v>2</v>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K68" t="n">
+        <v>3.90775617925232</v>
+      </c>
+      <c r="L68" t="n">
+        <v>48.78711318969727</v>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M68" t="n">
-        <v>4.635489365031789</v>
+      <c r="N68" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4.373189754483641</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C000778</t>
+          <t>C004625</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>9.425271785204528</v>
+        <v>20.79230790464902</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.5 | D=0.0 | P=-0.0 | A=1.5 | R=3.5</t>
+          <t>H=0.0 | C=3.0 | D=1.9 | P=-0.0 | A=2.0 | R=3.0 | Pop=32.2 | PopScore=3.5</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>4.463248418953047</v>
+        <v>2.952950685405072</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1.940211780642993</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1.487749472984349</v>
+        <v>1.95442278545652</v>
       </c>
       <c r="J69" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.503513564669079</v>
       </c>
       <c r="L69" t="n">
-        <v>4</v>
-      </c>
-      <c r="M69" t="n">
-        <v>4.463248418953047</v>
+        <v>32.23200988769531</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>3</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4.893162466048064</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C000811</t>
+          <t>C001388</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9.09215250078045</v>
+        <v>20.72247200261078</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.4 | D=0.0 | P=-0.0 | A=1.5 | R=2.0</t>
+          <t>H=0.0 | C=3.7 | D=0.0 | P=-0.0 | A=1.2 | R=3.0 | Pop=73.0 | PopScore=4.3</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>4.373189754482189</v>
+        <v>3.692620096995865</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -3847,47 +4277,53 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1.45772991816073</v>
+        <v>1.230873365665288</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K70" t="n">
+        <v>4.304714824017505</v>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
-      </c>
-      <c r="M70" t="n">
-        <v>4.373189754482189</v>
+        <v>73.048095703125</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" t="n">
+        <v>3.692620096995865</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C000812</t>
+          <t>C002569</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>9.043081382307493</v>
+        <v>20.63697053399682</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.3 | D=0.0 | P=-0.0 | A=1.4 | R=3.0</t>
+          <t>H=0.0 | C=3.8 | D=0.0 | P=-0.0 | A=1.3 | R=3.0 | Pop=64.7 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>4.299876089659422</v>
+        <v>3.827820329916125</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -3896,145 +4332,163 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1.433292029886474</v>
+        <v>1.275940109972042</v>
       </c>
       <c r="J71" t="n">
         <v>3</v>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K71" t="n">
+        <v>4.184578621055787</v>
+      </c>
+      <c r="L71" t="n">
+        <v>64.66582489013672</v>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L71" t="n">
-        <v>3</v>
-      </c>
-      <c r="M71" t="n">
-        <v>4.299876089659422</v>
+      <c r="N71" t="n">
+        <v>3</v>
+      </c>
+      <c r="O71" t="n">
+        <v>3.827820329916125</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C000846</t>
+          <t>C009728</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>8.733486528088097</v>
+        <v>20.49795094052968</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.7 | D=1.4 | P=-0.0 | A=1.6 | R=3.0</t>
+          <t>H=0.0 | C=3.9 | D=0.0 | P=-0.0 | A=1.3 | R=3.5 | Pop=59.3 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>2.737857030764379</v>
+        <v>3.860569414898508</v>
       </c>
       <c r="G72" t="n">
-        <v>1.398297836845784</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1.611767928677685</v>
+        <v>1.286856471632836</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>4.099375487856459</v>
       </c>
       <c r="L72" t="n">
-        <v>3</v>
-      </c>
-      <c r="M72" t="n">
-        <v>4.136154867610164</v>
+        <v>59.30261611938477</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>4</v>
+      </c>
+      <c r="O72" t="n">
+        <v>3.860569414898508</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C000850</t>
+          <t>C013107</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>8.705932181602464</v>
+        <v>20.44527971232607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.2 | D=0.0 | P=-0.0 | A=1.4 | R=2.0</t>
+          <t>H=0.0 | C=6.9 | D=0.0 | P=-1.0 | A=2.3 | R=3.0 | Pop=20.0 | PopScore=3.0</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>4.183245335214327</v>
+        <v>6.915401198320448</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1.015271448997697</v>
       </c>
       <c r="I73" t="n">
-        <v>1.394415111738109</v>
+        <v>2.305133732773483</v>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K73" t="n">
+        <v>3.043259429800305</v>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
-      </c>
-      <c r="M73" t="n">
-        <v>4.183245335214327</v>
+        <v>19.9734935760498</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>3</v>
+      </c>
+      <c r="O73" t="n">
+        <v>6.915401198320448</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C000851</t>
+          <t>C011102</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>8.703729783135666</v>
+        <v>20.15742847916727</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>H=4.2 | C=0.0 | D=0.0 | P=-0.0 | A=0.7 | R=2.0</t>
+          <t>H=0.0 | C=3.8 | D=0.0 | P=-0.0 | A=1.3 | R=3.0 | Pop=57.1 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4.216725512298678</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>3.772306650585076</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -4043,145 +4497,163 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7027875853831129</v>
+        <v>1.257435550195025</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K74" t="n">
+        <v>4.062357207659206</v>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
-      </c>
-      <c r="M74" t="n">
-        <v>4.216725512298678</v>
+        <v>57.11112976074219</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>3</v>
+      </c>
+      <c r="O74" t="n">
+        <v>3.772306650585076</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C000861</t>
+          <t>C003299</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>8.617137835054999</v>
+        <v>20.03916473204784</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>H=4.1 | C=0.0 | D=0.0 | P=-0.0 | A=0.7 | R=3.5</t>
+          <t>H=0.0 | C=0.0 | D=3.5 | P=-0.0 | A=1.8 | R=3.0 | Pop=64.0 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4.099407190936363</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>3.518940451240022</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6832345318227271</v>
+        <v>1.759470225620011</v>
       </c>
       <c r="J75" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4.175112269001931</v>
       </c>
       <c r="L75" t="n">
-        <v>4</v>
-      </c>
-      <c r="M75" t="n">
-        <v>4.099407190936363</v>
+        <v>64.04714202880859</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>3</v>
+      </c>
+      <c r="O75" t="n">
+        <v>3.518940451240022</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C000901</t>
+          <t>C007629</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>8.199824476958087</v>
+        <v>19.79242665442377</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.9 | D=0.0 | P=-0.0 | A=1.3 | R=3.5</t>
+          <t>H=0.0 | C=2.9 | D=0.5 | P=-0.0 | A=1.2 | R=2.0 | Pop=66.7 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>3.860569414897419</v>
+        <v>2.936381335558953</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>0.4764708462320955</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1.286856471632473</v>
+        <v>1.217029201635699</v>
       </c>
       <c r="J76" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4.215006456892702</v>
       </c>
       <c r="L76" t="n">
-        <v>4</v>
-      </c>
-      <c r="M76" t="n">
-        <v>3.860569414897419</v>
+        <v>66.69460296630859</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>3.412852181791048</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C000911</t>
+          <t>C003503</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>8.083234670820534</v>
+        <v>19.59134245509013</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.8 | D=0.0 | P=-0.0 | A=1.3 | R=3.0</t>
+          <t>H=2.9 | C=0.0 | D=0.0 | P=-0.0 | A=0.5 | R=2.0 | Pop=90.5 | PopScore=4.5</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>2.897321255307693</v>
       </c>
       <c r="F77" t="n">
-        <v>3.827820329911738</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -4190,145 +4662,163 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1.275940109970579</v>
+        <v>0.4828868758846154</v>
       </c>
       <c r="J77" t="n">
-        <v>3</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4.516137085628762</v>
       </c>
       <c r="L77" t="n">
-        <v>3</v>
-      </c>
-      <c r="M77" t="n">
-        <v>3.827820329911738</v>
+        <v>90.48152923583984</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>2.897321255307693</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C000918</t>
+          <t>C007523</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>8.024684789096783</v>
+        <v>19.56230822293649</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>H=0.0 | C=1.9 | D=1.9 | P=-0.0 | A=1.6 | R=3.5</t>
+          <t>H=7.1 | C=0.0 | D=0.0 | P=-0.0 | A=1.2 | R=2.0 | Pop=4.3 | PopScore=1.7</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>7.11693830062474</v>
       </c>
       <c r="F78" t="n">
-        <v>1.864966596162784</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.893944411495507</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>1.568627737802015</v>
+        <v>1.186156383437457</v>
       </c>
       <c r="J78" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1.669938661114421</v>
       </c>
       <c r="L78" t="n">
-        <v>4</v>
-      </c>
-      <c r="M78" t="n">
-        <v>3.758911007658291</v>
+        <v>4.31184196472168</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>7.11693830062474</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C000923</t>
+          <t>C012535</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7.970356856189654</v>
+        <v>19.18777171328794</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.8 | D=0.0 | P=-0.0 | A=1.3 | R=3.0</t>
+          <t>H=4.9 | C=0.8 | D=1.7 | P=-0.0 | A=2.0 | R=2.0 | Pop=2.6 | PopScore=1.3</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>4.941164250425158</v>
       </c>
       <c r="F79" t="n">
-        <v>3.772306650585076</v>
+        <v>0.839974786229631</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1.699858572627701</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1.257435550195025</v>
+        <v>1.953448256794587</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1.276810556347832</v>
       </c>
       <c r="L79" t="n">
-        <v>3</v>
-      </c>
-      <c r="M79" t="n">
-        <v>3.772306650585076</v>
+        <v>2.585186719894409</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
+      </c>
+      <c r="O79" t="n">
+        <v>7.48099760928249</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C000944</t>
+          <t>C013820</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>7.80832753055957</v>
+        <v>18.96830414473136</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.7 | D=0.0 | P=-0.0 | A=1.2 | R=3.0</t>
+          <t>H=0.0 | C=3.3 | D=0.0 | P=-0.0 | A=1.1 | R=2.0 | Pop=54.4 | PopScore=4.0</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>3.69262009699651</v>
+        <v>3.307286388498296</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -4337,96 +4827,108 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1.230873365665503</v>
+        <v>1.102428796166099</v>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4.014496162706052</v>
       </c>
       <c r="L80" t="n">
-        <v>3</v>
-      </c>
-      <c r="M80" t="n">
-        <v>3.69262009699651</v>
+        <v>54.39537811279297</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>2</v>
+      </c>
+      <c r="O80" t="n">
+        <v>3.307286388498296</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C000973</t>
+          <t>C002955</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>7.513827925063221</v>
+        <v>18.70258967594721</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>H=0.0 | C=0.0 | D=3.5 | P=-0.0 | A=1.8 | R=3.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=64.0 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>2.940270563016239</v>
       </c>
       <c r="G81" t="n">
-        <v>3.518940451250351</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1.759470225625176</v>
+        <v>0.9800901876720797</v>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K81" t="n">
+        <v>4.174679843715841</v>
       </c>
       <c r="L81" t="n">
-        <v>3</v>
-      </c>
-      <c r="M81" t="n">
-        <v>3.518940451250351</v>
+        <v>64.01902008056641</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" t="n">
+        <v>2.940270563016239</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C000998</t>
+          <t>C000355</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7.311229723353519</v>
+        <v>18.62474664217783</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.5 | D=0.0 | P=-0.0 | A=1.2 | R=2.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0 | Pop=61.9 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>3.49732609345255</v>
+        <v>2.902167261053638</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4435,145 +4937,163 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>1.165775364484184</v>
+        <v>0.9673890870178793</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K82" t="n">
+        <v>4.14122440378959</v>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
-      </c>
-      <c r="M82" t="n">
-        <v>3.49732609345255</v>
+        <v>61.87976455688477</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>3</v>
+      </c>
+      <c r="O82" t="n">
+        <v>2.902167261053638</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C001013</t>
+          <t>C009484</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>7.147407283745667</v>
+        <v>18.55584654582344</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.5 | P=-0.0 | A=1.2 | R=2.0</t>
+          <t>H=6.3 | C=0.0 | D=0.0 | P=-0.0 | A=1.1 | R=2.0 | Pop=5.5 | PopScore=1.9</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>6.319133518128093</v>
       </c>
       <c r="F83" t="n">
-        <v>2.936381335558953</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4764708462320955</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1.217029201635699</v>
+        <v>1.053188919688016</v>
       </c>
       <c r="J83" t="n">
         <v>2</v>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K83" t="n">
+        <v>1.870753539199483</v>
+      </c>
+      <c r="L83" t="n">
+        <v>5.493187427520752</v>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L83" t="n">
-        <v>2</v>
-      </c>
-      <c r="M83" t="n">
-        <v>3.412852181791048</v>
+      <c r="N83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="n">
+        <v>6.319133518128093</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C001023</t>
+          <t>C005576</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>7.066111653949901</v>
+        <v>18.40808090620157</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>H=2.3 | C=0.0 | D=1.0 | P=-0.0 | A=0.9 | R=3.5</t>
+          <t>H=0.0 | C=2.6 | D=0.0 | P=-0.0 | A=0.9 | R=2.0 | Pop=74.3 | PopScore=4.3</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2.341859880898093</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>2.579124782857473</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9723711678725593</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8764955640859617</v>
+        <v>0.859708260952491</v>
       </c>
       <c r="J84" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K84" t="n">
+        <v>4.321286838130457</v>
       </c>
       <c r="L84" t="n">
-        <v>4</v>
-      </c>
-      <c r="M84" t="n">
-        <v>3.314231048770652</v>
+        <v>74.28544616699219</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" t="n">
+        <v>2.579124782857473</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C001036</t>
+          <t>C012055</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6.924815656613203</v>
+        <v>18.36185281806422</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.3 | D=0.0 | P=-0.0 | A=1.1 | R=2.0</t>
+          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=2.0 | Pop=62.2 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>3.307286388498296</v>
+        <v>2.814533612675373</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -4582,96 +5102,108 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>1.102428796166099</v>
+        <v>0.9381778708917909</v>
       </c>
       <c r="J85" t="n">
         <v>2</v>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K85" t="n">
+        <v>4.146322601874766</v>
+      </c>
+      <c r="L85" t="n">
+        <v>62.20115661621094</v>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L85" t="n">
-        <v>2</v>
-      </c>
-      <c r="M85" t="n">
-        <v>3.307286388498296</v>
+      <c r="N85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2.814533612675373</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C001063</t>
+          <t>C005101</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6.72245155385994</v>
+        <v>18.30867863439222</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>H=0.0 | C=0.0 | D=3.1 | P=-0.0 | A=1.6 | R=3.0</t>
+          <t>H=0.0 | C=2.8 | D=0.3 | P=-0.0 | A=1.1 | R=3.0 | Pop=49.3 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>2.783142749899745</v>
       </c>
       <c r="G86" t="n">
-        <v>3.132903197004849</v>
+        <v>0.2902671059658464</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1.566451598502424</v>
+        <v>1.072847802949505</v>
       </c>
       <c r="J86" t="n">
         <v>3</v>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K86" t="n">
+        <v>3.918191380788697</v>
+      </c>
+      <c r="L86" t="n">
+        <v>49.30937194824219</v>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="L86" t="n">
-        <v>3</v>
-      </c>
-      <c r="M86" t="n">
-        <v>3.132903197004849</v>
+      <c r="N86" t="n">
+        <v>3</v>
+      </c>
+      <c r="O86" t="n">
+        <v>3.073409855865592</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C001083</t>
+          <t>C010454</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6.445954548197911</v>
+        <v>18.26993157444471</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>H=3.1 | C=0.0 | D=0.0 | P=-0.0 | A=0.5 | R=2.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=56.6 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3.097167544560947</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>2.907250272935932</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4680,47 +5212,53 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5161945907601578</v>
+        <v>0.9690834243119771</v>
       </c>
       <c r="J87" t="n">
         <v>2</v>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K87" t="n">
+        <v>4.052840895380551</v>
+      </c>
+      <c r="L87" t="n">
+        <v>56.56074905395508</v>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L87" t="n">
-        <v>2</v>
-      </c>
-      <c r="M87" t="n">
-        <v>3.097167544560947</v>
+      <c r="N87" t="n">
+        <v>2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>2.907250272935932</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C001103</t>
+          <t>C008145</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>6.272547807805161</v>
+        <v>18.23640306428288</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
+          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=53.8 | PopScore=4.0</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>2.937318594002538</v>
+        <v>2.964500885514751</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4729,96 +5267,108 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9791061980008461</v>
+        <v>0.9881669618382501</v>
       </c>
       <c r="J88" t="n">
-        <v>3</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K88" t="n">
+        <v>4.002861532356519</v>
       </c>
       <c r="L88" t="n">
-        <v>3</v>
-      </c>
-      <c r="M88" t="n">
-        <v>2.937318594002538</v>
+        <v>53.75460815429688</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" t="n">
+        <v>2.964500885514751</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C001105</t>
+          <t>C008296</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6.26193764844994</v>
+        <v>18.15578680887578</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
+          <t>H=0.0 | C=1.2 | D=0.8 | P=-0.0 | A=0.8 | R=2.0 | Pop=98.6 | PopScore=4.6</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>2.981280810713085</v>
+        <v>1.203253305403871</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>0.8327698711867052</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.993760270237695</v>
+        <v>0.8174693707279761</v>
       </c>
       <c r="J89" t="n">
         <v>2</v>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K89" t="n">
+        <v>4.600664506207277</v>
+      </c>
+      <c r="L89" t="n">
+        <v>98.55044555664062</v>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L89" t="n">
-        <v>2</v>
-      </c>
-      <c r="M89" t="n">
-        <v>2.981280810713085</v>
+      <c r="N89" t="n">
+        <v>2</v>
+      </c>
+      <c r="O89" t="n">
+        <v>2.036023176590576</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C001107</t>
+          <t>C006879</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>6.252125132700542</v>
+        <v>18.0090305815006</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
+          <t>H=0.0 | C=3.3 | D=0.0 | P=-0.0 | A=1.1 | R=2.0 | Pop=40.4 | PopScore=3.7</t>
         </is>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>2.927274655426496</v>
+        <v>3.264930335612142</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -4827,47 +5377,53 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0.9757582184754987</v>
+        <v>1.088310111870714</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K90" t="n">
+        <v>3.723446299696415</v>
       </c>
       <c r="L90" t="n">
-        <v>3</v>
-      </c>
-      <c r="M90" t="n">
-        <v>2.927274655426496</v>
+        <v>40.4068489074707</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>3.264930335612142</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C001108</t>
+          <t>C010153</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6.24441894686862</v>
+        <v>17.65686473252007</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
+          <t>H=0.0 | C=4.5 | D=0.0 | P=-0.0 | A=1.5 | R=3.5 | Pop=14.5 | PopScore=2.7</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>2.972665055837026</v>
+        <v>4.463248418956013</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4876,47 +5432,53 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.9908883519456754</v>
+        <v>1.487749472985338</v>
       </c>
       <c r="J91" t="n">
-        <v>2</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2.743864315769838</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2.972665055837026</v>
+        <v>14.54694747924805</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>4</v>
+      </c>
+      <c r="O91" t="n">
+        <v>4.463248418956013</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C001113</t>
+          <t>C003964</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>6.223732527693402</v>
+        <v>17.58709108552898</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
+          <t>H=0.0 | C=2.7 | D=0.0 | P=-0.0 | A=0.9 | R=3.0 | Pop=51.4 | PopScore=4.0</t>
         </is>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>2.962491407062329</v>
+        <v>2.660939597323611</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -4925,47 +5487,53 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9874971356874429</v>
+        <v>0.886979865774537</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K92" t="n">
+        <v>3.958837968101435</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
-      </c>
-      <c r="M92" t="n">
-        <v>2.962491407062329</v>
+        <v>51.39640426635742</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>3</v>
+      </c>
+      <c r="O92" t="n">
+        <v>2.660939597323611</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C001119</t>
+          <t>C013966</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>6.201073430803066</v>
+        <v>17.50918176039009</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
+          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=2.0 | Pop=46.1 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>2.902167261050689</v>
+        <v>2.828606644240314</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -4974,47 +5542,53 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9673890870168962</v>
+        <v>0.9428688814134379</v>
       </c>
       <c r="J93" t="n">
-        <v>3</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K93" t="n">
+        <v>3.852560527922706</v>
       </c>
       <c r="L93" t="n">
-        <v>3</v>
-      </c>
-      <c r="M93" t="n">
-        <v>2.902167261050689</v>
+        <v>46.11354446411133</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>2</v>
+      </c>
+      <c r="O93" t="n">
+        <v>2.828606644240314</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C001125</t>
+          <t>C000888</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>6.14691969457726</v>
+        <v>17.47568534571645</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.5</t>
+          <t>H=0.0 | C=2.7 | D=0.0 | P=-0.0 | A=0.9 | R=3.0 | Pop=48.0 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>2.850944112087177</v>
+        <v>2.704190852491417</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -5023,194 +5597,218 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9503147040290592</v>
+        <v>0.9013969508304723</v>
       </c>
       <c r="J94" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3.892387981883525</v>
       </c>
       <c r="L94" t="n">
-        <v>4</v>
-      </c>
-      <c r="M94" t="n">
-        <v>2.850944112087177</v>
+        <v>48.02782440185547</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>3</v>
+      </c>
+      <c r="O94" t="n">
+        <v>2.704190852491417</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C001132</t>
+          <t>C000068</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>6.111408888303061</v>
+        <v>17.45402143499637</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
+          <t>H=1.3 | C=2.0 | D=0.4 | P=-1.0 | A=1.1 | R=3.0 | Pop=63.1 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1.331433635211078</v>
       </c>
       <c r="F95" t="n">
-        <v>2.907250272935932</v>
+        <v>2.041252395463951</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>0.3846345741024767</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>0.9844485460177469</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9690834243119771</v>
+        <v>1.094640358074402</v>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4.161087275895718</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
-      </c>
-      <c r="M95" t="n">
-        <v>2.907250272935932</v>
+        <v>63.1412239074707</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>3</v>
+      </c>
+      <c r="O95" t="n">
+        <v>3.757320604777506</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C001133</t>
+          <t>C001954</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>6.107434725714692</v>
+        <v>17.28369932128276</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0</t>
+          <t>H=0.0 | C=1.7 | D=0.6 | P=-0.0 | A=0.8 | R=3.5 | Pop=62.0 | PopScore=4.1</t>
         </is>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>2.856115438876078</v>
+        <v>1.651873015815432</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>0.5597941664238303</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.9520384796253594</v>
+        <v>0.8305214218170589</v>
       </c>
       <c r="J96" t="n">
-        <v>3</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="K96" t="n">
+        <v>4.142437604874178</v>
       </c>
       <c r="L96" t="n">
-        <v>3</v>
-      </c>
-      <c r="M96" t="n">
-        <v>2.856115438876078</v>
+        <v>61.95609664916992</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>4</v>
+      </c>
+      <c r="O96" t="n">
+        <v>2.211667182239262</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C001141</t>
+          <t>C008187</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>6.070292466579317</v>
+        <v>17.2775298135002</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=3.0</t>
+          <t>H=0.0 | C=0.0 | D=2.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=74.9 | PopScore=4.3</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>2.837848754055402</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1.994032912597058</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9459495846851339</v>
+        <v>0.997016456298529</v>
       </c>
       <c r="J97" t="n">
-        <v>3</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="K97" t="n">
+        <v>4.329920780892077</v>
       </c>
       <c r="L97" t="n">
-        <v>3</v>
-      </c>
-      <c r="M97" t="n">
-        <v>2.837848754055402</v>
+        <v>74.93827056884766</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>2</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1.994032912597058</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C001145</t>
+          <t>C013375</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>6.042931198203846</v>
+        <v>17.22524748024495</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>H=2.9 | C=0.0 | D=0.0 | P=-0.0 | A=0.5 | R=2.0</t>
+          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=38.1 | PopScore=3.7</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2.897321255307693</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>2.962491407066286</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -5219,47 +5817,53 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4828868758846154</v>
+        <v>0.9874971356887619</v>
       </c>
       <c r="J98" t="n">
         <v>2</v>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K98" t="n">
+        <v>3.667171650847834</v>
+      </c>
+      <c r="L98" t="n">
+        <v>38.14104461669922</v>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="L98" t="n">
-        <v>2</v>
-      </c>
-      <c r="M98" t="n">
-        <v>2.897321255307693</v>
+      <c r="N98" t="n">
+        <v>2</v>
+      </c>
+      <c r="O98" t="n">
+        <v>2.962491407066286</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C001152</t>
+          <t>C002520</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>6.008807926813411</v>
+        <v>17.2116064063011</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=2.0</t>
+          <t>H=0.0 | C=2.6 | D=0.0 | P=-0.0 | A=0.9 | R=3.0 | Pop=48.1 | PopScore=3.9</t>
         </is>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>2.856790783678727</v>
+        <v>2.57340946214139</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -5268,47 +5872,53 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9522635945595755</v>
+        <v>0.85780315404713</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K99" t="n">
+        <v>3.893002388871203</v>
       </c>
       <c r="L99" t="n">
-        <v>2</v>
-      </c>
-      <c r="M99" t="n">
-        <v>2.856790783678727</v>
+        <v>48.05795669555664</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>3</v>
+      </c>
+      <c r="O99" t="n">
+        <v>2.57340946214139</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C001165</t>
+          <t>C002593</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5.951500176645296</v>
+        <v>17.20280026967236</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=2.0</t>
+          <t>H=0.0 | C=2.1 | D=0.0 | P=-0.0 | A=0.7 | R=3.0 | Pop=65.0 | PopScore=4.2</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>2.828606644251785</v>
+        <v>2.130288984669355</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -5317,47 +5927,53 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0.9428688814172617</v>
+        <v>0.7100963282231182</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K100" t="n">
+        <v>4.190404222503778</v>
       </c>
       <c r="L100" t="n">
-        <v>2</v>
-      </c>
-      <c r="M100" t="n">
-        <v>2.828606644251785</v>
+        <v>65.04948425292969</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>3</v>
+      </c>
+      <c r="O100" t="n">
+        <v>2.130288984669355</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C001166</t>
+          <t>C001680</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5.947784333824027</v>
+        <v>17.15358996915397</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=2.0</t>
+          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0 | Pop=36.6 | PopScore=3.6</t>
         </is>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>2.826779180569194</v>
+        <v>2.937318594005888</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -5366,21 +5982,27 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0.9422597268563979</v>
+        <v>0.9791061980019629</v>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="K101" t="n">
+        <v>3.627014053780666</v>
       </c>
       <c r="L101" t="n">
-        <v>2</v>
-      </c>
-      <c r="M101" t="n">
-        <v>2.826779180569194</v>
+        <v>36.60037612915039</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>3</v>
+      </c>
+      <c r="O101" t="n">
+        <v>2.937318594005888</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/best_areas.xlsx
+++ b/data/processed/best_areas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,68 +451,103 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>prescription_component</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>competition_component</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>population_component</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>road_component</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>prescription_norm</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>competition_norm</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>population_norm</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>road_norm</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>prescription_score</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>competition_score</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>population_score</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>road_score</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>hospital_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>clinic_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>doctor_score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>competition_score</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>accessibility_score</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>road_score</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>population_score</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>road_type</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>road_weight</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>prescription_score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C005049</t>
+          <t>C009759</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>152.2458335984106</v>
+        <v>67.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -521,53 +556,74 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>H=7.5 | C=36.7 | D=49.9 | P=-17.4 | A=38.4 | R=3.0 | Pop=60.2 | PopScore=4.1</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=100.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7.503206542971671</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>36.68067306449847</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>49.85956986769806</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>17.44131900928699</v>
+        <v>7.5</v>
       </c>
       <c r="I2" t="n">
-        <v>38.40721037917714</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4.114056879339158</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>60.19447326660156</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M2" t="n">
+        <v>16.51184771146742</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>94.04344947516819</v>
+        <v>4.368882248176226</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.443471657628298</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5.555543759289683</v>
+      </c>
+      <c r="S2" t="n">
+        <v>9.512832294549437</v>
+      </c>
+      <c r="T2" t="n">
+        <v>77.95532989501953</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C010144</t>
+          <t>C000138</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>131.1203934800488</v>
+        <v>66.13962398319762</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -576,53 +632,74 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>H=10.3 | C=36.8 | D=35.7 | P=-17.1 | A=31.9 | R=2.0 | Pop=83.3 | PopScore=4.4</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=94.6 | Road=75.0</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.32873884313252</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>36.8394746908071</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>35.70506290083514</v>
+        <v>23.63962398319762</v>
       </c>
       <c r="H3" t="n">
-        <v>17.10478168980269</v>
+        <v>7.5</v>
       </c>
       <c r="I3" t="n">
-        <v>31.85381282120869</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.434268132595471</v>
+        <v>94.55849593279048</v>
       </c>
       <c r="L3" t="n">
-        <v>83.29041290283203</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14.29987736537275</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>82.87327643477477</v>
+        <v>4.1158933937474</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8.130224859129246</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6.169652506243509</v>
+      </c>
+      <c r="T3" t="n">
+        <v>60.30696105957031</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C003823</t>
+          <t>C013419</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100.9989823833701</v>
+        <v>65.42494696176338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -631,53 +708,74 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>H=12.3 | C=11.2 | D=25.9 | P=-4.1 | A=18.7 | R=2.0 | Pop=62.2 | PopScore=4.1</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=91.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12.34697120073556</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>11.1555702568467</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>25.88835262833924</v>
+        <v>22.92494696176339</v>
       </c>
       <c r="H4" t="n">
-        <v>4.098387000678795</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
-        <v>18.72052826657445</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>4.146767462302017</v>
+        <v>91.69978784705354</v>
       </c>
       <c r="L4" t="n">
-        <v>62.22927856445312</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14.1663681705177</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>49.3908940859215</v>
+        <v>3.991461024041562</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.608525682096874</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10.55784248842083</v>
+      </c>
+      <c r="T4" t="n">
+        <v>53.1339225769043</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C003450</t>
+          <t>C009261</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.7803814946822</v>
+        <v>65.36840622320143</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -686,53 +784,74 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>H=5.0 | C=10.4 | D=20.5 | P=-0.0 | A=14.5 | R=2.0 | Pop=87.0 | PopScore=4.5</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=91.5 | Road=75.0</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.954424467859699</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>10.42168495840273</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>20.47117022892906</v>
+        <v>22.86840622320143</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I5" t="n">
-        <v>14.53521751190872</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.477433477702784</v>
+        <v>91.47362489280573</v>
       </c>
       <c r="L5" t="n">
-        <v>87.00850677490234</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14.47159564706446</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>35.84727965519149</v>
+        <v>3.981616719729017</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>14.47159564706446</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>52.6036262512207</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C005034</t>
+          <t>C004996</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78.24311694896231</v>
+        <v>65.27313590200377</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -741,53 +860,74 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>H=9.0 | C=24.1 | D=10.9 | P=-7.8 | A=15.0 | R=3.0 | Pop=49.2 | PopScore=3.9</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=91.1 | Road=75.0</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9.040023607965294</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>24.10292321794611</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>10.86045501989848</v>
+        <v>22.77313590200377</v>
       </c>
       <c r="H6" t="n">
-        <v>7.768914938306009</v>
+        <v>7.5</v>
       </c>
       <c r="I6" t="n">
-        <v>14.97120585059217</v>
+        <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.915312495733783</v>
+        <v>91.09254360801509</v>
       </c>
       <c r="L6" t="n">
-        <v>49.16474533081055</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18.44093098873054</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>44.00340184580989</v>
+        <v>3.965029210303471</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>14.72328944197298</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.035025367816185</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.682616178941371</v>
+      </c>
+      <c r="T6" t="n">
+        <v>51.72180938720703</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C000178</t>
+          <t>C009017</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66.46850909104536</v>
+        <v>63.12186317729812</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -796,53 +936,74 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>H=0.0 | C=10.7 | D=22.1 | P=-4.2 | A=14.6 | R=3.0 | Pop=48.2 | PopScore=3.9</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=92.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>10.67810828022539</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>22.07466302594043</v>
+        <v>23.12186317729812</v>
       </c>
       <c r="H7" t="n">
-        <v>4.162207734391663</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>14.59670093971202</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.896639862639165</v>
+        <v>92.48745270919247</v>
       </c>
       <c r="L7" t="n">
-        <v>48.23672866821289</v>
-      </c>
-      <c r="M7" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15.66096022946828</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.025746093517168</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.691455119737899</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.31422922481618</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.655275884914199</v>
+      </c>
+      <c r="T7" t="n">
+        <v>55.02209091186523</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>32.75277130616583</v>
+      <c r="V7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C012630</t>
+          <t>C012479</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63.85241373373253</v>
+        <v>62.49594175647037</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -851,53 +1012,74 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>H=0.0 | C=18.5 | D=13.1 | P=-4.1 | A=12.7 | R=3.0 | Pop=44.8 | PopScore=3.8</t>
+          <t>Prescription=99.5 | Competition=0.0 | Population=90.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>34.82903748497327</v>
       </c>
       <c r="F8" t="n">
-        <v>18.50476759986521</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>13.10700375921821</v>
+        <v>22.6669042714971</v>
       </c>
       <c r="H8" t="n">
-        <v>4.138364947558304</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>12.72175774623084</v>
+        <v>99.51153567135221</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.823930027872508</v>
+        <v>90.6676170859884</v>
       </c>
       <c r="L8" t="n">
-        <v>44.78378677368164</v>
-      </c>
-      <c r="M8" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13.86471869370364</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.946533228027264</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10.73502665301193</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.744008625134775</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3856834155569375</v>
+      </c>
+      <c r="T8" t="n">
+        <v>50.75563049316406</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>31.61177135908342</v>
+      <c r="V8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C013600</t>
+          <t>C012629</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62.40361758297414</v>
+        <v>62.14404380146085</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -906,53 +1088,74 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>H=5.5 | C=4.6 | D=18.5 | P=-2.9 | A=11.7 | R=2.0 | Pop=66.2 | PopScore=4.2</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=88.6 | Road=50.0</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.488450747519946</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>4.638795203608812</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>18.47659404171509</v>
+        <v>22.14404380146085</v>
       </c>
       <c r="H9" t="n">
-        <v>2.932194972044189</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>11.69930387998047</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.207530708473655</v>
+        <v>88.57617520584338</v>
       </c>
       <c r="L9" t="n">
-        <v>66.19042205810547</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16.65055602921596</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>28.60383999284384</v>
+        <v>3.855498025605961</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8.665046346321709</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.894348002857561</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6.091161680036689</v>
+      </c>
+      <c r="T9" t="n">
+        <v>46.25214385986328</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C005080</t>
+          <t>C013729</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.49789215471246</v>
+        <v>61.82222056186308</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -961,53 +1164,74 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>H=6.7 | C=7.8 | D=18.0 | P=-4.7 | A=12.7 | R=3.5 | Pop=18.8 | PopScore=3.0</t>
+          <t>Prescription=100.0 | Competition=10.6 | Population=100.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.747676714883866</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
-        <v>7.845538347346629</v>
+        <v>3.177779438136925</v>
       </c>
       <c r="G10" t="n">
-        <v>17.98573221872826</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>4.747448385233445</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>12.73265834429365</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>10.59259812712308</v>
       </c>
       <c r="K10" t="n">
-        <v>2.986358971355304</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>18.81340980529785</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17.27743170594908</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>0.8546953997455184</v>
       </c>
       <c r="O10" t="n">
-        <v>32.57894728095876</v>
+        <v>4.439639397584378</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.8625006549112778</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10.67050215670293</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5.744428894334872</v>
+      </c>
+      <c r="T10" t="n">
+        <v>83.74437713623047</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C009766</t>
+          <t>C001872</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60.10875235362665</v>
+        <v>60.17561953859038</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1016,53 +1240,74 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>H=1.3 | C=17.8 | D=9.3 | P=-3.2 | A=10.8 | R=3.5 | Pop=47.6 | PopScore=3.9</t>
+          <t>Prescription=94.6 | Competition=0.0 | Population=78.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.290032651072631</v>
+        <v>33.09574754836455</v>
       </c>
       <c r="F11" t="n">
-        <v>17.79715424324383</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>9.259417406821518</v>
+        <v>19.57987199022583</v>
       </c>
       <c r="H11" t="n">
-        <v>3.220308836059012</v>
+        <v>7.5</v>
       </c>
       <c r="I11" t="n">
-        <v>10.77709889300415</v>
+        <v>94.55927870961301</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>78.31948796090332</v>
+      </c>
+      <c r="L11" t="n">
+        <v>75</v>
+      </c>
+      <c r="M11" t="n">
+        <v>13.17473185740145</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.409050238373943</v>
+      </c>
+      <c r="P11" t="n">
         <v>3.5</v>
       </c>
-      <c r="K11" t="n">
-        <v>3.882920123409102</v>
-      </c>
-      <c r="L11" t="n">
-        <v>47.56582641601562</v>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10.33562517302392</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.839106684377524</v>
+      </c>
+      <c r="T11" t="n">
+        <v>29.23651313781738</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>28.34660430113798</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C009195</t>
+          <t>C002139</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50.37479796641327</v>
+        <v>60.12498114994295</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1071,53 +1316,74 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>H=14.4 | C=1.2 | D=3.1 | P=-0.0 | A=4.3 | R=2.0 | Pop=63.3 | PopScore=4.2</t>
+          <t>Prescription=89.1 | Competition=0.0 | Population=85.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14.39515752672992</v>
+        <v>31.19413930690592</v>
       </c>
       <c r="F12" t="n">
-        <v>1.168460452173742</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3.061808531302996</v>
+        <v>21.43084184303703</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4.319584004164399</v>
+        <v>89.12611230544549</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1639955151945</v>
+        <v>85.72336737214813</v>
       </c>
       <c r="L12" t="n">
-        <v>63.32803344726562</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M12" t="n">
+        <v>12.41774098893925</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>18.62542651020666</v>
+        <v>3.731322479024902</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>9.783628745659058</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.634112243280191</v>
+      </c>
+      <c r="T12" t="n">
+        <v>40.7342643737793</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C009017</t>
+          <t>C005105</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>44.18725442655661</v>
+        <v>60.06327504669362</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1126,53 +1392,74 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>H=5.7 | C=6.3 | D=3.7 | P=-0.0 | A=4.9 | R=3.0 | Pop=55.0 | PopScore=4.0</t>
+          <t>Prescription=100.0 | Competition=16.5 | Population=100.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.691455119737899</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
-        <v>6.31422922481618</v>
+        <v>4.93672495330638</v>
       </c>
       <c r="G13" t="n">
-        <v>3.655275884914199</v>
+        <v>25</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.880956870685476</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>16.4557498443546</v>
       </c>
       <c r="K13" t="n">
-        <v>4.025746093517168</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>55.02209091186523</v>
-      </c>
-      <c r="M13" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M13" t="n">
+        <v>28.3771447042245</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.327781298085819</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.35559049529125</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>9.988164139416247</v>
+      </c>
+      <c r="R13" t="n">
+        <v>13.72884910660469</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.660131458203558</v>
+      </c>
+      <c r="T13" t="n">
+        <v>76.91281890869141</v>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>15.66096022946828</v>
+      <c r="V13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C003467</t>
+          <t>C008162</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>43.7469618622326</v>
+        <v>59.76664117776571</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1181,53 +1468,74 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H=0.0 | C=16.8 | D=2.7 | P=-3.2 | A=6.9 | R=2.0 | Pop=84.1 | PopScore=4.4</t>
+          <t>Prescription=87.5 | Competition=0.0 | Population=96.6 | Road=50.0</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>30.61686170909667</v>
       </c>
       <c r="F14" t="n">
-        <v>16.83420964215612</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.657241368377704</v>
+        <v>24.14977946866903</v>
       </c>
       <c r="H14" t="n">
-        <v>3.154326101402702</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.940023898240892</v>
+        <v>87.47674774027622</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4.444345251849656</v>
+        <v>96.59911787467612</v>
       </c>
       <c r="L14" t="n">
-        <v>84.14411163330078</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M14" t="n">
+        <v>12.187938729682</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>19.49145101053382</v>
+        <v>4.204716532132689</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8.618143666159648</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.569795063522354</v>
+      </c>
+      <c r="T14" t="n">
+        <v>66.00160217285156</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C009261</t>
+          <t>C000086</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41.7204279748848</v>
+        <v>59.248137412368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1236,53 +1544,74 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>H=0.0 | C=14.5 | D=0.0 | P=-0.0 | A=4.8 | R=3.5 | Pop=52.6 | PopScore=4.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=67.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
-        <v>14.47159564706446</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>16.748137412368</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I15" t="n">
-        <v>4.823865215688155</v>
+        <v>100</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>66.99254964947201</v>
+      </c>
+      <c r="L15" t="n">
+        <v>75</v>
+      </c>
+      <c r="M15" t="n">
+        <v>14.6176870305769</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.916017115252559</v>
+      </c>
+      <c r="P15" t="n">
         <v>3.5</v>
       </c>
-      <c r="K15" t="n">
-        <v>3.981616719729017</v>
-      </c>
-      <c r="L15" t="n">
-        <v>52.6036262512207</v>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7.904269188429921</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6.713417842146983</v>
+      </c>
+      <c r="T15" t="n">
+        <v>17.46758651733398</v>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="V15" t="n">
         <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>14.47159564706446</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C013577</t>
+          <t>C008345</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>40.38279149254797</v>
+        <v>58.5540126333852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1291,53 +1620,74 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>H=0.0 | C=8.6 | D=4.3 | P=-0.0 | A=5.0 | R=2.0 | Pop=103.2 | PopScore=4.6</t>
+          <t>Prescription=99.7 | Competition=10.4 | Population=87.1 | Road=50.0</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>34.89544288428147</v>
       </c>
       <c r="F16" t="n">
-        <v>8.603859148010979</v>
+        <v>3.121886771380264</v>
       </c>
       <c r="G16" t="n">
-        <v>4.268245621894352</v>
+        <v>21.78045652048399</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.002075860284169</v>
+        <v>99.70126538366137</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>10.40628923793421</v>
       </c>
       <c r="K16" t="n">
-        <v>4.646124788902965</v>
+        <v>87.12182608193595</v>
       </c>
       <c r="L16" t="n">
-        <v>103.1804809570312</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13.89115330825619</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>0.8396625108725151</v>
       </c>
       <c r="O16" t="n">
-        <v>12.87210476990533</v>
+        <v>3.792193867769657</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.003067283305269</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.787889982759375</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10.10019604219154</v>
+      </c>
+      <c r="T16" t="n">
+        <v>43.35359954833984</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C012479</t>
+          <t>C013500</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40.15870530732162</v>
+        <v>56.46935742914103</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1346,53 +1696,74 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>H=10.7 | C=2.7 | D=0.4 | P=-0.0 | A=2.9 | R=3.0 | Pop=50.8 | PopScore=3.9</t>
+          <t>Prescription=93.0 | Competition=0.0 | Population=95.6 | Road=0.0</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10.73502665301193</v>
+        <v>32.55794434772347</v>
       </c>
       <c r="F17" t="n">
-        <v>2.744008625134775</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3856834155569375</v>
+        <v>23.91141308141756</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2.896682358325382</v>
+        <v>93.02269813635277</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3.946533228027264</v>
+        <v>95.64565232567026</v>
       </c>
       <c r="L17" t="n">
-        <v>50.75563049316406</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>12.96064353834643</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>13.86471869370364</v>
+        <v>4.163214575956184</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>12.96064353834643</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>63.27781677246094</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C013500</t>
+          <t>C000424</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.04295225583963</v>
+        <v>53.88578640764644</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1401,43 +1772,64 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>H=0.0 | C=13.0 | D=0.0 | P=-0.0 | A=4.3 | R=2.0 | Pop=63.3 | PopScore=4.2</t>
+          <t>Prescription=74.6 | Competition=0.0 | Population=91.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>26.09451659110864</v>
       </c>
       <c r="F18" t="n">
-        <v>12.96064353834643</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>22.79126981653779</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>4.320214512782144</v>
+        <v>74.55576168888184</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.163214575956184</v>
+        <v>91.16507926615117</v>
       </c>
       <c r="L18" t="n">
-        <v>63.27781677246094</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10.3876867725672</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>12.96064353834643</v>
+        <v>3.968186504983218</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9.391685291600806</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.9960014809663902</v>
+      </c>
+      <c r="T18" t="n">
+        <v>51.88853073120117</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1447,7 +1839,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38.43194566476656</v>
+        <v>51.80656184533169</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1456,53 +1848,74 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>H=12.3 | C=0.0 | D=2.3 | P=-0.0 | A=3.2 | R=2.0 | Pop=17.7 | PopScore=2.9</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=67.2 | Road=0.0</t>
         </is>
       </c>
       <c r="E19" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>16.80656184533169</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>67.22624738132676</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>14.56741730093812</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.926189389474839</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
         <v>12.29483911743335</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.272578183504773</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.185428944657945</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="T19" t="n">
+        <v>17.65640258789062</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
         <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.926189389474839</v>
-      </c>
-      <c r="L19" t="n">
-        <v>17.65640258789062</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>14.56741730093812</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C010110</t>
+          <t>C000101</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>37.85652144781051</v>
+        <v>51.72313635741015</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1511,53 +1924,74 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>H=0.0 | C=7.5 | D=5.4 | P=-0.0 | A=5.2 | R=2.0 | Pop=43.5 | PopScore=3.8</t>
+          <t>Prescription=79.5 | Competition=14.7 | Population=93.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>27.84055308493168</v>
       </c>
       <c r="F20" t="n">
-        <v>7.512356792524591</v>
+        <v>4.408512129753122</v>
       </c>
       <c r="G20" t="n">
-        <v>5.364958206938954</v>
+        <v>23.29109540223159</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.186598034311007</v>
+        <v>79.54443738551909</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>14.69504043251041</v>
       </c>
       <c r="K20" t="n">
-        <v>3.794410548484106</v>
+        <v>93.16438160892636</v>
       </c>
       <c r="L20" t="n">
-        <v>43.4520263671875</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11.0827477493812</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1.185713203315138</v>
       </c>
       <c r="O20" t="n">
-        <v>12.87731499946354</v>
+        <v>4.055211105190279</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.315526071977458</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5.176321890113948</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.590899787289793</v>
+      </c>
+      <c r="T20" t="n">
+        <v>56.69734191894531</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C008162</t>
+          <t>C009733</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>37.75578826447685</v>
+        <v>51.61742848372653</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1566,53 +2000,74 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>H=0.0 | C=8.6 | D=3.6 | P=-0.0 | A=4.7 | R=3.0 | Pop=66.0 | PopScore=4.2</t>
+          <t>Prescription=68.0 | Competition=0.0 | Population=81.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>23.78747250060239</v>
       </c>
       <c r="F21" t="n">
-        <v>8.618143666159648</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>3.569795063522354</v>
+        <v>20.32995598312414</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I21" t="n">
-        <v>4.657612087147726</v>
+        <v>67.96420714457825</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4.204716532132689</v>
+        <v>81.31982393249658</v>
       </c>
       <c r="L21" t="n">
-        <v>66.00160217285156</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M21" t="n">
+        <v>9.46930028707672</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>12.187938729682</v>
+        <v>3.539647313577855</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.831780012489994</v>
+      </c>
+      <c r="R21" t="n">
+        <v>5.637520274586725</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>33.45476531982422</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C010638</t>
+          <t>C012336</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35.12727087790941</v>
+        <v>50.62480463778627</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1621,108 +2076,150 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.3 | D=7.0 | P=-1.0 | A=5.6 | R=3.0 | Pop=32.3 | PopScore=3.5</t>
+          <t>Prescription=95.3 | Competition=0.0 | Population=69.1 | Road=0.0</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>33.35052392140594</v>
       </c>
       <c r="F22" t="n">
-        <v>6.303320442934357</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>7.046935017718495</v>
+        <v>17.27428071638033</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9837542626313882</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>5.6245743231707</v>
+        <v>95.28721120401697</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5051884373936</v>
+        <v>69.09712286552131</v>
       </c>
       <c r="L22" t="n">
-        <v>32.28771591186523</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>13.27615305640946</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>13.35025546065285</v>
+        <v>3.007623891683858</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>12.17389847792689</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.102254578482571</v>
+      </c>
+      <c r="T22" t="n">
+        <v>19.2392520904541</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C001412</t>
+          <t>C007949</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34.055939319896</v>
+        <v>49.71240805785547</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>H=10.9 | C=0.0 | D=1.1 | P=-0.0 | A=2.4 | R=3.0 | Pop=23.0 | PopScore=3.2</t>
+          <t>Prescription=60.6 | Competition=0.0 | Population=94.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10.87807738632181</v>
+        <v>21.20469825695342</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.112129259612113</v>
+        <v>23.50770980090205</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>2.369077527526358</v>
+        <v>60.58485216272405</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3.17953942509184</v>
+        <v>94.03083920360821</v>
       </c>
       <c r="L23" t="n">
-        <v>23.03568077087402</v>
-      </c>
-      <c r="M23" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M23" t="n">
+        <v>8.441151336564211</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.092925824050106</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.437333420948989</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.003817915615222</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>58.91493606567383</v>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>11.99020664593392</v>
+      <c r="V23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C000101</t>
+          <t>C001072</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>31.4313370246224</v>
+        <v>49.60662477693847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1731,108 +2228,150 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>H=3.3 | C=5.2 | D=2.6 | P=-1.2 | A=3.6 | R=3.0 | Pop=56.7 | PopScore=4.1</t>
+          <t>Prescription=63.8 | Competition=0.0 | Population=89.1 | Road=50.0</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.315526071977458</v>
+        <v>22.32745553064121</v>
       </c>
       <c r="F24" t="n">
-        <v>5.176321890113948</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.590899787289793</v>
+        <v>22.27916924629727</v>
       </c>
       <c r="H24" t="n">
-        <v>1.185713203315138</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>3.57347820234579</v>
+        <v>63.79273008754631</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>4.055211105190279</v>
+        <v>89.11667698518909</v>
       </c>
       <c r="L24" t="n">
-        <v>56.69734191894531</v>
-      </c>
-      <c r="M24" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M24" t="n">
+        <v>8.888097760728444</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.879024708015324</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.917634677837338</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5.970463082891105</v>
+      </c>
+      <c r="T24" t="n">
+        <v>47.37701034545898</v>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>11.0827477493812</v>
+      <c r="V24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C002152</t>
+          <t>C009251</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>30.87656602088459</v>
+        <v>48.48451732496753</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>H=5.9 | C=5.3 | D=0.0 | P=-0.9 | A=2.8 | R=3.0 | Pop=31.8 | PopScore=3.5</t>
+          <t>Prescription=51.3 | Competition=0.0 | Population=92.1 | Road=75.0</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.911861988325854</v>
+        <v>17.95085038129304</v>
       </c>
       <c r="F25" t="n">
-        <v>5.311549128188136</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>23.03366694367449</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8718113783728645</v>
+        <v>7.5</v>
       </c>
       <c r="I25" t="n">
-        <v>2.755826707450354</v>
+        <v>51.28814394655156</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3.489865084076724</v>
+        <v>92.13466777469796</v>
       </c>
       <c r="L25" t="n">
-        <v>31.78152465820312</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7.145861867608882</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>11.22341111651399</v>
+        <v>4.010390253018906</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.8378481678594797</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4.411657315824704</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.896356383924698</v>
+      </c>
+      <c r="T25" t="n">
+        <v>54.16839599609375</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C007153</t>
+          <t>C010135</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>30.63719787594754</v>
+        <v>48.05491519850658</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1841,218 +2380,302 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>H=5.8 | C=2.9 | D=0.0 | P=-0.0 | A=1.9 | R=2.0 | Pop=71.5 | PopScore=4.3</t>
+          <t>Prescription=100.0 | Competition=52.5 | Population=95.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5.828603238305402</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>2.868906694920994</v>
+        <v>15.74723544578666</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>23.80215064429324</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.927736104691232</v>
+        <v>100</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>52.49078481928887</v>
       </c>
       <c r="K26" t="n">
-        <v>4.283134799675208</v>
+        <v>95.20860257717297</v>
       </c>
       <c r="L26" t="n">
-        <v>71.46725463867188</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M26" t="n">
+        <v>37.51187441225131</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>4.235375662860431</v>
       </c>
       <c r="O26" t="n">
-        <v>8.697509933226396</v>
+        <v>4.144190900136958</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>21.28470454870176</v>
+      </c>
+      <c r="S26" t="n">
+        <v>16.22716986354955</v>
+      </c>
+      <c r="T26" t="n">
+        <v>62.06657409667969</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C001072</t>
+          <t>C003250</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30.10904728890866</v>
+        <v>46.63412035944046</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=6.0 | P=-0.0 | A=4.0 | R=3.0 | Pop=47.4 | PopScore=3.9</t>
+          <t>Prescription=58.9 | Competition=0.0 | Population=84.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>20.63128163322788</v>
       </c>
       <c r="F27" t="n">
-        <v>2.917634677837338</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>5.970463082891105</v>
+        <v>21.00283872621258</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>3.957776434057998</v>
+        <v>58.94651895207966</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>3.879024708015324</v>
+        <v>84.01135490485032</v>
       </c>
       <c r="L27" t="n">
-        <v>47.37701034545898</v>
-      </c>
-      <c r="M27" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M27" t="n">
+        <v>8.212886051148903</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.656802884199994</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.816629923851119</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.221403653836721</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.174852473461062</v>
+      </c>
+      <c r="T27" t="n">
+        <v>37.73729705810547</v>
+      </c>
+      <c r="U27" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" t="n">
-        <v>8.888097760728444</v>
+      <c r="V27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C007949</t>
+          <t>C007153</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.65182963281506</v>
+        <v>46.448861632499</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>H=5.4 | C=3.0 | D=0.0 | P=-0.0 | A=1.9 | R=3.0 | Pop=58.9 | PopScore=4.1</t>
+          <t>Prescription=62.4 | Competition=0.0 | Population=98.4 | Road=0.0</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5.437333420948989</v>
+        <v>21.84868702946253</v>
       </c>
       <c r="F28" t="n">
-        <v>3.003817915615222</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>24.60017460303647</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1.907494875363239</v>
+        <v>62.42482008417867</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>4.092925824050106</v>
+        <v>98.40069841214589</v>
       </c>
       <c r="L28" t="n">
-        <v>58.91493606567383</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>8.697509933226396</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>8.441151336564211</v>
+        <v>4.283134799675208</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>5.828603238305402</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.868906694920994</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>71.46725463867188</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C000329</t>
+          <t>C009276</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.37567315045393</v>
+        <v>46.00132372369897</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>H=0.0 | C=9.5 | D=7.9 | P=-5.8 | A=7.1 | R=3.0 | Pop=36.9 | PopScore=3.6</t>
+          <t>Prescription=38.6 | Competition=0.0 | Population=100.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>13.50132372369897</v>
       </c>
       <c r="F29" t="n">
-        <v>9.508691587425922</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>7.889633812909215</v>
+        <v>25</v>
       </c>
       <c r="H29" t="n">
-        <v>5.779239989659096</v>
+        <v>7.5</v>
       </c>
       <c r="I29" t="n">
-        <v>7.114380768929914</v>
+        <v>38.57521063913993</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3.635101413955985</v>
+        <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>36.90569686889648</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.374597431883562</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>17.39832540033514</v>
+        <v>4.371524559764783</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.689398157092578</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.685199274790985</v>
+      </c>
+      <c r="T29" t="n">
+        <v>78.16423034667969</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C000083</t>
+          <t>C010639</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29.33345828406825</v>
+        <v>45.61347133350648</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2061,988 +2684,1366 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.6 | D=3.9 | P=-0.0 | A=3.5 | R=3.5 | Pop=46.8 | PopScore=3.9</t>
+          <t>Prescription=100.0 | Competition=63.1 | Population=98.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F30" t="n">
-        <v>4.620588592704674</v>
+        <v>18.93826130957106</v>
       </c>
       <c r="G30" t="n">
-        <v>3.896417821776707</v>
+        <v>24.55173264307755</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>3.488405108456578</v>
+        <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>63.1275376985702</v>
       </c>
       <c r="K30" t="n">
-        <v>3.866868314753275</v>
+        <v>98.20693057231018</v>
       </c>
       <c r="L30" t="n">
-        <v>46.79248046875</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M30" t="n">
+        <v>15.26680285426496</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>5.093633820589746</v>
       </c>
       <c r="O30" t="n">
-        <v>8.517006414481381</v>
+        <v>4.274700573178339</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6.521435483981919</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8.745367370283038</v>
+      </c>
+      <c r="T30" t="n">
+        <v>70.85861968994141</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C010348</t>
+          <t>C002749</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29.15867748541768</v>
+        <v>45.41052252329797</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>H=5.7 | C=2.2 | D=0.0 | P=-0.0 | A=1.7 | R=2.0 | Pop=74.7 | PopScore=4.3</t>
+          <t>Prescription=37.9 | Competition=0.0 | Population=98.5 | Road=75.0</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5.749083099575197</v>
+        <v>13.27859588568416</v>
       </c>
       <c r="F31" t="n">
-        <v>2.156139470819884</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>24.63192663761381</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I31" t="n">
-        <v>1.676893673535828</v>
+        <v>37.93884538766903</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>4.326847659091311</v>
+        <v>98.52770655045524</v>
       </c>
       <c r="L31" t="n">
-        <v>74.70526123046875</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5.285934091110377</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>7.905222570395081</v>
+        <v>4.288663144349717</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.285934091110377</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>71.86898803710938</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C002135</t>
+          <t>C002731</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28.97982846590996</v>
+        <v>45.19814001045243</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.8 | D=2.0 | P=-0.0 | A=3.3 | R=3.5 | Pop=33.8 | PopScore=3.6</t>
+          <t>Prescription=56.9 | Competition=0.0 | Population=81.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>19.89907236321378</v>
       </c>
       <c r="F32" t="n">
-        <v>6.828422784918054</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.99744542351781</v>
+        <v>20.29906764723866</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>3.274863640064924</v>
+        <v>56.85449246632508</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3.550201895010578</v>
+        <v>81.19627058895463</v>
       </c>
       <c r="L32" t="n">
-        <v>33.82034683227539</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M32" t="n">
+        <v>7.921408701019788</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>8.825868208435864</v>
+        <v>3.534269347426393</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.440739442429406</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.480669258590382</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>33.26996612548828</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C000421</t>
+          <t>C007221</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.20786679371711</v>
+        <v>44.47751858461215</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.2 | D=2.7 | P=-0.0 | A=3.1 | R=2.0 | Pop=49.9 | PopScore=3.9</t>
+          <t>Prescription=48.0 | Competition=0.0 | Population=90.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>16.79369801097107</v>
       </c>
       <c r="F33" t="n">
-        <v>5.209290742673871</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2.745111592456297</v>
+        <v>22.68382057364108</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>3.108986043786105</v>
+        <v>47.9819943170602</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3.929387839692722</v>
+        <v>90.73528229456431</v>
       </c>
       <c r="L33" t="n">
-        <v>49.87582397460938</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M33" t="n">
+        <v>6.685223467618975</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>7.954402335130167</v>
+        <v>3.949478524292997</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.629728717812311</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.055494749806664</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>50.90829086303711</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C004536</t>
+          <t>C005092</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.8723351666621</v>
+        <v>43.03412109582057</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=4.2 | P=-0.0 | A=3.0 | R=2.0 | Pop=82.6 | PopScore=4.4</t>
+          <t>Prescription=51.6 | Competition=0.0 | Population=79.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>18.04774255974857</v>
       </c>
       <c r="F34" t="n">
-        <v>2.884034236427663</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>4.160424044356455</v>
+        <v>19.986378536072</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>3.041556767654115</v>
+        <v>51.56497874213879</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>4.426420976109486</v>
+        <v>79.945514144288</v>
       </c>
       <c r="L34" t="n">
-        <v>82.63156127929688</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M34" t="n">
+        <v>7.184432637716602</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>7.044458280784118</v>
+        <v>3.479827066624365</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.641167798163308</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.543264839553295</v>
+      </c>
+      <c r="T34" t="n">
+        <v>31.45410919189453</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C008680</t>
+          <t>C001396</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27.14040499478731</v>
+        <v>42.86265542999502</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>H=5.4 | C=0.0 | D=1.8 | P=-0.0 | A=1.8 | R=2.0 | Pop=62.6 | PopScore=4.2</t>
+          <t>Prescription=29.6 | Competition=0.0 | Population=100.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.388515065028164</v>
+        <v>10.36265542999501</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.76319376362805</v>
+        <v>25</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I35" t="n">
-        <v>1.779682725985386</v>
+        <v>29.6075869428429</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>4.153006354958781</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>62.62499237060547</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.125158569732197</v>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>7.151708828656214</v>
+        <v>4.436695914981709</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4.125158569732197</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>83.49530029296875</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C002731</t>
+          <t>C013609</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26.91899341031226</v>
+        <v>42.74259460910534</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>H=5.4 | C=2.5 | D=0.0 | P=-0.0 | A=1.7 | R=3.0 | Pop=33.3 | PopScore=3.5</t>
+          <t>Prescription=51.6 | Competition=0.0 | Population=98.7 | Road=0.0</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.440739442429406</v>
+        <v>18.06289490015254</v>
       </c>
       <c r="F36" t="n">
-        <v>2.480669258590382</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>24.6796997089528</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1.733679659935028</v>
+        <v>51.60827114329297</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>3.534269347426393</v>
+        <v>98.7187988358112</v>
       </c>
       <c r="L36" t="n">
-        <v>33.26996612548828</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.190464470704891</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>7.921408701019788</v>
+        <v>4.296980910692486</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>4.265947898143581</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.92451657256131</v>
+      </c>
+      <c r="T36" t="n">
+        <v>72.47762298583984</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C003481</t>
+          <t>C001844</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26.35352653782149</v>
+        <v>42.74100470540596</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>H=3.8 | C=2.6 | D=0.0 | P=-0.0 | A=1.5 | R=2.0 | Pop=80.2 | PopScore=4.4</t>
+          <t>Prescription=42.3 | Competition=0.0 | Population=91.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.805604668166855</v>
+        <v>14.81946861929645</v>
       </c>
       <c r="F37" t="n">
-        <v>2.600561869615027</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>22.9215360861095</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>1.501121401232818</v>
+        <v>42.34133891227557</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>4.39702710737815</v>
+        <v>91.68614434443802</v>
       </c>
       <c r="L37" t="n">
-        <v>80.20908355712891</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.899323622863868</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6.406166537781882</v>
+        <v>3.990867156703372</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5.899323622863868</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>53.10178375244141</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C003128</t>
+          <t>C004536</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.18591276209523</v>
+        <v>42.69611825115366</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>H=7.0 | C=2.0 | D=0.0 | P=-1.7 | A=1.8 | R=2.0 | Pop=76.5 | PopScore=4.3</t>
+          <t>Prescription=50.6 | Competition=0.0 | Population=100.0 | Road=0.0</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6.989004499737087</v>
+        <v>17.69611825115366</v>
       </c>
       <c r="F38" t="n">
-        <v>1.964123331075413</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H38" t="n">
-        <v>1.717308862274173</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1.819541860314652</v>
+        <v>50.56033786043904</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>100</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>7.044458280784118</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4.426420976109486</v>
+      </c>
+      <c r="P38" t="n">
         <v>2</v>
       </c>
-      <c r="K38" t="n">
-        <v>4.349876500420431</v>
-      </c>
-      <c r="L38" t="n">
-        <v>76.46889495849609</v>
-      </c>
-      <c r="M38" t="inlineStr">
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.884034236427663</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.160424044356455</v>
+      </c>
+      <c r="T38" t="n">
+        <v>82.63156127929688</v>
+      </c>
+      <c r="U38" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="N38" t="n">
+      <c r="V38" t="n">
         <v>2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>8.9531278308125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C008633</t>
+          <t>C000644</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26.14907113066759</v>
+        <v>42.51186752887152</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>H=11.5 | C=5.7 | D=5.0 | P=-10.8 | A=6.3 | R=3.5 | Pop=82.2 | PopScore=4.4</t>
+          <t>Prescription=53.0 | Competition=0.0 | Population=75.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>11.49874588567654</v>
+        <v>18.53531770294905</v>
       </c>
       <c r="F39" t="n">
-        <v>5.665547634402373</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>5.033028302640711</v>
+        <v>18.97654982592247</v>
       </c>
       <c r="H39" t="n">
-        <v>10.83004941088425</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>6.321487677067238</v>
+        <v>52.95805057985442</v>
       </c>
       <c r="J39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>4.420808983391451</v>
+        <v>75.90619930368989</v>
       </c>
       <c r="L39" t="n">
-        <v>82.16353607177734</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M39" t="n">
+        <v>7.37852620706756</v>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>22.19732182271963</v>
+        <v>3.304005855598542</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.424949195382705</v>
+      </c>
+      <c r="R39" t="n">
+        <v>4.953577011684855</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>26.22146606445312</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C007221</t>
+          <t>C002290</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25.64789447840737</v>
+        <v>42.18564171419526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>H=5.6 | C=1.1 | D=0.0 | P=-0.0 | A=1.3 | R=3.0 | Pop=50.9 | PopScore=3.9</t>
+          <t>Prescription=40.5 | Competition=0.0 | Population=92.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5.629728717812311</v>
+        <v>14.18679431316879</v>
       </c>
       <c r="F40" t="n">
-        <v>1.055494749806664</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>22.99884740102647</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I40" t="n">
-        <v>1.290119702904273</v>
+        <v>40.53369803762513</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>3.949478524292997</v>
+        <v>91.99538960410588</v>
       </c>
       <c r="L40" t="n">
-        <v>50.90829086303711</v>
-      </c>
-      <c r="M40" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M40" t="n">
+        <v>5.647469081004117</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4.004327824713779</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.382385358840881</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.265083722163237</v>
+      </c>
+      <c r="T40" t="n">
+        <v>53.83495330810547</v>
+      </c>
+      <c r="U40" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>6.685223467618975</v>
+      <c r="V40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C001365</t>
+          <t>C003482</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25.54091485555339</v>
+        <v>42.16729634962339</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.6 | D=5.8 | P=-1.2 | A=3.7 | R=2.0 | Pop=54.3 | PopScore=4.0</t>
+          <t>Prescription=50.4 | Competition=0.0 | Population=98.2 | Road=0.0</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>17.62488291390111</v>
       </c>
       <c r="F41" t="n">
-        <v>2.575962790427726</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>5.751932056380634</v>
+        <v>24.54241343572228</v>
       </c>
       <c r="H41" t="n">
-        <v>1.242562953267371</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>3.734620291666225</v>
+        <v>50.35680832543176</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>98.16965374288911</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>7.016100967938944</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4.27307800659201</v>
+      </c>
+      <c r="P41" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="n">
-        <v>4.013117330857386</v>
-      </c>
-      <c r="L41" t="n">
-        <v>54.31904983520508</v>
-      </c>
-      <c r="M41" t="inlineStr">
+      <c r="Q41" t="n">
+        <v>5.77119842704059</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.244902540898354</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>70.74211883544922</v>
+      </c>
+      <c r="U41" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="N41" t="n">
+      <c r="V41" t="n">
         <v>2</v>
-      </c>
-      <c r="O41" t="n">
-        <v>8.327894846808359</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C005092</t>
+          <t>C008680</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25.42354864388941</v>
+        <v>41.81832050009496</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.6 | D=4.5 | P=-0.0 | A=3.2 | R=3.0 | Pop=31.5 | PopScore=3.5</t>
+          <t>Prescription=51.3 | Competition=0.0 | Population=95.4 | Road=0.0</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>17.96553831185908</v>
       </c>
       <c r="F42" t="n">
-        <v>2.641167798163308</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>4.543264839553295</v>
+        <v>23.85278218823589</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>3.152021685831083</v>
+        <v>51.33010946245451</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>3.479827066624365</v>
+        <v>95.41112875294354</v>
       </c>
       <c r="L42" t="n">
-        <v>31.45410919189453</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7.151708828656214</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>7.184432637716602</v>
+        <v>4.153006354958781</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>5.388515065028164</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.76319376362805</v>
+      </c>
+      <c r="T42" t="n">
+        <v>62.62499237060547</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C009257</t>
+          <t>C003341</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24.26506128832253</v>
+        <v>41.65864806682673</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>H=6.0 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.5 | Pop=50.9 | PopScore=3.9</t>
+          <t>Prescription=41.1 | Competition=0.0 | Population=89.1 | Road=50.0</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5.984602491423172</v>
+        <v>14.39213214123901</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>22.26651592558771</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9974337485705287</v>
+        <v>41.12037754639718</v>
       </c>
       <c r="J43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>3.948704310206379</v>
+        <v>89.06606370235086</v>
       </c>
       <c r="L43" t="n">
-        <v>50.86811828613281</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5.729209818875439</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>5.984602491423172</v>
+        <v>3.876821639169793</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4.528969473397168</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.200240345478271</v>
+      </c>
+      <c r="T43" t="n">
+        <v>47.27054977416992</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C001844</t>
+          <t>C011052</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24.16957077621892</v>
+        <v>41.31074579714926</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=3.0 | Pop=53.1 | PopScore=4.0</t>
+          <t>Prescription=43.5 | Competition=0.0 | Population=84.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5.899323622863868</v>
+        <v>15.22922696349521</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>21.08151883365405</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9832206038106447</v>
+        <v>43.51207703855773</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>3.990867156703372</v>
+        <v>84.32607533461621</v>
       </c>
       <c r="L44" t="n">
-        <v>53.10178375244141</v>
-      </c>
-      <c r="M44" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.062439935715313</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.67050187258779</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3.458027088468519</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.604412847246794</v>
+      </c>
+      <c r="T44" t="n">
+        <v>38.27161026000977</v>
+      </c>
+      <c r="U44" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N44" t="n">
-        <v>3</v>
-      </c>
-      <c r="O44" t="n">
-        <v>5.899323622863868</v>
+      <c r="V44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C004637</t>
+          <t>C009739</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>24.06804466045589</v>
+        <v>41.06559688268784</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>H=5.3 | C=2.8 | D=0.0 | P=-0.0 | A=1.8 | R=2.0 | Pop=11.5 | PopScore=2.5</t>
+          <t>Prescription=36.6 | Competition=0.0 | Population=83.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5.260475422682626</v>
+        <v>12.81076351994144</v>
       </c>
       <c r="F45" t="n">
-        <v>2.799794475853701</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>20.7548333627464</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I45" t="n">
-        <v>1.810010729065005</v>
+        <v>36.60218148554698</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>2.522167930158913</v>
+        <v>83.01933345098558</v>
       </c>
       <c r="L45" t="n">
-        <v>11.45557022094727</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M45" t="n">
+        <v>5.099699712694632</v>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>8.060269898536326</v>
+        <v>3.613622686501845</v>
+      </c>
+      <c r="P45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>5.099699712694632</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>36.10021209716797</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C003004</t>
+          <t>C009728</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.0373812770499</v>
+        <v>40.74274441212144</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>H=5.0 | C=0.0 | D=0.0 | P=-0.0 | A=0.8 | R=2.0 | Pop=94.7 | PopScore=4.6</t>
+          <t>Prescription=27.7 | Competition=0.0 | Population=94.2 | Road=75.0</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5.035189989905803</v>
+        <v>9.697990982384914</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>23.54475342973653</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8391983316509672</v>
+        <v>27.7085456639569</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>4.561027154691065</v>
+        <v>94.17901371894611</v>
       </c>
       <c r="L46" t="n">
-        <v>94.68170928955078</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.860569414898508</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>5.035189989905803</v>
+        <v>4.099375487856459</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3.860569414898508</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>59.30261611938477</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C002290</t>
+          <t>C000343</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.85058866755243</v>
+        <v>40.39411103454712</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.4 | D=3.3 | P=-0.0 | A=2.4 | R=3.0 | Pop=53.8 | PopScore=4.0</t>
+          <t>Prescription=34.1 | Competition=0.0 | Population=93.8 | Road=50.0</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>11.94543289494654</v>
       </c>
       <c r="F47" t="n">
-        <v>2.382385358840881</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>3.265083722163237</v>
+        <v>23.44867813960058</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>2.426670314028578</v>
+        <v>34.12980827127583</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>4.004327824713779</v>
+        <v>93.79471255840234</v>
       </c>
       <c r="L47" t="n">
-        <v>53.83495330810547</v>
-      </c>
-      <c r="M47" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.755229507401785</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4.08264782534144</v>
+      </c>
+      <c r="P47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.827951706315079</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.927277801086707</v>
+      </c>
+      <c r="T47" t="n">
+        <v>58.30228424072266</v>
+      </c>
+      <c r="U47" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v>3</v>
-      </c>
-      <c r="O47" t="n">
-        <v>5.647469081004117</v>
+      <c r="V47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C011052</t>
+          <t>C009010</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>23.68187370117195</v>
+        <v>40.20483443779532</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3051,713 +4052,986 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.5 | D=2.6 | P=-0.0 | A=2.5 | R=3.0 | Pop=38.3 | PopScore=3.7</t>
+          <t>Prescription=69.3 | Competition=35.6 | Population=86.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>24.25788075962127</v>
       </c>
       <c r="F48" t="n">
-        <v>3.458027088468519</v>
+        <v>10.6792853241599</v>
       </c>
       <c r="G48" t="n">
-        <v>2.604412847246794</v>
+        <v>21.62623900233395</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>2.45488211977957</v>
+        <v>69.30823074177506</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>35.59761774719968</v>
       </c>
       <c r="K48" t="n">
-        <v>3.67050187258779</v>
+        <v>86.50495600933581</v>
       </c>
       <c r="L48" t="n">
-        <v>38.27161026000977</v>
-      </c>
-      <c r="M48" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M48" t="n">
+        <v>9.656560075272292</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.872300050025061</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.765343065717771</v>
+      </c>
+      <c r="P48" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5.872794764559936</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2.821195878400136</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.9625694323122199</v>
+      </c>
+      <c r="T48" t="n">
+        <v>42.17851638793945</v>
+      </c>
+      <c r="U48" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N48" t="n">
-        <v>3</v>
-      </c>
-      <c r="O48" t="n">
-        <v>6.062439935715313</v>
+      <c r="V48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C003341</t>
+          <t>C001486</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23.52437939709079</v>
+        <v>39.57920744410765</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>H=4.5 | C=0.0 | D=1.2 | P=-0.0 | A=1.4 | R=3.0 | Pop=47.3 | PopScore=3.9</t>
+          <t>Prescription=35.6 | Competition=0.0 | Population=88.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.528969473397168</v>
+        <v>12.46650123337507</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1.200240345478271</v>
+        <v>22.11270621073258</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
-        <v>1.35494841830533</v>
+        <v>35.61857495250022</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>3.876821639169793</v>
+        <v>88.4508248429303</v>
       </c>
       <c r="L49" t="n">
-        <v>47.27054977416992</v>
-      </c>
-      <c r="M49" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.962656024302349</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.85004183972305</v>
+      </c>
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.740583577744701</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.222072446557649</v>
+      </c>
+      <c r="T49" t="n">
+        <v>45.99502944946289</v>
+      </c>
+      <c r="U49" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N49" t="n">
-        <v>3</v>
-      </c>
-      <c r="O49" t="n">
-        <v>5.729209818875439</v>
+      <c r="V49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C002755</t>
+          <t>C013790</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.50898397344857</v>
+        <v>39.48971452117198</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.2 | D=1.9 | P=-0.0 | A=2.7 | R=3.5 | Pop=17.4 | PopScore=2.9</t>
+          <t>Prescription=30.9 | Competition=0.0 | Population=94.8 | Road=50.0</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>10.80155672942695</v>
       </c>
       <c r="F50" t="n">
-        <v>5.174152023412173</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.899070870149719</v>
+        <v>23.68815779174503</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>2.674252776212251</v>
+        <v>30.86159065550558</v>
       </c>
       <c r="J50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>2.915037636234521</v>
+        <v>94.75263116698014</v>
       </c>
       <c r="L50" t="n">
-        <v>17.44950675964355</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.299876089662234</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>7.073222893561892</v>
+        <v>4.124343611996036</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4.299876089662234</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>60.82721328735352</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C003442</t>
+          <t>C001365</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>23.24090432065266</v>
+        <v>39.34963984517759</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.8 | D=1.6 | P=-0.0 | A=2.1 | R=2.0 | Pop=52.9 | PopScore=4.0</t>
+          <t>Prescription=59.8 | Competition=15.4 | Population=92.2 | Road=0.0</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>20.92019089591231</v>
       </c>
       <c r="F51" t="n">
-        <v>3.825468315911813</v>
+        <v>4.619880959531804</v>
       </c>
       <c r="G51" t="n">
-        <v>1.610903291683232</v>
+        <v>23.04932990879709</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>2.080607751145554</v>
+        <v>59.77197398832087</v>
       </c>
       <c r="J51" t="n">
+        <v>15.39960319843935</v>
+      </c>
+      <c r="K51" t="n">
+        <v>92.19731963518835</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>8.327894846808359</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.242562953267371</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4.013117330857386</v>
+      </c>
+      <c r="P51" t="n">
         <v>2</v>
       </c>
-      <c r="K51" t="n">
-        <v>3.986700110116005</v>
-      </c>
-      <c r="L51" t="n">
-        <v>52.87680816650391</v>
-      </c>
-      <c r="M51" t="inlineStr">
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.575962790427726</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5.751932056380634</v>
+      </c>
+      <c r="T51" t="n">
+        <v>54.31904983520508</v>
+      </c>
+      <c r="U51" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="N51" t="n">
+      <c r="V51" t="n">
         <v>2</v>
-      </c>
-      <c r="O51" t="n">
-        <v>5.436371607595046</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C009010</t>
+          <t>C000822</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>22.53229744459433</v>
+        <v>39.24357790950415</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>H=5.9 | C=2.8 | D=1.0 | P=-2.9 | A=2.4 | R=3.0 | Pop=42.2 | PopScore=3.8</t>
+          <t>Prescription=21.5 | Competition=0.0 | Population=96.9 | Road=75.0</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5.872794764559936</v>
+        <v>7.515472369994811</v>
       </c>
       <c r="F52" t="n">
-        <v>2.821195878400136</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9625694323122199</v>
+        <v>24.22810553950935</v>
       </c>
       <c r="H52" t="n">
-        <v>2.872300050025061</v>
+        <v>7.5</v>
       </c>
       <c r="I52" t="n">
-        <v>2.400482469716144</v>
+        <v>21.47277819998518</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>3.765343065717771</v>
+        <v>96.91242215803739</v>
       </c>
       <c r="L52" t="n">
-        <v>42.17851638793945</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.991753943968063</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>9.656560075272292</v>
+        <v>4.218353879230892</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.991753943968063</v>
+      </c>
+      <c r="T52" t="n">
+        <v>66.92158508300781</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C002094</t>
+          <t>C004503</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.37678567494557</v>
+        <v>39.02728200866012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>H=5.6 | C=0.0 | D=0.0 | P=-0.0 | A=0.9 | R=3.0 | Pop=36.3 | PopScore=3.6</t>
+          <t>Prescription=28.4 | Competition=0.0 | Population=96.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.564298190349531</v>
+        <v>9.953769935313051</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>24.07351207334706</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9273830317249219</v>
+        <v>28.43934267232301</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>3.618483663691339</v>
+        <v>96.29404829338826</v>
       </c>
       <c r="L53" t="n">
-        <v>36.2809944152832</v>
-      </c>
-      <c r="M53" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.962389720201196</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4.191437620895052</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2.530708245784684</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1.431681474416512</v>
+      </c>
+      <c r="T53" t="n">
+        <v>65.11777496337891</v>
+      </c>
+      <c r="U53" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N53" t="n">
-        <v>3</v>
-      </c>
-      <c r="O53" t="n">
-        <v>5.564298190349531</v>
+      <c r="V53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C000343</t>
+          <t>C001388</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.2490314377594</v>
+        <v>39.00021125014148</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.8 | D=1.9 | P=-0.0 | A=1.9 | R=3.0 | Pop=58.3 | PopScore=4.1</t>
+          <t>Prescription=26.5 | Competition=0.0 | Population=98.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>9.276091828277785</v>
       </c>
       <c r="F54" t="n">
-        <v>2.827951706315079</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1.927277801086707</v>
+        <v>24.72411942186369</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I54" t="n">
-        <v>1.906289469315047</v>
+        <v>26.5031195093651</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>4.08264782534144</v>
+        <v>98.89647768745476</v>
       </c>
       <c r="L54" t="n">
-        <v>58.30228424072266</v>
-      </c>
-      <c r="M54" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.692620096995865</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>4.304714824017505</v>
+      </c>
+      <c r="P54" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3.692620096995865</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>73.048095703125</v>
+      </c>
+      <c r="U54" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N54" t="n">
-        <v>3</v>
-      </c>
-      <c r="O54" t="n">
-        <v>4.755229507401785</v>
+      <c r="V54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C007721</t>
+          <t>C005441</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>22.1539080011263</v>
+        <v>38.79071834580276</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=26.6 | PopScore=3.3</t>
+          <t>Prescription=44.8 | Competition=10.4 | Population=85.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.948850750096658</v>
+        <v>15.66799149311814</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>3.116706617383964</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>21.23943347006858</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9914751250161097</v>
+        <v>44.76568998033756</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>10.38902205794655</v>
       </c>
       <c r="K55" t="n">
-        <v>3.319019662810459</v>
+        <v>84.95773388027432</v>
       </c>
       <c r="L55" t="n">
-        <v>26.63324737548828</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M55" t="n">
+        <v>6.237103010416181</v>
       </c>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>0.8382692569111241</v>
       </c>
       <c r="O55" t="n">
-        <v>5.948850750096658</v>
+        <v>3.697996379660176</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6.237103010416181</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>39.3663444519043</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C007183</t>
+          <t>C002569</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22.11685937659464</v>
+        <v>38.64984066377865</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>H=8.8 | C=4.4 | D=0.0 | P=-5.4 | A=2.9 | R=2.0 | Pop=43.0 | PopScore=3.8</t>
+          <t>Prescription=27.5 | Competition=0.0 | Population=96.1 | Road=50.0</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>8.807818466339167</v>
+        <v>9.615723239804026</v>
       </c>
       <c r="F56" t="n">
-        <v>4.398655339369084</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>24.03411742397462</v>
       </c>
       <c r="H56" t="n">
-        <v>5.379780117041485</v>
+        <v>5</v>
       </c>
       <c r="I56" t="n">
-        <v>2.934188190846223</v>
+        <v>27.47349497086865</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>3.783277765739326</v>
+        <v>96.13646969589848</v>
       </c>
       <c r="L56" t="n">
-        <v>42.95989608764648</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.827820329916125</v>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>13.20647380570825</v>
+        <v>4.184578621055787</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>3.827820329916125</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>64.66582489013672</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C001396</t>
+          <t>C002822</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>22.04791017006726</v>
+        <v>38.53216135303814</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.1 | D=0.0 | P=-0.0 | A=1.4 | R=3.5 | Pop=83.5 | PopScore=4.4</t>
+          <t>Prescription=69.6 | Competition=41.8 | Population=76.9 | Road=75.0</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>24.35476603309433</v>
       </c>
       <c r="F57" t="n">
-        <v>4.125158569732197</v>
+        <v>12.54310385566123</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>19.22049917560504</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I57" t="n">
-        <v>1.375052856577399</v>
+        <v>69.58504580884095</v>
       </c>
       <c r="J57" t="n">
+        <v>41.81034618553743</v>
+      </c>
+      <c r="K57" t="n">
+        <v>76.88199670242017</v>
+      </c>
+      <c r="L57" t="n">
+        <v>75</v>
+      </c>
+      <c r="M57" t="n">
+        <v>9.695128096649457</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3.373592589625787</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3.346479861000707</v>
+      </c>
+      <c r="P57" t="n">
         <v>3.5</v>
       </c>
-      <c r="K57" t="n">
-        <v>4.436695914981709</v>
-      </c>
-      <c r="L57" t="n">
-        <v>83.49530029296875</v>
-      </c>
-      <c r="M57" t="inlineStr">
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>5.961471408471607</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3.73365668817785</v>
+      </c>
+      <c r="T57" t="n">
+        <v>27.4025764465332</v>
+      </c>
+      <c r="U57" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="N57" t="n">
+      <c r="V57" t="n">
         <v>4</v>
-      </c>
-      <c r="O57" t="n">
-        <v>4.125158569732197</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C012690</t>
+          <t>C002329</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.94506651243444</v>
+        <v>38.09134938011756</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>H=5.9 | C=0.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=25.6 | PopScore=3.3</t>
+          <t>Prescription=35.9 | Competition=0.0 | Population=82.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5.900928961236548</v>
+        <v>12.54873600165587</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>20.5426133784617</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9834881602060913</v>
+        <v>35.85353143330249</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>3.281619924646912</v>
+        <v>82.17045351384678</v>
       </c>
       <c r="L58" t="n">
-        <v>25.61885833740234</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4.995391982898593</v>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>5.900928961236548</v>
+        <v>3.576673078844827</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>4.995391982898593</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>34.75439071655273</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C005441</t>
+          <t>C003299</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>21.56129082276006</v>
+        <v>37.81954518677505</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.2 | D=0.0 | P=-0.8 | A=2.1 | R=3.0 | Pop=39.4 | PopScore=3.7</t>
+          <t>Prescription=25.3 | Competition=0.0 | Population=95.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>8.839797733457514</v>
       </c>
       <c r="F59" t="n">
-        <v>6.237103010416181</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>23.97974745331754</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8382692569111241</v>
+        <v>5</v>
       </c>
       <c r="I59" t="n">
-        <v>2.079034336805393</v>
+        <v>25.25656495273575</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>3.697996379660176</v>
+        <v>95.91898981327014</v>
       </c>
       <c r="L59" t="n">
-        <v>39.3663444519043</v>
-      </c>
-      <c r="M59" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.518940451240022</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>4.175112269001931</v>
+      </c>
+      <c r="P59" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3.518940451240022</v>
+      </c>
+      <c r="T59" t="n">
+        <v>64.04714202880859</v>
+      </c>
+      <c r="U59" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N59" t="n">
-        <v>3</v>
-      </c>
-      <c r="O59" t="n">
-        <v>6.237103010416181</v>
+      <c r="V59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C009739</t>
+          <t>C011102</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>21.56025747531795</v>
+        <v>37.80840844228237</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.1 | D=0.0 | P=-0.0 | A=1.7 | R=3.5 | Pop=36.1 | PopScore=3.6</t>
+          <t>Prescription=27.1 | Competition=0.0 | Population=93.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>9.476269417403149</v>
       </c>
       <c r="F60" t="n">
-        <v>5.099699712694632</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>23.33213902487922</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I60" t="n">
-        <v>1.699899904231544</v>
+        <v>27.07505547829471</v>
       </c>
       <c r="J60" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>3.613622686501845</v>
+        <v>93.32855609951687</v>
       </c>
       <c r="L60" t="n">
-        <v>36.10021209716797</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.772306650585076</v>
       </c>
       <c r="N60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>5.099699712694632</v>
+        <v>4.062357207659206</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>3.772306650585076</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>57.11112976074219</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C013807</t>
+          <t>C003004</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>21.48117995204782</v>
+        <v>37.64871107569115</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3766,218 +5040,302 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>H=4.2 | C=0.0 | D=0.0 | P=-0.0 | A=0.7 | R=2.0 | Pop=69.7 | PopScore=4.3</t>
+          <t>Prescription=36.1 | Competition=0.0 | Population=100.0 | Road=0.0</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4.216725512315009</v>
+        <v>12.64871107569115</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7027875853858349</v>
+        <v>36.13917450197472</v>
       </c>
       <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>100</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>5.035189989905803</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>4.561027154691065</v>
+      </c>
+      <c r="P61" t="n">
         <v>2</v>
       </c>
-      <c r="K61" t="n">
-        <v>4.259150056293074</v>
-      </c>
-      <c r="L61" t="n">
-        <v>69.74982452392578</v>
-      </c>
-      <c r="M61" t="inlineStr">
+      <c r="Q61" t="n">
+        <v>5.035189989905803</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>94.68170928955078</v>
+      </c>
+      <c r="U61" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="N61" t="n">
+      <c r="V61" t="n">
         <v>2</v>
-      </c>
-      <c r="O61" t="n">
-        <v>4.216725512315009</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C012566</t>
+          <t>C008633</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>21.44384181314243</v>
+        <v>37.5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.1 | D=0.0 | P=-0.0 | A=1.4 | R=2.0 | Pop=71.8 | PopScore=4.3</t>
+          <t>Prescription=100.0 | Competition=100.0 | Population=100.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F62" t="n">
-        <v>4.12119091552514</v>
+        <v>30</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I62" t="n">
-        <v>1.373730305175047</v>
+        <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>4.288028983858216</v>
+        <v>100</v>
       </c>
       <c r="L62" t="n">
-        <v>71.82279205322266</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M62" t="n">
+        <v>22.19732182271963</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>10.83004941088425</v>
       </c>
       <c r="O62" t="n">
-        <v>4.12119091552514</v>
+        <v>4.420808983391451</v>
+      </c>
+      <c r="P62" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>11.49874588567654</v>
+      </c>
+      <c r="R62" t="n">
+        <v>5.665547634402373</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5.033028302640711</v>
+      </c>
+      <c r="T62" t="n">
+        <v>82.16353607177734</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C013790</t>
+          <t>C004625</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.41611221830132</v>
+        <v>37.41435096544772</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.3 | D=0.0 | P=-0.0 | A=1.4 | R=3.0 | Pop=60.8 | PopScore=4.1</t>
+          <t>Prescription=35.1 | Competition=0.0 | Population=80.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>12.29192908381521</v>
       </c>
       <c r="F63" t="n">
-        <v>4.299876089662234</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>20.1224218816325</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I63" t="n">
-        <v>1.433292029887411</v>
+        <v>35.11979738232918</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>4.124343611996036</v>
+        <v>80.48968752653002</v>
       </c>
       <c r="L63" t="n">
-        <v>60.82721328735352</v>
-      </c>
-      <c r="M63" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4.893162466048064</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.503513564669079</v>
+      </c>
+      <c r="P63" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2.952950685405072</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1.940211780642993</v>
+      </c>
+      <c r="T63" t="n">
+        <v>32.23200988769531</v>
+      </c>
+      <c r="U63" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N63" t="n">
-        <v>3</v>
-      </c>
-      <c r="O63" t="n">
-        <v>4.299876089662234</v>
+      <c r="V63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C002499</t>
+          <t>C001955</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>21.29013829482704</v>
+        <v>36.87377463890948</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>H=0.0 | C=5.0 | D=0.0 | P=-0.0 | A=1.7 | R=2.0 | Pop=36.2 | PopScore=3.6</t>
+          <t>Prescription=13.7 | Competition=0.0 | Population=98.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4.808251466188355</v>
       </c>
       <c r="F64" t="n">
-        <v>5.035759858469539</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>24.56552317272112</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I64" t="n">
-        <v>1.678586619489846</v>
+        <v>13.73786133196673</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>3.616919971979658</v>
+        <v>98.26209269088449</v>
       </c>
       <c r="L64" t="n">
-        <v>36.22274398803711</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.914065354692957</v>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>5.035759858469539</v>
+        <v>4.277101641397385</v>
+      </c>
+      <c r="P64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.135653399755299</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.7784119549376575</v>
+      </c>
+      <c r="T64" t="n">
+        <v>71.03136444091797</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C003285</t>
+          <t>C005411</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21.22307224184321</v>
+        <v>36.68514102468049</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3986,108 +5344,150 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.6 | D=0.0 | P=-0.0 | A=1.5 | R=2.0 | Pop=46.7 | PopScore=3.9</t>
+          <t>Prescription=100.0 | Competition=100.0 | Population=96.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F65" t="n">
-        <v>4.635489365046799</v>
+        <v>30</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>24.18514102468049</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I65" t="n">
-        <v>1.545163121682266</v>
+        <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K65" t="n">
-        <v>3.865859066527126</v>
+        <v>96.74056409872196</v>
       </c>
       <c r="L65" t="n">
-        <v>46.74427032470703</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M65" t="n">
+        <v>16.63706737083361</v>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>15.15448157485586</v>
       </c>
       <c r="O65" t="n">
-        <v>4.635489365046799</v>
+        <v>4.210873330349262</v>
+      </c>
+      <c r="P65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>12.0096763342439</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2.993790673287788</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1.633600363301921</v>
+      </c>
+      <c r="T65" t="n">
+        <v>66.41539001464844</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C002329</t>
+          <t>C010347</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>21.10405973537998</v>
+        <v>36.49877042085333</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>H=5.0 | C=0.0 | D=0.0 | P=-0.0 | A=0.8 | R=3.0 | Pop=34.8 | PopScore=3.6</t>
+          <t>Prescription=35.0 | Competition=0.0 | Population=97.1 | Road=0.0</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4.995391982898593</v>
+        <v>12.23578083824733</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>24.262989582606</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8325653304830989</v>
+        <v>34.95937382356381</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>3.576673078844827</v>
+        <v>97.05195833042401</v>
       </c>
       <c r="L66" t="n">
-        <v>34.75439071655273</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>4.870811012026991</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>4.995391982898593</v>
+        <v>4.224427537704934</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>4.262233086451984</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.608577925575007</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>67.33537292480469</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C004503</t>
+          <t>C013107</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>20.95503331833453</v>
+        <v>36.07606685022124</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -4096,163 +5496,226 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.5 | D=1.4 | P=-0.0 | A=1.6 | R=3.0 | Pop=65.1 | PopScore=4.2</t>
+          <t>Prescription=49.6 | Competition=12.6 | Population=69.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>17.37191881644968</v>
       </c>
       <c r="F67" t="n">
-        <v>2.530708245784684</v>
+        <v>3.774805311591686</v>
       </c>
       <c r="G67" t="n">
-        <v>1.431681474416512</v>
+        <v>17.47895334536324</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
-        <v>1.559410152469817</v>
+        <v>49.6340537612848</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>12.58268437197229</v>
       </c>
       <c r="K67" t="n">
-        <v>4.191437620895052</v>
+        <v>69.91581338145298</v>
       </c>
       <c r="L67" t="n">
-        <v>65.11777496337891</v>
-      </c>
-      <c r="M67" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M67" t="n">
+        <v>6.915401198320448</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1.015271448997697</v>
+      </c>
+      <c r="O67" t="n">
+        <v>3.043259429800305</v>
+      </c>
+      <c r="P67" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6.915401198320448</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>19.9734935760498</v>
+      </c>
+      <c r="U67" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N67" t="n">
-        <v>3</v>
-      </c>
-      <c r="O67" t="n">
-        <v>3.962389720201196</v>
+      <c r="V67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C000457</t>
+          <t>C000355</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20.81542103854036</v>
+        <v>36.07553761850385</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.4 | D=0.0 | P=-0.0 | A=1.5 | R=2.0 | Pop=48.8 | PopScore=3.9</t>
+          <t>Prescription=20.8 | Competition=0.0 | Population=95.1 | Road=50.0</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>7.290425038973381</v>
       </c>
       <c r="F68" t="n">
-        <v>4.373189754483641</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>23.78511257953047</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I68" t="n">
-        <v>1.457729918161214</v>
+        <v>20.82978582563823</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>3.90775617925232</v>
+        <v>95.14045031812188</v>
       </c>
       <c r="L68" t="n">
-        <v>48.78711318969727</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2.902167261053638</v>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.373189754483641</v>
+        <v>4.14122440378959</v>
+      </c>
+      <c r="P68" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2.902167261053638</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>61.87976455688477</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C004625</t>
+          <t>C002215</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>20.79230790464902</v>
+        <v>35.8657147424714</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.0 | D=1.9 | P=-0.0 | A=2.0 | R=3.0 | Pop=32.2 | PopScore=3.5</t>
+          <t>Prescription=26.0 | Competition=0.0 | Population=87.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>9.117341635512179</v>
       </c>
       <c r="F69" t="n">
-        <v>2.952950685405072</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1.940211780642993</v>
+        <v>21.74837310695922</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I69" t="n">
-        <v>1.95442278545652</v>
+        <v>26.0495475300348</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>3.503513564669079</v>
+        <v>86.99349242783687</v>
       </c>
       <c r="L69" t="n">
-        <v>32.23200988769531</v>
-      </c>
-      <c r="M69" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.629424932150556</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>3.78660782672817</v>
+      </c>
+      <c r="P69" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>3.629424932150556</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>43.10652923583984</v>
+      </c>
+      <c r="U69" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N69" t="n">
-        <v>3</v>
-      </c>
-      <c r="O69" t="n">
-        <v>4.893162466048064</v>
+      <c r="V69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C001388</t>
+          <t>C000129</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>20.72247200261078</v>
+        <v>35.77118919006131</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -4261,53 +5724,74 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.7 | D=0.0 | P=-0.0 | A=1.2 | R=3.0 | Pop=73.0 | PopScore=4.3</t>
+          <t>Prescription=18.2 | Competition=0.0 | Population=87.6 | Road=75.0</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>6.377408764538267</v>
       </c>
       <c r="F70" t="n">
-        <v>3.692620096995865</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>21.89378042552304</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I70" t="n">
-        <v>1.230873365665288</v>
+        <v>18.22116789868076</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>4.304714824017505</v>
+        <v>87.57512170209215</v>
       </c>
       <c r="L70" t="n">
-        <v>73.048095703125</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2.538714386041582</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.692620096995865</v>
+        <v>3.811924685503281</v>
+      </c>
+      <c r="P70" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.5822289040692653</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1.956485481972317</v>
+      </c>
+      <c r="T70" t="n">
+        <v>44.23742294311523</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C002569</t>
+          <t>C008510</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>20.63697053399682</v>
+        <v>35.58240768338413</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4316,53 +5800,74 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.8 | D=0.0 | P=-0.0 | A=1.3 | R=3.0 | Pop=64.7 | PopScore=4.2</t>
+          <t>Prescription=17.0 | Competition=0.0 | Population=98.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>5.953172695740633</v>
       </c>
       <c r="F71" t="n">
-        <v>3.827820329916125</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>24.6292349876435</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I71" t="n">
-        <v>1.275940109972042</v>
+        <v>17.00906484497324</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>4.184578621055787</v>
+        <v>98.516939950574</v>
       </c>
       <c r="L71" t="n">
-        <v>64.66582489013672</v>
-      </c>
-      <c r="M71" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2.369834790786054</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>4.288194501348502</v>
+      </c>
+      <c r="P71" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2.369834790786054</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>71.83484649658203</v>
+      </c>
+      <c r="U71" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N71" t="n">
-        <v>3</v>
-      </c>
-      <c r="O71" t="n">
-        <v>3.827820329916125</v>
+      <c r="V71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C009728</t>
+          <t>C011062</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>20.49795094052968</v>
+        <v>35.25752828262118</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4371,163 +5876,226 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.9 | D=0.0 | P=-0.0 | A=1.3 | R=3.5 | Pop=59.3 | PopScore=4.1</t>
+          <t>Prescription=8.8 | Competition=0.0 | Population=98.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>3.09181960209912</v>
       </c>
       <c r="F72" t="n">
-        <v>3.860569414898508</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>24.66570868052206</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I72" t="n">
-        <v>1.286856471632836</v>
+        <v>8.833770291711772</v>
       </c>
       <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>98.66283472208823</v>
+      </c>
+      <c r="L72" t="n">
+        <v>75</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.230789368017355</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>4.29454493364265</v>
+      </c>
+      <c r="P72" t="n">
         <v>3.5</v>
       </c>
-      <c r="K72" t="n">
-        <v>4.099375487856459</v>
-      </c>
-      <c r="L72" t="n">
-        <v>59.30261611938477</v>
-      </c>
-      <c r="M72" t="inlineStr">
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.8709706238756858</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.3598187441416697</v>
+      </c>
+      <c r="T72" t="n">
+        <v>72.29885101318359</v>
+      </c>
+      <c r="U72" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="N72" t="n">
+      <c r="V72" t="n">
         <v>4</v>
-      </c>
-      <c r="O72" t="n">
-        <v>3.860569414898508</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C013107</t>
+          <t>C013807</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.44527971232607</v>
+        <v>35.05509558280933</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>H=0.0 | C=6.9 | D=0.0 | P=-1.0 | A=2.3 | R=3.0 | Pop=20.0 | PopScore=3.0</t>
+          <t>Prescription=30.3 | Competition=0.0 | Population=97.8 | Road=0.0</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>10.59267729672423</v>
       </c>
       <c r="F73" t="n">
-        <v>6.915401198320448</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>24.4624182860851</v>
       </c>
       <c r="H73" t="n">
-        <v>1.015271448997697</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>2.305133732773483</v>
+        <v>30.26479227635494</v>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>3.043259429800305</v>
+        <v>97.8496731443404</v>
       </c>
       <c r="L73" t="n">
-        <v>19.9734935760498</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>4.216725512315009</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>6.915401198320448</v>
+        <v>4.259150056293074</v>
+      </c>
+      <c r="P73" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>4.216725512315009</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>69.74982452392578</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C011102</t>
+          <t>C005052</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.15742847916727</v>
+        <v>35</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.8 | D=0.0 | P=-0.0 | A=1.3 | R=3.0 | Pop=57.1 | PopScore=4.1</t>
+          <t>Prescription=100.0 | Competition=100.0 | Population=100.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>3.772306650585076</v>
+        <v>30</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I74" t="n">
-        <v>1.257435550195025</v>
+        <v>100</v>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="K74" t="n">
-        <v>4.062357207659206</v>
+        <v>100</v>
       </c>
       <c r="L74" t="n">
-        <v>57.11112976074219</v>
-      </c>
-      <c r="M74" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M74" t="n">
+        <v>30.83965299999198</v>
+      </c>
+      <c r="N74" t="n">
+        <v>17.90302066526227</v>
+      </c>
+      <c r="O74" t="n">
+        <v>4.419745706089935</v>
+      </c>
+      <c r="P74" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2.894869422757747</v>
+      </c>
+      <c r="S74" t="n">
+        <v>27.94478357723423</v>
+      </c>
+      <c r="T74" t="n">
+        <v>82.07515716552734</v>
+      </c>
+      <c r="U74" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N74" t="n">
-        <v>3</v>
-      </c>
-      <c r="O74" t="n">
-        <v>3.772306650585076</v>
+      <c r="V74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C003299</t>
+          <t>C009233</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>20.03916473204784</v>
+        <v>34.93626625421695</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4536,108 +6104,150 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>H=0.0 | C=0.0 | D=3.5 | P=-0.0 | A=1.8 | R=3.0 | Pop=64.0 | PopScore=4.2</t>
+          <t>Prescription=7.0 | Competition=0.0 | Population=99.9 | Road=75.0</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>2.453654063676462</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>3.518940451240022</v>
+        <v>24.98261219054048</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I75" t="n">
-        <v>1.759470225620011</v>
+        <v>7.010440181932749</v>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>4.175112269001931</v>
+        <v>99.93044876216193</v>
       </c>
       <c r="L75" t="n">
-        <v>64.04714202880859</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9767488802759563</v>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>3.518940451240022</v>
+        <v>4.349720983154575</v>
+      </c>
+      <c r="P75" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.9767488802759563</v>
+      </c>
+      <c r="T75" t="n">
+        <v>76.45684814453125</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C007629</t>
+          <t>C007183</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>19.79242665442377</v>
+        <v>34.90257162460892</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.5 | P=-0.0 | A=1.2 | R=2.0 | Pop=66.7 | PopScore=4.2</t>
+          <t>Prescription=94.8 | Competition=66.7 | Population=86.9 | Road=0.0</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>33.17548530084602</v>
       </c>
       <c r="F76" t="n">
-        <v>2.936381335558953</v>
+        <v>20.00216058577415</v>
       </c>
       <c r="G76" t="n">
-        <v>0.4764708462320955</v>
+        <v>21.72924690953706</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1.217029201635699</v>
+        <v>94.78710085956007</v>
       </c>
       <c r="J76" t="n">
+        <v>66.67386861924717</v>
+      </c>
+      <c r="K76" t="n">
+        <v>86.91698763814823</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>13.20647380570825</v>
+      </c>
+      <c r="N76" t="n">
+        <v>5.379780117041485</v>
+      </c>
+      <c r="O76" t="n">
+        <v>3.783277765739326</v>
+      </c>
+      <c r="P76" t="n">
         <v>2</v>
       </c>
-      <c r="K76" t="n">
-        <v>4.215006456892702</v>
-      </c>
-      <c r="L76" t="n">
-        <v>66.69460296630859</v>
-      </c>
-      <c r="M76" t="inlineStr">
+      <c r="Q76" t="n">
+        <v>8.807818466339167</v>
+      </c>
+      <c r="R76" t="n">
+        <v>4.398655339369084</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>42.95989608764648</v>
+      </c>
+      <c r="U76" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="N76" t="n">
+      <c r="V76" t="n">
         <v>2</v>
-      </c>
-      <c r="O76" t="n">
-        <v>3.412852181791048</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C003503</t>
+          <t>C000609</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>19.59134245509013</v>
+        <v>34.82037533857539</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4646,53 +6256,74 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>H=2.9 | C=0.0 | D=0.0 | P=-0.0 | A=0.5 | R=2.0 | Pop=90.5 | PopScore=4.5</t>
+          <t>Prescription=19.3 | Competition=0.0 | Population=82.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2.897321255307693</v>
+        <v>6.746868980812702</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>20.57350635776269</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4828868758846154</v>
+        <v>19.27676851660772</v>
       </c>
       <c r="J77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>4.516137085628762</v>
+        <v>82.29402543105076</v>
       </c>
       <c r="L77" t="n">
-        <v>90.48152923583984</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2.685788848531968</v>
       </c>
       <c r="N77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>2.897321255307693</v>
+        <v>3.582051853461061</v>
+      </c>
+      <c r="P77" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2.685788848531968</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>34.94722366333008</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C007523</t>
+          <t>C004637</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>19.56230822293649</v>
+        <v>34.73396589422817</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4701,108 +6332,150 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>H=7.1 | C=0.0 | D=0.0 | P=-0.0 | A=1.2 | R=2.0 | Pop=4.3 | PopScore=1.7</t>
+          <t>Prescription=57.9 | Competition=0.0 | Population=57.9 | Road=0.0</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>7.11693830062474</v>
+        <v>20.24790034597755</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>14.48606554825062</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>1.186156383437457</v>
+        <v>57.85114384565014</v>
       </c>
       <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>57.94426219300248</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>8.060269898536326</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>2.522167930158913</v>
+      </c>
+      <c r="P78" t="n">
         <v>2</v>
       </c>
-      <c r="K78" t="n">
-        <v>1.669938661114421</v>
-      </c>
-      <c r="L78" t="n">
-        <v>4.31184196472168</v>
-      </c>
-      <c r="M78" t="inlineStr">
+      <c r="Q78" t="n">
+        <v>5.260475422682626</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2.799794475853701</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>11.45557022094727</v>
+      </c>
+      <c r="U78" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="N78" t="n">
+      <c r="V78" t="n">
         <v>2</v>
-      </c>
-      <c r="O78" t="n">
-        <v>7.11693830062474</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C012535</t>
+          <t>C000068</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>19.18777171328794</v>
+        <v>34.67761350784531</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>H=4.9 | C=0.8 | D=1.7 | P=-0.0 | A=2.0 | R=2.0 | Pop=2.6 | PopScore=1.3</t>
+          <t>Prescription=27.0 | Competition=12.2 | Population=95.6 | Road=50.0</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4.941164250425158</v>
+        <v>9.438623536320801</v>
       </c>
       <c r="F79" t="n">
-        <v>0.839974786229631</v>
+        <v>3.660204967021518</v>
       </c>
       <c r="G79" t="n">
-        <v>1.699858572627701</v>
+        <v>23.89919493854602</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I79" t="n">
-        <v>1.953448256794587</v>
+        <v>26.96749581805943</v>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
+        <v>12.20068322340506</v>
       </c>
       <c r="K79" t="n">
-        <v>1.276810556347832</v>
+        <v>95.5967797541841</v>
       </c>
       <c r="L79" t="n">
-        <v>2.585186719894409</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.757320604777506</v>
       </c>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>0.9844485460177469</v>
       </c>
       <c r="O79" t="n">
-        <v>7.48099760928249</v>
+        <v>4.161087275895718</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.331433635211078</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2.041252395463951</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.3846345741024767</v>
+      </c>
+      <c r="T79" t="n">
+        <v>63.1412239074707</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C013820</t>
+          <t>C005122</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>18.96830414473136</v>
+        <v>34.44192716630756</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4811,53 +6484,74 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.3 | D=0.0 | P=-0.0 | A=1.1 | R=2.0 | Pop=54.4 | PopScore=4.0</t>
+          <t>Prescription=12.7 | Competition=0.0 | Population=100.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>4.441927166307563</v>
       </c>
       <c r="F80" t="n">
-        <v>3.307286388498296</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I80" t="n">
-        <v>1.102428796166099</v>
+        <v>12.69122047516447</v>
       </c>
       <c r="J80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>4.014496162706052</v>
+        <v>100</v>
       </c>
       <c r="L80" t="n">
-        <v>54.39537811279297</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.768239235590285</v>
       </c>
       <c r="N80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3.307286388498296</v>
+        <v>4.385358651340807</v>
+      </c>
+      <c r="P80" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1.768239235590285</v>
+      </c>
+      <c r="T80" t="n">
+        <v>79.26700592041016</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C002955</t>
+          <t>C003964</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>18.70258967594721</v>
+        <v>34.42202263007693</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4866,53 +6560,74 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=64.0 | PopScore=4.2</t>
+          <t>Prescription=19.1 | Competition=0.0 | Population=91.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>6.684446113033752</v>
       </c>
       <c r="F81" t="n">
-        <v>2.940270563016239</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>22.73757651704318</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I81" t="n">
-        <v>0.9800901876720797</v>
+        <v>19.09841746581072</v>
       </c>
       <c r="J81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>4.174679843715841</v>
+        <v>90.95030606817271</v>
       </c>
       <c r="L81" t="n">
-        <v>64.01902008056641</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2.660939597323611</v>
       </c>
       <c r="N81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>2.940270563016239</v>
+        <v>3.958837968101435</v>
+      </c>
+      <c r="P81" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2.660939597323611</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>51.39640426635742</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C000355</t>
+          <t>C002593</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>18.62474664217783</v>
+        <v>34.41899545307659</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4921,108 +6636,150 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0 | Pop=61.9 | PopScore=4.1</t>
+          <t>Prescription=15.3 | Competition=0.0 | Population=96.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>5.351418700948403</v>
       </c>
       <c r="F82" t="n">
-        <v>2.902167261053638</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>24.06757675212818</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9673890870178793</v>
+        <v>15.28976771699544</v>
       </c>
       <c r="J82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>4.14122440378959</v>
+        <v>96.27030700851273</v>
       </c>
       <c r="L82" t="n">
-        <v>61.87976455688477</v>
-      </c>
-      <c r="M82" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2.130288984669355</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>4.190404222503778</v>
+      </c>
+      <c r="P82" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2.130288984669355</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>65.04948425292969</v>
+      </c>
+      <c r="U82" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N82" t="n">
-        <v>3</v>
-      </c>
-      <c r="O82" t="n">
-        <v>2.902167261053638</v>
+      <c r="V82" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C009484</t>
+          <t>C001040</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>18.55584654582344</v>
+        <v>34.38334438379486</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>H=6.3 | C=0.0 | D=0.0 | P=-0.0 | A=1.1 | R=2.0 | Pop=5.5 | PopScore=1.9</t>
+          <t>Prescription=7.9 | Competition=0.0 | Population=96.4 | Road=75.0</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6.319133518128093</v>
+        <v>2.774172752696424</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>24.10917163109844</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I83" t="n">
-        <v>1.053188919688016</v>
+        <v>7.926207864846925</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1.870753539199483</v>
+        <v>96.43668652439378</v>
       </c>
       <c r="L83" t="n">
-        <v>5.493187427520752</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.104340734092007</v>
       </c>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>6.319133518128093</v>
+        <v>4.197646304175175</v>
+      </c>
+      <c r="P83" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1.104340734092007</v>
+      </c>
+      <c r="T83" t="n">
+        <v>65.52955627441406</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C005576</t>
+          <t>C001199</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>18.40808090620157</v>
+        <v>34.16958807606613</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -5031,53 +6788,74 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.6 | D=0.0 | P=-0.0 | A=0.9 | R=2.0 | Pop=74.3 | PopScore=4.3</t>
+          <t>Prescription=7.4 | Competition=0.0 | Population=96.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>2.605156193901499</v>
       </c>
       <c r="F84" t="n">
-        <v>2.579124782857473</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>24.06443188216463</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I84" t="n">
-        <v>0.859708260952491</v>
+        <v>7.443303411147141</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>4.321286838130457</v>
+        <v>96.25772752865852</v>
       </c>
       <c r="L84" t="n">
-        <v>74.28544616699219</v>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.037058741493719</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>2.579124782857473</v>
+        <v>4.189856669399026</v>
+      </c>
+      <c r="P84" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.037058741493719</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>65.01332855224609</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C012055</t>
+          <t>C003443</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>18.36185281806422</v>
+        <v>34.07325493750462</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -5086,53 +6864,74 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=2.0 | Pop=62.2 | PopScore=4.1</t>
+          <t>Prescription=31.4 | Competition=0.0 | Population=92.4 | Road=0.0</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>10.97326245270559</v>
       </c>
       <c r="F85" t="n">
-        <v>2.814533612675373</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>23.09999248479903</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0.9381778708917909</v>
+        <v>31.35217843630168</v>
       </c>
       <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>92.39996993919614</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>4.368228582962812</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>4.021938188669036</v>
+      </c>
+      <c r="P85" t="n">
         <v>2</v>
       </c>
-      <c r="K85" t="n">
-        <v>4.146322601874766</v>
-      </c>
-      <c r="L85" t="n">
-        <v>62.20115661621094</v>
-      </c>
-      <c r="M85" t="inlineStr">
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>3.228691694388785</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1.139536888574027</v>
+      </c>
+      <c r="T85" t="n">
+        <v>54.80916976928711</v>
+      </c>
+      <c r="U85" t="inlineStr">
         <is>
           <t>tertiary</t>
         </is>
       </c>
-      <c r="N85" t="n">
+      <c r="V85" t="n">
         <v>2</v>
-      </c>
-      <c r="O85" t="n">
-        <v>2.814533612675373</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C005101</t>
+          <t>C007721</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>18.30867863439222</v>
+        <v>34.0066654418853</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -5141,53 +6940,74 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.8 | D=0.3 | P=-0.0 | A=1.1 | R=3.0 | Pop=49.3 | PopScore=3.9</t>
+          <t>Prescription=42.7 | Competition=0.0 | Population=76.3 | Road=0.0</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>14.94388384971127</v>
       </c>
       <c r="F86" t="n">
-        <v>2.783142749899745</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.2902671059658464</v>
+        <v>19.06278159217402</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1.072847802949505</v>
+        <v>42.69681099917506</v>
       </c>
       <c r="J86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>3.918191380788697</v>
+        <v>76.25112636869609</v>
       </c>
       <c r="L86" t="n">
-        <v>49.30937194824219</v>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>5.948850750096658</v>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.073409855865592</v>
+        <v>3.319019662810459</v>
+      </c>
+      <c r="P86" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>5.948850750096658</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>26.63324737548828</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C010454</t>
+          <t>C003792</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>18.26993157444471</v>
+        <v>33.9931675008067</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -5196,53 +7016,74 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=56.6 | PopScore=4.1</t>
+          <t>Prescription=13.7 | Competition=0.0 | Population=86.9 | Road=75.0</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>4.778899146474155</v>
       </c>
       <c r="F87" t="n">
-        <v>2.907250272935932</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>21.71426835433255</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9690834243119771</v>
+        <v>13.65399756135473</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>4.052840895380551</v>
+        <v>86.85707341733018</v>
       </c>
       <c r="L87" t="n">
-        <v>56.56074905395508</v>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.902380803949324</v>
       </c>
       <c r="N87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>2.907250272935932</v>
+        <v>3.780669850467156</v>
+      </c>
+      <c r="P87" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1.902380803949324</v>
+      </c>
+      <c r="T87" t="n">
+        <v>42.84540176391602</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C008145</t>
+          <t>C012221</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>18.23640306428288</v>
+        <v>33.97632242009587</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -5251,53 +7092,74 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=53.8 | PopScore=4.0</t>
+          <t>Prescription=14.7 | Competition=0.0 | Population=95.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>5.156454675057673</v>
       </c>
       <c r="F88" t="n">
-        <v>2.964500885514751</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>23.8198677450382</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9881669618382501</v>
+        <v>14.73272764302192</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>4.002861532356519</v>
+        <v>95.27947098015279</v>
       </c>
       <c r="L88" t="n">
-        <v>53.75460815429688</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2.052677842657946</v>
       </c>
       <c r="N88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>2.964500885514751</v>
+        <v>4.147275623395008</v>
+      </c>
+      <c r="P88" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1.429588059991767</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0.623089782666179</v>
+      </c>
+      <c r="T88" t="n">
+        <v>62.26141738891602</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V88" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C008296</t>
+          <t>C002520</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>18.15578680887578</v>
+        <v>33.82401498136188</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -5306,53 +7168,74 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>H=0.0 | C=1.2 | D=0.8 | P=-0.0 | A=0.8 | R=2.0 | Pop=98.6 | PopScore=4.6</t>
+          <t>Prescription=18.5 | Competition=0.0 | Population=89.4 | Road=50.0</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>6.464564958091114</v>
       </c>
       <c r="F89" t="n">
-        <v>1.203253305403871</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8327698711867052</v>
+        <v>22.35945002327077</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8174693707279761</v>
+        <v>18.47018559454604</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>4.600664506207277</v>
+        <v>89.43780009308308</v>
       </c>
       <c r="L89" t="n">
-        <v>98.55044555664062</v>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.57340946214139</v>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>2.036023176590576</v>
+        <v>3.893002388871203</v>
+      </c>
+      <c r="P89" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>2.57340946214139</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>48.05795669555664</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C006879</t>
+          <t>C000053</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>18.0090305815006</v>
+        <v>33.77182585156439</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -5361,108 +7244,150 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.3 | D=0.0 | P=-0.0 | A=1.1 | R=2.0 | Pop=40.4 | PopScore=3.7</t>
+          <t>Prescription=13.9 | Competition=0.0 | Population=85.6 | Road=75.0</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>4.862308911231528</v>
       </c>
       <c r="F90" t="n">
-        <v>3.264930335612142</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>21.40951694033286</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I90" t="n">
-        <v>1.088310111870714</v>
+        <v>13.89231117494722</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>3.723446299696415</v>
+        <v>85.63806776133146</v>
       </c>
       <c r="L90" t="n">
-        <v>40.4068489074707</v>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.9355845043148</v>
       </c>
       <c r="N90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>3.264930335612142</v>
+        <v>3.727609601602453</v>
+      </c>
+      <c r="P90" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1.9355845043148</v>
+      </c>
+      <c r="T90" t="n">
+        <v>40.57959747314453</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V90" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C010153</t>
+          <t>C012690</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>17.65686473252007</v>
+        <v>33.67147761373074</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>H=0.0 | C=4.5 | D=0.0 | P=-0.0 | A=1.5 | R=3.5 | Pop=14.5 | PopScore=2.7</t>
+          <t>Prescription=42.4 | Competition=0.0 | Population=75.4 | Road=0.0</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>14.82350132934223</v>
       </c>
       <c r="F91" t="n">
-        <v>4.463248418956013</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>18.8479762843885</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1.487749472985338</v>
+        <v>42.35286094097781</v>
       </c>
       <c r="J91" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>2.743864315769838</v>
+        <v>75.39190513755402</v>
       </c>
       <c r="L91" t="n">
-        <v>14.54694747924805</v>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>5.900928961236548</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>4.463248418956013</v>
+        <v>3.281619924646912</v>
+      </c>
+      <c r="P91" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>5.900928961236548</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>25.61885833740234</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V91" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C003964</t>
+          <t>C002501</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>17.58709108552898</v>
+        <v>33.47132247768859</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -5471,53 +7396,74 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.7 | D=0.0 | P=-0.0 | A=0.9 | R=3.0 | Pop=51.4 | PopScore=4.0</t>
+          <t>Prescription=28.4 | Competition=0.0 | Population=94.2 | Road=0.0</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>9.924656437901096</v>
       </c>
       <c r="F92" t="n">
-        <v>2.660939597323611</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>23.5466660397875</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0.886979865774537</v>
+        <v>28.35616125114599</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>3.958837968101435</v>
+        <v>94.18666415914998</v>
       </c>
       <c r="L92" t="n">
-        <v>51.39640426635742</v>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>3.950800239671313</v>
       </c>
       <c r="N92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>2.660939597323611</v>
+        <v>4.099708492268002</v>
+      </c>
+      <c r="P92" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>3.950800239671313</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>59.32270050048828</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V92" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C013966</t>
+          <t>C001680</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>17.50918176039009</v>
+        <v>33.21047402725125</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -5526,53 +7472,74 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.8 | D=0.0 | P=-0.0 | A=0.9 | R=2.0 | Pop=46.1 | PopScore=3.9</t>
+          <t>Prescription=21.1 | Competition=0.0 | Population=83.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>7.37872737817603</v>
       </c>
       <c r="F93" t="n">
-        <v>2.828606644240314</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>20.83174664907522</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9428688814134379</v>
+        <v>21.08207822336009</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>3.852560527922706</v>
+        <v>83.32698659630088</v>
       </c>
       <c r="L93" t="n">
-        <v>46.11354446411133</v>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2.937318594005888</v>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>2.828606644240314</v>
+        <v>3.627014053780666</v>
+      </c>
+      <c r="P93" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2.937318594005888</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>36.60037612915039</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V93" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C000888</t>
+          <t>C005040</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>17.47568534571645</v>
+        <v>33.1480001060946</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -5581,53 +7548,74 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.7 | D=0.0 | P=-0.0 | A=0.9 | R=3.0 | Pop=48.0 | PopScore=3.9</t>
+          <t>Prescription=17.5 | Competition=0.0 | Population=88.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>6.139337391707823</v>
       </c>
       <c r="F94" t="n">
-        <v>2.704190852491417</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>22.00866271438678</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9013969508304723</v>
+        <v>17.54096397630807</v>
       </c>
       <c r="J94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>3.892387981883525</v>
+        <v>88.03465085754712</v>
       </c>
       <c r="L94" t="n">
-        <v>48.02782440185547</v>
-      </c>
-      <c r="M94" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2.443943101743472</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>3.831926833343236</v>
+      </c>
+      <c r="P94" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.516331421446902</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0.9276116802965699</v>
+      </c>
+      <c r="T94" t="n">
+        <v>45.1513786315918</v>
+      </c>
+      <c r="U94" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N94" t="n">
-        <v>3</v>
-      </c>
-      <c r="O94" t="n">
-        <v>2.704190852491417</v>
+      <c r="V94" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C000068</t>
+          <t>C004255</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>17.45402143499637</v>
+        <v>33.11488600682182</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -5636,53 +7624,74 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>H=1.3 | C=2.0 | D=0.4 | P=-1.0 | A=1.1 | R=3.0 | Pop=63.1 | PopScore=4.2</t>
+          <t>Prescription=49.9 | Competition=36.4 | Population=86.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1.331433635211078</v>
+        <v>17.4594253679512</v>
       </c>
       <c r="F95" t="n">
-        <v>2.041252395463951</v>
+        <v>10.91142307098628</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3846345741024767</v>
+        <v>21.5668837098569</v>
       </c>
       <c r="H95" t="n">
-        <v>0.9844485460177469</v>
+        <v>5</v>
       </c>
       <c r="I95" t="n">
-        <v>1.094640358074402</v>
+        <v>49.88407247986057</v>
       </c>
       <c r="J95" t="n">
-        <v>3</v>
+        <v>36.37141023662092</v>
       </c>
       <c r="K95" t="n">
-        <v>4.161087275895718</v>
+        <v>86.26753483942761</v>
       </c>
       <c r="L95" t="n">
-        <v>63.1412239074707</v>
-      </c>
-      <c r="M95" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M95" t="n">
+        <v>6.950235744665522</v>
+      </c>
+      <c r="N95" t="n">
+        <v>2.934735806874224</v>
+      </c>
+      <c r="O95" t="n">
+        <v>3.75500871960618</v>
+      </c>
+      <c r="P95" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>5.911019114987763</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1.039216629677759</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>41.73459243774414</v>
+      </c>
+      <c r="U95" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N95" t="n">
-        <v>3</v>
-      </c>
-      <c r="O95" t="n">
-        <v>3.757320604777506</v>
+      <c r="V95" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C001954</t>
+          <t>C002093</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>17.28369932128276</v>
+        <v>33.11390436402692</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5691,53 +7700,74 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>H=0.0 | C=1.7 | D=0.6 | P=-0.0 | A=0.8 | R=3.5 | Pop=62.0 | PopScore=4.1</t>
+          <t>Prescription=21.6 | Competition=0.0 | Population=82.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>7.550034300721182</v>
       </c>
       <c r="F96" t="n">
-        <v>1.651873015815432</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.5597941664238303</v>
+        <v>20.56387006330574</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I96" t="n">
-        <v>0.8305214218170589</v>
+        <v>21.57152657348909</v>
       </c>
       <c r="J96" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>4.142437604874178</v>
+        <v>82.25548025322296</v>
       </c>
       <c r="L96" t="n">
-        <v>61.95609664916992</v>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>primary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3.005512332991565</v>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>2.211667182239262</v>
+        <v>3.580374078860088</v>
+      </c>
+      <c r="P96" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>3.005512332991565</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>34.886962890625</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V96" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C008187</t>
+          <t>C010661</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>17.2775298135002</v>
+        <v>32.92057656131267</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5746,108 +7776,150 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>H=0.0 | C=0.0 | D=2.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=74.9 | PopScore=4.3</t>
+          <t>Prescription=5.2 | Competition=0.0 | Population=94.4 | Road=75.0</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1.825915689046522</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>1.994032912597058</v>
+        <v>23.59466087226615</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.997016456298529</v>
+        <v>5.21690196870435</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>4.329920780892077</v>
+        <v>94.37864348906459</v>
       </c>
       <c r="L97" t="n">
-        <v>74.93827056884766</v>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.7268592305478555</v>
       </c>
       <c r="N97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1.994032912597058</v>
+        <v>4.10806486942837</v>
+      </c>
+      <c r="P97" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.7268592305478555</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>59.82889175415039</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V97" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C013375</t>
+          <t>C000566</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>17.22524748024495</v>
+        <v>32.78057148689416</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>H=0.0 | C=3.0 | D=0.0 | P=-0.0 | A=1.0 | R=2.0 | Pop=38.1 | PopScore=3.7</t>
+          <t>Prescription=100.0 | Competition=100.0 | Population=91.1 | Road=50.0</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F98" t="n">
-        <v>2.962491407066286</v>
+        <v>30</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>22.78057148689416</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9874971356887619</v>
+        <v>100</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K98" t="n">
-        <v>3.667171650847834</v>
+        <v>91.12228594757664</v>
       </c>
       <c r="L98" t="n">
-        <v>38.14104461669922</v>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>tertiary</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="M98" t="n">
+        <v>96.95707514290143</v>
       </c>
       <c r="N98" t="n">
-        <v>2</v>
+        <v>30.80745044097855</v>
       </c>
       <c r="O98" t="n">
-        <v>2.962491407066286</v>
+        <v>3.966323819504986</v>
+      </c>
+      <c r="P98" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>6.967140901460901</v>
+      </c>
+      <c r="R98" t="n">
+        <v>38.78516257146202</v>
+      </c>
+      <c r="S98" t="n">
+        <v>51.20477166997851</v>
+      </c>
+      <c r="T98" t="n">
+        <v>51.79010772705078</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="V98" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C002520</t>
+          <t>C000078</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>17.2116064063011</v>
+        <v>32.55230263012822</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5856,53 +7928,74 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.6 | D=0.0 | P=-0.0 | A=0.9 | R=3.0 | Pop=48.1 | PopScore=3.9</t>
+          <t>Prescription=12.5 | Competition=0.0 | Population=82.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>4.378264108616531</v>
       </c>
       <c r="F99" t="n">
-        <v>2.57340946214139</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>20.67403852151169</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I99" t="n">
-        <v>0.85780315404713</v>
+        <v>12.50932602461866</v>
       </c>
       <c r="J99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>3.893002388871203</v>
+        <v>82.69615408604677</v>
       </c>
       <c r="L99" t="n">
-        <v>48.05795669555664</v>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.74289629045584</v>
       </c>
       <c r="N99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>2.57340946214139</v>
+        <v>3.599555501950892</v>
+      </c>
+      <c r="P99" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1.74289629045584</v>
+      </c>
+      <c r="T99" t="n">
+        <v>35.58197021484375</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="V99" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C002593</t>
+          <t>C003503</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>17.20280026967236</v>
+        <v>32.27825157050953</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5911,53 +8004,74 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.1 | D=0.0 | P=-0.0 | A=0.7 | R=3.0 | Pop=65.0 | PopScore=4.2</t>
+          <t>Prescription=20.8 | Competition=0.0 | Population=100.0 | Road=0.0</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>7.278251570509533</v>
       </c>
       <c r="F100" t="n">
-        <v>2.130288984669355</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0.7100963282231182</v>
+        <v>20.7950044871701</v>
       </c>
       <c r="J100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>4.190404222503778</v>
+        <v>100</v>
       </c>
       <c r="L100" t="n">
-        <v>65.04948425292969</v>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>secondary</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2.897321255307693</v>
       </c>
       <c r="N100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>2.130288984669355</v>
+        <v>4.516137085628762</v>
+      </c>
+      <c r="P100" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>2.897321255307693</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>90.48152923583984</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>tertiary</t>
+        </is>
+      </c>
+      <c r="V100" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C001680</t>
+          <t>C005118</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>17.15358996915397</v>
+        <v>32.25753739358888</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5966,43 +8080,64 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>H=0.0 | C=2.9 | D=0.0 | P=-0.0 | A=1.0 | R=3.0 | Pop=36.6 | PopScore=3.6</t>
+          <t>Prescription=11.2 | Competition=0.0 | Population=93.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>3.930562245514911</v>
       </c>
       <c r="F101" t="n">
-        <v>2.937318594005888</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>23.32697514807397</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I101" t="n">
-        <v>0.9791061980019629</v>
+        <v>11.23017784432832</v>
       </c>
       <c r="J101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>3.627014053780666</v>
+        <v>93.30790059229587</v>
       </c>
       <c r="L101" t="n">
-        <v>36.60037612915039</v>
-      </c>
-      <c r="M101" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.564675448343019</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>4.0614581254046</v>
+      </c>
+      <c r="P101" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1.564675448343019</v>
+      </c>
+      <c r="T101" t="n">
+        <v>57.05890655517578</v>
+      </c>
+      <c r="U101" t="inlineStr">
         <is>
           <t>secondary</t>
         </is>
       </c>
-      <c r="N101" t="n">
-        <v>3</v>
-      </c>
-      <c r="O101" t="n">
-        <v>2.937318594005888</v>
+      <c r="V101" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/best_areas.xlsx
+++ b/data/processed/best_areas.xlsx
@@ -543,11 +543,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C009759</t>
+          <t>C013419</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67.5</v>
+        <v>94.85961873320241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -556,20 +556,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=0.0 | Population=100.0 | Road=75.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=99.5 | Road=75.0</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>29.85961873320241</v>
       </c>
       <c r="H2" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -578,34 +578,34 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>99.53206244400803</v>
       </c>
       <c r="L2" t="n">
         <v>75</v>
       </c>
       <c r="M2" t="n">
-        <v>16.51184771146742</v>
+        <v>14.16636817049609</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.368882248176226</v>
+        <v>9.834024723754817</v>
       </c>
       <c r="P2" t="n">
         <v>3.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.443471657628298</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.555543759289683</v>
+        <v>3.608525682040129</v>
       </c>
       <c r="S2" t="n">
-        <v>9.512832294549437</v>
+        <v>10.55784248845596</v>
       </c>
       <c r="T2" t="n">
-        <v>77.95532989501953</v>
+        <v>18656.89619154111</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C000138</t>
+          <t>C009261</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.13962398319762</v>
+        <v>94.64823301415258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -632,20 +632,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=0.0 | Population=94.6 | Road=75.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=98.8 | Road=75.0</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>23.63962398319762</v>
+        <v>29.64823301415258</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -654,19 +654,19 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>94.55849593279048</v>
+        <v>98.82744338050861</v>
       </c>
       <c r="L3" t="n">
         <v>75</v>
       </c>
       <c r="M3" t="n">
-        <v>14.29987736537275</v>
+        <v>14.47159564707925</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1158933937474</v>
+        <v>9.764406541220117</v>
       </c>
       <c r="P3" t="n">
         <v>3.5</v>
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>8.130224859129246</v>
+        <v>14.47159564707925</v>
       </c>
       <c r="S3" t="n">
-        <v>6.169652506243509</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>60.30696105957031</v>
+        <v>17402.15065991879</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -695,11 +695,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C013419</t>
+          <t>C004997</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.42494696176338</v>
+        <v>94.64668463303241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -708,20 +708,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=0.0 | Population=91.7 | Road=75.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=98.8 | Road=75.0</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>22.92494696176339</v>
+        <v>29.6466846330324</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
         <v>100</v>
@@ -730,34 +730,34 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>91.69978784705354</v>
+        <v>98.82228211010802</v>
       </c>
       <c r="L4" t="n">
         <v>75</v>
       </c>
       <c r="M4" t="n">
-        <v>14.1663681705177</v>
+        <v>16.11387051099258</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.991461024041562</v>
+        <v>9.763896594380082</v>
       </c>
       <c r="P4" t="n">
         <v>3.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>9.78273790260512</v>
       </c>
       <c r="R4" t="n">
-        <v>3.608525682096874</v>
+        <v>3.306003776712432</v>
       </c>
       <c r="S4" t="n">
-        <v>10.55784248842083</v>
+        <v>3.025128831675025</v>
       </c>
       <c r="T4" t="n">
-        <v>53.1339225769043</v>
+        <v>17393.27824065648</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -771,11 +771,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C009261</t>
+          <t>C000087</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.36840622320143</v>
+        <v>94.38053258775734</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -784,20 +784,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=0.0 | Population=91.5 | Road=75.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=97.9 | Road=75.0</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>22.86840622320143</v>
+        <v>29.38053258775734</v>
       </c>
       <c r="H5" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>100</v>
@@ -806,34 +806,34 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>91.47362489280573</v>
+        <v>97.93510862585781</v>
       </c>
       <c r="L5" t="n">
         <v>75</v>
       </c>
       <c r="M5" t="n">
-        <v>14.47159564706446</v>
+        <v>25.9704704610001</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.981616719729017</v>
+        <v>9.676241563788464</v>
       </c>
       <c r="P5" t="n">
         <v>3.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.8564191511931554</v>
       </c>
       <c r="R5" t="n">
-        <v>14.47159564706446</v>
+        <v>10.9043488242049</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>14.20970248560205</v>
       </c>
       <c r="T5" t="n">
-        <v>52.6036262512207</v>
+        <v>15933.49545707926</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -847,11 +847,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C004996</t>
+          <t>C009759</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.27313590200377</v>
+        <v>94.28850096489613</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -860,20 +860,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=0.0 | Population=91.1 | Road=75.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=97.6 | Road=75.0</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>22.77313590200377</v>
+        <v>29.28850096489613</v>
       </c>
       <c r="H6" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
         <v>100</v>
@@ -882,34 +882,34 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>91.09254360801509</v>
+        <v>97.62833654965377</v>
       </c>
       <c r="L6" t="n">
         <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>18.44093098873054</v>
+        <v>16.51184771140679</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.965029210303471</v>
+        <v>9.645931690689579</v>
       </c>
       <c r="P6" t="n">
         <v>3.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.72328944197298</v>
+        <v>1.443471657619113</v>
       </c>
       <c r="R6" t="n">
-        <v>1.035025367816185</v>
+        <v>5.555543759264908</v>
       </c>
       <c r="S6" t="n">
-        <v>2.682616178941371</v>
+        <v>9.51283229452277</v>
       </c>
       <c r="T6" t="n">
-        <v>51.72180938720703</v>
+        <v>15457.76894677058</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -923,11 +923,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C009017</t>
+          <t>C000138</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63.12186317729812</v>
+        <v>94.11410238275872</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -936,20 +936,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=0.0 | Population=92.5 | Road=50.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=97.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>23.12186317729812</v>
+        <v>29.11410238275871</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
         <v>100</v>
@@ -958,52 +958,52 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92.48745270919247</v>
+        <v>97.04700794252905</v>
       </c>
       <c r="L7" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M7" t="n">
-        <v>15.66096022946828</v>
+        <v>14.29987736531525</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.025746093517168</v>
+        <v>9.588494923534208</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.691455119737899</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>6.31422922481618</v>
+        <v>8.130224859092312</v>
       </c>
       <c r="S7" t="n">
-        <v>3.655275884914199</v>
+        <v>6.169652506222936</v>
       </c>
       <c r="T7" t="n">
-        <v>55.02209091186523</v>
+        <v>14594.88507122546</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C012479</t>
+          <t>C001872</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62.49594175647037</v>
+        <v>90.87166170518293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1012,74 +1012,74 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Prescription=99.5 | Competition=0.0 | Population=90.7 | Road=50.0</t>
+          <t>Prescription=94.6 | Competition=0.0 | Population=95.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34.82903748497327</v>
+        <v>47.27963935475323</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>22.6669042714971</v>
+        <v>28.59202235042969</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>99.51153567135221</v>
+        <v>94.55927870950646</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>90.6676170859884</v>
+        <v>95.30674116809898</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M8" t="n">
-        <v>13.86471869370364</v>
+        <v>13.1747318574043</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.946533228027264</v>
+        <v>9.416552073507345</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.73502665301193</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.744008625134775</v>
+        <v>10.33562517301334</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3856834155569375</v>
+        <v>2.83910668439096</v>
       </c>
       <c r="T8" t="n">
-        <v>50.75563049316406</v>
+        <v>12289.13360466808</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C012629</t>
+          <t>C000433</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62.14404380146085</v>
+        <v>90.0117337929578</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1088,74 +1088,74 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=0.0 | Population=88.6 | Road=50.0</t>
+          <t>Prescription=100.0 | Competition=16.0 | Population=99.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4.786210236216758</v>
       </c>
       <c r="G9" t="n">
-        <v>22.14404380146085</v>
+        <v>29.79794402917456</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>15.95403412072253</v>
       </c>
       <c r="K9" t="n">
-        <v>88.57617520584338</v>
+        <v>99.32648009724855</v>
       </c>
       <c r="L9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>16.65055602921596</v>
+        <v>19.09394683393043</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.2145498112098656</v>
       </c>
       <c r="O9" t="n">
-        <v>3.855498025605961</v>
+        <v>9.813712657158813</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.665046346321709</v>
+        <v>7.248761323583166</v>
       </c>
       <c r="R9" t="n">
-        <v>1.894348002857561</v>
+        <v>2.499993189881885</v>
       </c>
       <c r="S9" t="n">
-        <v>6.091161680036689</v>
+        <v>9.345192320465383</v>
       </c>
       <c r="T9" t="n">
-        <v>46.25214385986328</v>
+        <v>18281.73877125978</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C013729</t>
+          <t>C009339</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.82222056186308</v>
+        <v>89.82568513897535</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1164,56 +1164,56 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=10.6 | Population=100.0 | Road=50.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=99.4 | Road=50.0</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>3.177779438136925</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>29.82568513897535</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>10.59259812712308</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>99.41895046325115</v>
       </c>
       <c r="L10" t="n">
         <v>50</v>
       </c>
       <c r="M10" t="n">
-        <v>17.27743170594908</v>
+        <v>14.59736229196001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8546953997455184</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.439639397584378</v>
+        <v>9.822848968043518</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8625006549112778</v>
+        <v>3.747549849414678</v>
       </c>
       <c r="R10" t="n">
-        <v>10.67050215670293</v>
+        <v>7.099015846224423</v>
       </c>
       <c r="S10" t="n">
-        <v>5.744428894334872</v>
+        <v>3.750796596320913</v>
       </c>
       <c r="T10" t="n">
-        <v>83.74437713623047</v>
+        <v>18449.54093563557</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C001872</t>
+          <t>C005036</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60.17561953859038</v>
+        <v>89.46121165270563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1240,64 +1240,64 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Prescription=94.6 | Competition=0.0 | Population=78.3 | Road=75.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=98.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>33.09574754836455</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>19.57987199022583</v>
+        <v>29.46121165270564</v>
       </c>
       <c r="H11" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>94.55927870961301</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>78.31948796090332</v>
+        <v>98.20403884235212</v>
       </c>
       <c r="L11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>13.17473185740145</v>
+        <v>14.82268691514426</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.409050238373943</v>
+        <v>9.702812563454604</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.938993980343114</v>
       </c>
       <c r="R11" t="n">
-        <v>10.33562517302392</v>
+        <v>6.106033776932642</v>
       </c>
       <c r="S11" t="n">
-        <v>2.839106684377524</v>
+        <v>1.777659157868501</v>
       </c>
       <c r="T11" t="n">
-        <v>29.23651313781738</v>
+        <v>16362.56610456109</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60.12498114994295</v>
+        <v>89.33805784654913</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1316,41 +1316,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Prescription=89.1 | Competition=0.0 | Population=85.7 | Road=75.0</t>
+          <t>Prescription=89.1 | Competition=0.0 | Population=99.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31.19413930690592</v>
+        <v>44.56305615231693</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>21.43084184303703</v>
+        <v>29.77500169423221</v>
       </c>
       <c r="H12" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I12" t="n">
-        <v>89.12611230544549</v>
+        <v>89.12611230463386</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>85.72336737214813</v>
+        <v>99.25000564744069</v>
       </c>
       <c r="L12" t="n">
         <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>12.41774098893925</v>
+        <v>12.41774098884285</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.731322479024902</v>
+        <v>9.806156784089579</v>
       </c>
       <c r="P12" t="n">
         <v>3.5</v>
@@ -1359,13 +1359,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>9.783628745659058</v>
+        <v>9.783628745567299</v>
       </c>
       <c r="S12" t="n">
-        <v>2.634112243280191</v>
+        <v>2.63411224327555</v>
       </c>
       <c r="T12" t="n">
-        <v>40.7342643737793</v>
+        <v>18144.11729768664</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1379,11 +1379,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C005105</t>
+          <t>C012479</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60.06327504669362</v>
+        <v>89.32030273105114</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1392,56 +1392,56 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=16.5 | Population=100.0 | Road=50.0</t>
+          <t>Prescription=99.5 | Competition=0.0 | Population=98.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>49.75576783562482</v>
       </c>
       <c r="F13" t="n">
-        <v>4.93672495330638</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>25</v>
+        <v>29.56453489542632</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>100</v>
+        <v>99.51153567124965</v>
       </c>
       <c r="J13" t="n">
-        <v>16.4557498443546</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>98.54844965142107</v>
       </c>
       <c r="L13" t="n">
         <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>28.3771447042245</v>
+        <v>13.86471869370798</v>
       </c>
       <c r="N13" t="n">
-        <v>1.327781298085819</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.35559049529125</v>
+        <v>9.736841240529568</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.988164139416247</v>
+        <v>10.73502665301071</v>
       </c>
       <c r="R13" t="n">
-        <v>13.72884910660469</v>
+        <v>2.744008625138783</v>
       </c>
       <c r="S13" t="n">
-        <v>4.660131458203558</v>
+        <v>0.3856834155584904</v>
       </c>
       <c r="T13" t="n">
-        <v>76.91281890869141</v>
+        <v>16928.9790982753</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1455,11 +1455,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C008162</t>
+          <t>C013729</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59.76664117776571</v>
+        <v>86.82222056186606</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1468,56 +1468,56 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Prescription=87.5 | Competition=0.0 | Population=96.6 | Road=50.0</t>
+          <t>Prescription=100.0 | Competition=10.6 | Population=100.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>30.61686170909667</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3.177779438133937</v>
       </c>
       <c r="G14" t="n">
-        <v>24.14977946866903</v>
+        <v>30</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
-        <v>87.47674774027622</v>
+        <v>100</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>10.59259812711312</v>
       </c>
       <c r="K14" t="n">
-        <v>96.59911787467612</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>12.187938729682</v>
+        <v>17.27743170594908</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.1424492332909197</v>
       </c>
       <c r="O14" t="n">
-        <v>4.204716532132689</v>
+        <v>9.905619601297188</v>
       </c>
       <c r="P14" t="n">
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.8625006549112778</v>
       </c>
       <c r="R14" t="n">
-        <v>8.618143666159648</v>
+        <v>10.67050215670293</v>
       </c>
       <c r="S14" t="n">
-        <v>3.569795063522354</v>
+        <v>5.744428894334872</v>
       </c>
       <c r="T14" t="n">
-        <v>66.00160217285156</v>
+        <v>20041.68646386266</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1531,11 +1531,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C000086</t>
+          <t>C008345</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.248137412368</v>
+        <v>86.19172453227155</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1544,74 +1544,74 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=0.0 | Population=67.0 | Road=75.0</t>
+          <t>Prescription=99.7 | Competition=10.4 | Population=98.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>49.85063269153971</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3.121886771355467</v>
       </c>
       <c r="G15" t="n">
-        <v>16.748137412368</v>
+        <v>29.46297861208731</v>
       </c>
       <c r="H15" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>100</v>
+        <v>99.70126538307942</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>10.40628923785156</v>
       </c>
       <c r="K15" t="n">
-        <v>66.99254964947201</v>
+        <v>98.20992870695771</v>
       </c>
       <c r="L15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>14.6176870305769</v>
+        <v>13.89115330819377</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.1399437518111059</v>
       </c>
       <c r="O15" t="n">
-        <v>2.916017115252559</v>
+        <v>9.703394497283046</v>
       </c>
       <c r="P15" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.003067283292438</v>
       </c>
       <c r="R15" t="n">
-        <v>7.904269188429921</v>
+        <v>1.787889982751606</v>
       </c>
       <c r="S15" t="n">
-        <v>6.713417842146983</v>
+        <v>10.10019604214972</v>
       </c>
       <c r="T15" t="n">
-        <v>17.46758651733398</v>
+        <v>16372.09138850495</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C008345</t>
+          <t>C001412</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58.5540126333852</v>
+        <v>83.02878055836175</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1620,56 +1620,56 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Prescription=99.7 | Competition=10.4 | Population=87.1 | Road=50.0</t>
+          <t>Prescription=86.1 | Competition=0.0 | Population=100.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>34.89544288428147</v>
+        <v>43.02878055836174</v>
       </c>
       <c r="F16" t="n">
-        <v>3.121886771380264</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>21.78045652048399</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>99.70126538366137</v>
+        <v>86.05756111672348</v>
       </c>
       <c r="J16" t="n">
-        <v>10.40628923793421</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>87.12182608193595</v>
+        <v>100</v>
       </c>
       <c r="L16" t="n">
         <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>13.89115330825619</v>
+        <v>11.99020664590825</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8396625108725151</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.792193867769657</v>
+        <v>9.90583274698372</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.003067283305269</v>
+        <v>10.87807738630281</v>
       </c>
       <c r="R16" t="n">
-        <v>1.787889982759375</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>10.10019604219154</v>
+        <v>1.112129259605435</v>
       </c>
       <c r="T16" t="n">
-        <v>43.35359954833984</v>
+        <v>20045.95893134177</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C013500</t>
+          <t>C008162</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56.46935742914103</v>
+        <v>82.45250953215755</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1696,74 +1696,74 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Prescription=93.0 | Competition=0.0 | Population=95.6 | Road=0.0</t>
+          <t>Prescription=87.5 | Competition=0.0 | Population=95.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>32.55794434772347</v>
+        <v>43.73837387011292</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>23.91141308141756</v>
+        <v>28.71413566204462</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>93.02269813635277</v>
+        <v>87.47674774022585</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>95.64565232567026</v>
+        <v>95.71378554014875</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M17" t="n">
-        <v>12.96064353834643</v>
+        <v>12.18793872969136</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.163214575956184</v>
+        <v>9.45676910830108</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>12.96064353834643</v>
+        <v>8.618143666169638</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.569795063521719</v>
       </c>
       <c r="T17" t="n">
-        <v>63.27781677246094</v>
+        <v>12793.48001801968</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C000424</t>
+          <t>C000376</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.88578640764644</v>
+        <v>79.02526056690783</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1772,56 +1772,56 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Prescription=74.6 | Competition=0.0 | Population=91.2 | Road=50.0</t>
+          <t>Prescription=85.0 | Competition=10.9 | Population=99.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>26.09451659110864</v>
+        <v>42.48339701053073</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>3.261694432209514</v>
       </c>
       <c r="G18" t="n">
-        <v>22.79126981653779</v>
+        <v>29.80355798858663</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>74.55576168888184</v>
+        <v>84.96679402106146</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>10.87231477403171</v>
       </c>
       <c r="K18" t="n">
-        <v>91.16507926615117</v>
+        <v>99.34519329528875</v>
       </c>
       <c r="L18" t="n">
         <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>10.3876867725672</v>
+        <v>11.83823251708294</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.1462108620635879</v>
       </c>
       <c r="O18" t="n">
-        <v>3.968186504983218</v>
+        <v>9.815561569435612</v>
       </c>
       <c r="P18" t="n">
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.391685291600806</v>
+        <v>4.968067659166701</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>6.320706845348123</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9960014809663902</v>
+        <v>0.5494580125681127</v>
       </c>
       <c r="T18" t="n">
-        <v>51.88853073120117</v>
+        <v>18315.57322025299</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51.80656184533169</v>
+        <v>78.6048938256633</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1848,17 +1848,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=0.0 | Population=67.2 | Road=0.0</t>
+          <t>Prescription=100.0 | Competition=0.0 | Population=95.3 | Road=0.0</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>16.80656184533169</v>
+        <v>28.6048938256633</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>67.22624738132676</v>
+        <v>95.34964608554434</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.926189389474839</v>
+        <v>9.420791190115279</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
@@ -1897,7 +1897,7 @@
         <v>2.272578183504773</v>
       </c>
       <c r="T19" t="n">
-        <v>17.65640258789062</v>
+        <v>12341.34349787328</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -1911,11 +1911,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C000101</t>
+          <t>C009733</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51.72313635741015</v>
+        <v>78.21271486203059</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1924,74 +1924,74 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Prescription=79.5 | Competition=14.7 | Population=93.2 | Road=50.0</t>
+          <t>Prescription=68.0 | Competition=0.0 | Population=97.4 | Road=75.0</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>27.84055308493168</v>
+        <v>33.98210357263902</v>
       </c>
       <c r="F20" t="n">
-        <v>4.408512129753122</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>23.29109540223159</v>
+        <v>29.23061128939157</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I20" t="n">
-        <v>79.54443738551909</v>
+        <v>67.96420714527804</v>
       </c>
       <c r="J20" t="n">
-        <v>14.69504043251041</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>93.16438160892636</v>
+        <v>97.43537096463858</v>
       </c>
       <c r="L20" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M20" t="n">
-        <v>11.0827477493812</v>
+        <v>9.469300287186941</v>
       </c>
       <c r="N20" t="n">
-        <v>1.185713203315138</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.055211105190279</v>
+        <v>9.626866192725638</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.315526071977458</v>
+        <v>3.831780012556585</v>
       </c>
       <c r="R20" t="n">
-        <v>5.176321890113948</v>
+        <v>5.637520274630356</v>
       </c>
       <c r="S20" t="n">
-        <v>2.590899787289793</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>56.69734191894531</v>
+        <v>15165.83162712678</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C009733</t>
+          <t>C012336</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>51.61742848372653</v>
+        <v>76.75133889616626</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2000,74 +2000,74 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Prescription=68.0 | Competition=0.0 | Population=81.3 | Road=75.0</t>
+          <t>Prescription=95.3 | Competition=0.0 | Population=97.0 | Road=0.0</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>23.78747250060239</v>
+        <v>47.64360560194448</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>20.32995598312414</v>
+        <v>29.10773329422177</v>
       </c>
       <c r="H21" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>67.96420714457825</v>
+        <v>95.28721120388896</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>81.31982393249658</v>
+        <v>97.02577764740592</v>
       </c>
       <c r="L21" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>9.46930028707672</v>
+        <v>13.27615305640946</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.539647313577855</v>
+        <v>9.586397315567419</v>
       </c>
       <c r="P21" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.831780012489994</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.637520274586725</v>
+        <v>12.17389847792689</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.102254578482571</v>
       </c>
       <c r="T21" t="n">
-        <v>33.45476531982422</v>
+        <v>14564.30071462691</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C012336</t>
+          <t>C013500</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50.62480463778627</v>
+        <v>75.98022359526736</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2076,41 +2076,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Prescription=95.3 | Competition=0.0 | Population=69.1 | Road=0.0</t>
+          <t>Prescription=93.0 | Competition=0.0 | Population=98.2 | Road=0.0</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>33.35052392140594</v>
+        <v>46.51134906825025</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>17.27428071638033</v>
+        <v>29.46887452701711</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>95.28721120401697</v>
+        <v>93.02269813650051</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>69.09712286552131</v>
+        <v>98.22958175672369</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>13.27615305640946</v>
+        <v>12.96064353838443</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.007623891683858</v>
+        <v>9.705336269336696</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -2119,13 +2119,13 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>12.17389847792689</v>
+        <v>12.96064353838443</v>
       </c>
       <c r="S22" t="n">
-        <v>1.102254578482571</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>19.2392520904541</v>
+        <v>16403.91508697998</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2139,69 +2139,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C007949</t>
+          <t>C012716</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>49.71240805785547</v>
+        <v>74.64535354459269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Prescription=60.6 | Competition=0.0 | Population=94.0 | Road=50.0</t>
+          <t>Prescription=100.0 | Competition=51.1 | Population=99.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>21.20469825695342</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>15.33002719406195</v>
       </c>
       <c r="G23" t="n">
-        <v>23.50770980090205</v>
+        <v>29.97538073865464</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>60.58485216272405</v>
+        <v>100</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>51.10009064687316</v>
       </c>
       <c r="K23" t="n">
-        <v>94.03083920360821</v>
+        <v>99.91793579551546</v>
       </c>
       <c r="L23" t="n">
         <v>50</v>
       </c>
       <c r="M23" t="n">
-        <v>8.441151336564211</v>
+        <v>30.34525252113698</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.6871938920359499</v>
       </c>
       <c r="O23" t="n">
-        <v>4.092925824050106</v>
+        <v>9.872150007063368</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.437333420948989</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.003817915615222</v>
+        <v>17.89137469024122</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>12.45387783089576</v>
       </c>
       <c r="T23" t="n">
-        <v>58.91493606567383</v>
+        <v>19381.96772417426</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2215,11 +2215,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C001072</t>
+          <t>C001065</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>49.60662477693847</v>
+        <v>72.00002635845217</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2228,56 +2228,56 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Prescription=63.8 | Competition=0.0 | Population=89.1 | Road=50.0</t>
+          <t>Prescription=81.8 | Competition=28.6 | Population=98.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>22.32745553064121</v>
+        <v>40.91446742217089</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>8.589801153230258</v>
       </c>
       <c r="G24" t="n">
-        <v>22.27916924629727</v>
+        <v>29.67536008951154</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>63.79273008754631</v>
+        <v>81.82893484434177</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>28.63267051076753</v>
       </c>
       <c r="K24" t="n">
-        <v>89.11667698518909</v>
+        <v>98.91786696503848</v>
       </c>
       <c r="L24" t="n">
         <v>50</v>
       </c>
       <c r="M24" t="n">
-        <v>8.888097760728444</v>
+        <v>11.40104164778096</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.3850520818769096</v>
       </c>
       <c r="O24" t="n">
-        <v>3.879024708015324</v>
+        <v>9.773340624811295</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>7.521288256284354</v>
       </c>
       <c r="R24" t="n">
-        <v>2.917634677837338</v>
+        <v>3.879753391496605</v>
       </c>
       <c r="S24" t="n">
-        <v>5.970463082891105</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>47.37701034545898</v>
+        <v>17558.32847668603</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -2291,315 +2291,315 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C009251</t>
+          <t>C001072</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>48.48451732496753</v>
+        <v>71.74688387865828</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Prescription=51.3 | Competition=0.0 | Population=92.1 | Road=75.0</t>
+          <t>Prescription=63.8 | Competition=0.0 | Population=99.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17.95085038129304</v>
+        <v>31.89636504371175</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>23.03366694367449</v>
+        <v>29.85051883494654</v>
       </c>
       <c r="H25" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>51.28814394655156</v>
+        <v>63.7927300874235</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>92.13466777469796</v>
+        <v>99.5017294498218</v>
       </c>
       <c r="L25" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M25" t="n">
-        <v>7.145861867608882</v>
+        <v>8.888097760723273</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.010390253018906</v>
+        <v>9.831027745620855</v>
       </c>
       <c r="P25" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8378481678594797</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.411657315824704</v>
+        <v>2.917634677831475</v>
       </c>
       <c r="S25" t="n">
-        <v>1.896356383924698</v>
+        <v>5.970463082891799</v>
       </c>
       <c r="T25" t="n">
-        <v>54.16839599609375</v>
+        <v>18601.06259245798</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C010135</t>
+          <t>C004991</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48.05491519850658</v>
+        <v>71.49059178236466</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=52.5 | Population=95.2 | Road=50.0</t>
+          <t>Prescription=54.8 | Competition=0.0 | Population=97.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>35</v>
+        <v>27.38180345079117</v>
       </c>
       <c r="F26" t="n">
-        <v>15.74723544578666</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>23.80215064429324</v>
+        <v>29.10878833157349</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I26" t="n">
-        <v>100</v>
+        <v>54.76360690158235</v>
       </c>
       <c r="J26" t="n">
-        <v>52.49078481928887</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>95.20860257717297</v>
+        <v>97.02929443857829</v>
       </c>
       <c r="L26" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M26" t="n">
-        <v>37.51187441225131</v>
+        <v>7.63009031286221</v>
       </c>
       <c r="N26" t="n">
-        <v>4.235375662860431</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.144190900136958</v>
+        <v>9.586744783614279</v>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.850292848284808</v>
       </c>
       <c r="R26" t="n">
-        <v>21.28470454870176</v>
+        <v>1.162045182371362</v>
       </c>
       <c r="S26" t="n">
-        <v>16.22716986354955</v>
+        <v>1.61775228220604</v>
       </c>
       <c r="T26" t="n">
-        <v>62.06657409667969</v>
+        <v>14569.36257058382</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C003250</t>
+          <t>C002371</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>46.63412035944046</v>
+        <v>70.98002574202516</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Prescription=58.9 | Competition=0.0 | Population=84.0 | Road=50.0</t>
+          <t>Prescription=87.5 | Competition=58.1 | Population=98.8 | Road=75.0</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>20.63128163322788</v>
+        <v>43.76784837063909</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>17.4394734973879</v>
       </c>
       <c r="G27" t="n">
-        <v>21.00283872621258</v>
+        <v>29.65165086877397</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I27" t="n">
-        <v>58.94651895207966</v>
+        <v>87.53569674127819</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>58.13157832462635</v>
       </c>
       <c r="K27" t="n">
-        <v>84.01135490485032</v>
+        <v>98.83883622924658</v>
       </c>
       <c r="L27" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M27" t="n">
-        <v>8.212886051148903</v>
+        <v>12.19615196156797</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.7817533208532002</v>
       </c>
       <c r="O27" t="n">
-        <v>3.656802884199994</v>
+        <v>9.765532184087471</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.816629923851119</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.221403653836721</v>
+        <v>7.611503232602359</v>
       </c>
       <c r="S27" t="n">
-        <v>2.174852473461062</v>
+        <v>4.584648728965611</v>
       </c>
       <c r="T27" t="n">
-        <v>37.73729705810547</v>
+        <v>17421.75142198801</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C007153</t>
+          <t>C010639</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>46.448861632499</v>
+        <v>70.54088757438478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Prescription=62.4 | Competition=0.0 | Population=98.4 | Road=0.0</t>
+          <t>Prescription=100.0 | Competition=63.1 | Population=98.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>21.84868702946253</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>18.93826130955282</v>
       </c>
       <c r="G28" t="n">
-        <v>24.60017460303647</v>
+        <v>29.4791488839376</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>62.42482008417867</v>
+        <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>63.12753769850939</v>
       </c>
       <c r="K28" t="n">
-        <v>98.40069841214589</v>
+        <v>98.26382961312534</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M28" t="n">
-        <v>8.697509933226396</v>
+        <v>15.26680285419346</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.8489389700982715</v>
       </c>
       <c r="O28" t="n">
-        <v>4.283134799675208</v>
+        <v>9.708720045964242</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.828603238305402</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.868906694920994</v>
+        <v>6.52143548395171</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>8.74536737024175</v>
       </c>
       <c r="T28" t="n">
-        <v>71.46725463867188</v>
+        <v>16459.51967893168</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C009276</t>
+          <t>C009251</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>46.00132372369897</v>
+        <v>70.290998890022</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2608,56 +2608,56 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Prescription=38.6 | Competition=0.0 | Population=100.0 | Road=75.0</t>
+          <t>Prescription=51.3 | Competition=0.0 | Population=98.8 | Road=75.0</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>13.50132372369897</v>
+        <v>25.64407197321786</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>25</v>
+        <v>29.64692691680414</v>
       </c>
       <c r="H29" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I29" t="n">
-        <v>38.57521063913993</v>
+        <v>51.28814394643572</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>98.82308972268048</v>
       </c>
       <c r="L29" t="n">
         <v>75</v>
       </c>
       <c r="M29" t="n">
-        <v>5.374597431883562</v>
+        <v>7.145861867602344</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.371524559764783</v>
+        <v>9.763976388587192</v>
       </c>
       <c r="P29" t="n">
         <v>3.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.689398157092578</v>
+        <v>0.8378481678454439</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.411657315832509</v>
       </c>
       <c r="S29" t="n">
-        <v>1.685199274790985</v>
+        <v>1.896356383924392</v>
       </c>
       <c r="T29" t="n">
-        <v>78.16423034667969</v>
+        <v>17394.66625867411</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -2671,11 +2671,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C010639</t>
+          <t>C007949</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45.61347133350648</v>
+        <v>69.91654764647946</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2684,56 +2684,56 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=63.1 | Population=98.2 | Road=50.0</t>
+          <t>Prescription=60.6 | Competition=0.0 | Population=98.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>30.29242608153729</v>
       </c>
       <c r="F30" t="n">
-        <v>18.93826130957106</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>24.55173264307755</v>
+        <v>29.62412156494217</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>100</v>
+        <v>60.58485216307459</v>
       </c>
       <c r="J30" t="n">
-        <v>63.1275376985702</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>98.20693057231018</v>
+        <v>98.74707188314056</v>
       </c>
       <c r="L30" t="n">
         <v>50</v>
       </c>
       <c r="M30" t="n">
-        <v>15.26680285426496</v>
+        <v>8.44115133662439</v>
       </c>
       <c r="N30" t="n">
-        <v>5.093633820589746</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.274700573178339</v>
+        <v>9.756465629791226</v>
       </c>
       <c r="P30" t="n">
         <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.437333420946562</v>
       </c>
       <c r="R30" t="n">
-        <v>6.521435483981919</v>
+        <v>3.003817915677828</v>
       </c>
       <c r="S30" t="n">
-        <v>8.745367370283038</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>70.85861968994141</v>
+        <v>17264.50103700254</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -2747,11 +2747,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C002749</t>
+          <t>C003250</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>45.41052252329797</v>
+        <v>69.29137184963902</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2760,64 +2760,64 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Prescription=37.9 | Competition=0.0 | Population=98.5 | Road=75.0</t>
+          <t>Prescription=58.9 | Competition=0.0 | Population=99.4 | Road=50.0</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>13.27859588568416</v>
+        <v>29.4732594759771</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>24.63192663761381</v>
+        <v>29.81811237366192</v>
       </c>
       <c r="H31" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>37.93884538766903</v>
+        <v>58.9465189519542</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>98.52770655045524</v>
+        <v>99.39370791220641</v>
       </c>
       <c r="L31" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M31" t="n">
-        <v>5.285934091110377</v>
+        <v>8.212886051142455</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.288663144349717</v>
+        <v>9.820354938833541</v>
       </c>
       <c r="P31" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.285934091110377</v>
+        <v>3.816629923843446</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.221403653830972</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.174852473468039</v>
       </c>
       <c r="T31" t="n">
-        <v>71.86898803710938</v>
+        <v>18403.58208278567</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>45.19814001045243</v>
+        <v>68.26770305470269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2836,56 +2836,56 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Prescription=56.9 | Competition=0.0 | Population=81.2 | Road=50.0</t>
+          <t>Prescription=56.9 | Competition=0.0 | Population=99.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>19.89907236321378</v>
+        <v>28.42724623314212</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>20.29906764723866</v>
+        <v>29.84045682156058</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>56.85449246632508</v>
+        <v>56.85449246628423</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>81.19627058895463</v>
+        <v>99.46818940520194</v>
       </c>
       <c r="L32" t="n">
         <v>50</v>
       </c>
       <c r="M32" t="n">
-        <v>7.921408701019788</v>
+        <v>7.921408701024738</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.534269347426393</v>
+        <v>9.827713902624653</v>
       </c>
       <c r="P32" t="n">
         <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.440739442429406</v>
+        <v>5.44073944244955</v>
       </c>
       <c r="R32" t="n">
-        <v>2.480669258590382</v>
+        <v>2.480669258575189</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>33.26996612548828</v>
+        <v>18539.52030467987</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -2899,11 +2899,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C007221</t>
+          <t>C009257</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>44.47751858461215</v>
+        <v>66.2552138689188</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2912,150 +2912,150 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Prescription=48.0 | Competition=0.0 | Population=90.7 | Road=50.0</t>
+          <t>Prescription=43.0 | Competition=0.0 | Population=99.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>16.79369801097107</v>
+        <v>21.47670636021478</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>22.68382057364108</v>
+        <v>29.77850750870402</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I33" t="n">
-        <v>47.9819943170602</v>
+        <v>42.95341272042957</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>90.73528229456431</v>
+        <v>99.26169169568007</v>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M33" t="n">
-        <v>6.685223467618975</v>
+        <v>5.984602491423046</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.949478524292997</v>
+        <v>9.807311395824604</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.629728717812311</v>
+        <v>5.984602491423046</v>
       </c>
       <c r="R33" t="n">
-        <v>1.055494749806664</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>50.90829086303711</v>
+        <v>18165.07996259257</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C005092</t>
+          <t>C002764</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>43.03412109582057</v>
+        <v>66.12482212584906</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Prescription=51.6 | Competition=0.0 | Population=79.9 | Road=50.0</t>
+          <t>Prescription=100.0 | Competition=94.9 | Population=98.6 | Road=75.0</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>18.04774255974857</v>
+        <v>50</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>28.46350815275157</v>
       </c>
       <c r="G34" t="n">
-        <v>19.986378536072</v>
+        <v>29.58833027860063</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I34" t="n">
-        <v>51.56497874213879</v>
+        <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>94.87836050917188</v>
       </c>
       <c r="K34" t="n">
-        <v>79.945514144288</v>
+        <v>98.62776759533543</v>
       </c>
       <c r="L34" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M34" t="n">
-        <v>7.184432637716602</v>
+        <v>14.00106013226523</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.275923956355592</v>
       </c>
       <c r="O34" t="n">
-        <v>3.479827066624365</v>
+        <v>9.744678058157355</v>
       </c>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>7.77655997757646</v>
       </c>
       <c r="R34" t="n">
-        <v>2.641167798163308</v>
+        <v>3.293456866629568</v>
       </c>
       <c r="S34" t="n">
-        <v>4.543264839553295</v>
+        <v>2.931043288059203</v>
       </c>
       <c r="T34" t="n">
-        <v>31.45410919189453</v>
+        <v>17062.17750100046</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C001396</t>
+          <t>C005092</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>42.86265542999502</v>
+        <v>65.48089861320693</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3064,150 +3064,150 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Prescription=29.6 | Competition=0.0 | Population=100.0 | Road=75.0</t>
+          <t>Prescription=51.6 | Competition=0.0 | Population=99.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10.36265542999501</v>
+        <v>25.78248937095341</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>25</v>
+        <v>29.69840924225353</v>
       </c>
       <c r="H35" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
-        <v>29.6075869428429</v>
+        <v>51.56497874190682</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>98.99469747417842</v>
       </c>
       <c r="L35" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M35" t="n">
-        <v>4.125158569732197</v>
+        <v>7.184432637693934</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.436695914981709</v>
+        <v>9.78093167746175</v>
       </c>
       <c r="P35" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.125158569732197</v>
+        <v>2.641167798158019</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4.543264839535915</v>
       </c>
       <c r="T35" t="n">
-        <v>83.49530029296875</v>
+        <v>17692.12946632504</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C013609</t>
+          <t>C009209</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>42.74259460910534</v>
+        <v>64.2383381224187</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Prescription=51.6 | Competition=0.0 | Population=98.7 | Road=0.0</t>
+          <t>Prescription=100.0 | Competition=100.0 | Population=97.5 | Road=75.0</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>18.06289490015254</v>
+        <v>50</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G36" t="n">
-        <v>24.6796997089528</v>
+        <v>29.2383381224187</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I36" t="n">
-        <v>51.60827114329297</v>
+        <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36" t="n">
-        <v>98.7187988358112</v>
+        <v>97.46112707472899</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M36" t="n">
-        <v>7.190464470704891</v>
+        <v>15.95500318165793</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.443805585404594</v>
       </c>
       <c r="O36" t="n">
-        <v>4.296980910692486</v>
+        <v>9.629410962895143</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>11.2943478230163</v>
       </c>
       <c r="R36" t="n">
-        <v>4.265947898143581</v>
+        <v>2.860216053513301</v>
       </c>
       <c r="S36" t="n">
-        <v>2.92451657256131</v>
+        <v>1.800439305128325</v>
       </c>
       <c r="T36" t="n">
-        <v>72.47762298583984</v>
+        <v>15204.47687860392</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C001844</t>
+          <t>C007221</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>42.74100470540596</v>
+        <v>63.34749969681642</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -3216,56 +3216,56 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Prescription=42.3 | Competition=0.0 | Population=91.7 | Road=50.0</t>
+          <t>Prescription=48.0 | Competition=0.0 | Population=97.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>14.81946861929645</v>
+        <v>23.99099715849901</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>22.9215360861095</v>
+        <v>29.35650253831741</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>42.34133891227557</v>
+        <v>47.98199431699801</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>91.68614434443802</v>
+        <v>97.85500846105805</v>
       </c>
       <c r="L37" t="n">
         <v>50</v>
       </c>
       <c r="M37" t="n">
-        <v>5.899323622863868</v>
+        <v>6.685223467619291</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.990867156703372</v>
+        <v>9.6683274607178</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.899323622863868</v>
+        <v>5.62972871780407</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.055494749815221</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>53.10178375244141</v>
+        <v>15807.88591668569</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -3279,11 +3279,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C004536</t>
+          <t>C002908</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>42.69611825115366</v>
+        <v>62.84938997479763</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -3292,74 +3292,74 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Prescription=50.6 | Competition=0.0 | Population=100.0 | Road=0.0</t>
+          <t>Prescription=45.9 | Competition=0.0 | Population=99.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>17.69611825115366</v>
+        <v>22.92670745172741</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>25</v>
+        <v>29.92268252307023</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>50.56033786043904</v>
+        <v>45.85341490345481</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>100</v>
+        <v>99.74227507690075</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M38" t="n">
-        <v>7.044458280784118</v>
+        <v>6.388653280184019</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.426420976109486</v>
+        <v>9.85479427457444</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.390529231774066</v>
       </c>
       <c r="R38" t="n">
-        <v>2.884034236427663</v>
+        <v>1.998124048409953</v>
       </c>
       <c r="S38" t="n">
-        <v>4.160424044356455</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>82.63156127929688</v>
+        <v>19048.46458859742</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C000644</t>
+          <t>C011172</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>42.51186752887152</v>
+        <v>62.37128730507963</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -3368,117 +3368,117 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Prescription=53.0 | Competition=0.0 | Population=75.9 | Road=50.0</t>
+          <t>Prescription=34.8 | Competition=0.0 | Population=99.9 | Road=75.0</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>18.53531770294905</v>
+        <v>17.38816282473398</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>18.97654982592247</v>
+        <v>29.98312448034565</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I39" t="n">
-        <v>52.95805057985442</v>
+        <v>34.77632564946796</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>75.90619930368989</v>
+        <v>99.94374826781885</v>
       </c>
       <c r="L39" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M39" t="n">
-        <v>7.37852620706756</v>
+        <v>4.845307321188884</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.304005855598542</v>
+        <v>9.874700345965021</v>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.424949195382705</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.953577011684855</v>
+        <v>1.9243211746728</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.920986146516084</v>
       </c>
       <c r="T39" t="n">
-        <v>26.22146606445312</v>
+        <v>19431.46395003796</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C002290</t>
+          <t>C000328</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>42.18564171419526</v>
+        <v>61.97121381734134</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Prescription=40.5 | Competition=0.0 | Population=92.0 | Road=50.0</t>
+          <t>Prescription=88.7 | Competition=73.6 | Population=99.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>14.18679431316879</v>
+        <v>44.34733197227181</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>22.08762898727569</v>
       </c>
       <c r="G40" t="n">
-        <v>22.99884740102647</v>
+        <v>29.71151083234522</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>40.53369803762513</v>
+        <v>88.69466394454362</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>73.62542995758564</v>
       </c>
       <c r="K40" t="n">
-        <v>91.99538960410588</v>
+        <v>99.03836944115072</v>
       </c>
       <c r="L40" t="n">
         <v>50</v>
       </c>
       <c r="M40" t="n">
-        <v>5.647469081004117</v>
+        <v>12.3576282581613</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>0.9901145991111744</v>
       </c>
       <c r="O40" t="n">
-        <v>4.004327824713779</v>
+        <v>9.785246580543179</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
@@ -3487,13 +3487,13 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.382385358840881</v>
+        <v>6.00119638931078</v>
       </c>
       <c r="S40" t="n">
-        <v>3.265083722163237</v>
+        <v>6.356431868850521</v>
       </c>
       <c r="T40" t="n">
-        <v>53.83495330810547</v>
+        <v>17768.63855111599</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -3507,11 +3507,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C003482</t>
+          <t>C009739</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>42.16729634962339</v>
+        <v>61.85830913674079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -3520,74 +3520,74 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Prescription=50.4 | Competition=0.0 | Population=98.2 | Road=0.0</t>
+          <t>Prescription=36.6 | Competition=0.0 | Population=95.2 | Road=75.0</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>17.62488291390111</v>
+        <v>18.30109074275167</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>24.54241343572228</v>
+        <v>28.55721839398911</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I41" t="n">
-        <v>50.35680832543176</v>
+        <v>36.60218148550334</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>98.16965374288911</v>
+        <v>95.19072797996371</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M41" t="n">
-        <v>7.016100967938944</v>
+        <v>5.099699712695404</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4.27307800659201</v>
+        <v>9.405089671017237</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.77119842704059</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.244902540898354</v>
+        <v>5.099699712695404</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>70.74211883544922</v>
+        <v>12149.06345048547</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C008680</t>
+          <t>C005060</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41.81832050009496</v>
+        <v>61.16012455899661</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -3596,74 +3596,74 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Prescription=51.3 | Competition=0.0 | Population=95.4 | Road=0.0</t>
+          <t>Prescription=34.4 | Competition=0.0 | Population=96.5 | Road=75.0</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>17.96553831185908</v>
+        <v>17.19610595384018</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>23.85278218823589</v>
+        <v>28.96401860515643</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I42" t="n">
-        <v>51.33010946245451</v>
+        <v>34.39221190768037</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>95.41112875294354</v>
+        <v>96.54672868385477</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M42" t="n">
-        <v>7.151708828656214</v>
+        <v>4.791789616529331</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>4.153006354958781</v>
+        <v>9.539066041244622</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.388515065028164</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.927708767381317</v>
       </c>
       <c r="S42" t="n">
-        <v>1.76319376362805</v>
+        <v>1.864080849148014</v>
       </c>
       <c r="T42" t="n">
-        <v>62.62499237060547</v>
+        <v>13890.96703961119</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C003341</t>
+          <t>C001844</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41.65864806682673</v>
+        <v>61.0298514376488</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -3672,56 +3672,56 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Prescription=41.1 | Competition=0.0 | Population=89.1 | Road=50.0</t>
+          <t>Prescription=42.3 | Competition=0.0 | Population=99.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>14.39213214123901</v>
+        <v>21.17066945612485</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>22.26651592558771</v>
+        <v>29.85918198152395</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>41.12037754639718</v>
+        <v>42.3413389122497</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>89.06606370235086</v>
+        <v>99.53060660507984</v>
       </c>
       <c r="L43" t="n">
         <v>50</v>
       </c>
       <c r="M43" t="n">
-        <v>5.729209818875439</v>
+        <v>5.899323622868189</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.876821639169793</v>
+        <v>9.833880883110284</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.528969473397168</v>
+        <v>5.899323622868189</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.200240345478271</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>47.27054977416992</v>
+        <v>18654.21262073517</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -3735,11 +3735,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C011052</t>
+          <t>C002094</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.31074579714926</v>
+        <v>59.96837693156382</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -3748,56 +3748,56 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Prescription=43.5 | Competition=0.0 | Population=84.3 | Road=50.0</t>
+          <t>Prescription=39.9 | Competition=0.0 | Population=100.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>15.22922696349521</v>
+        <v>19.96837693156382</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>21.08151883365405</v>
+        <v>30</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>43.51207703855773</v>
+        <v>39.93675386312765</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>84.32607533461621</v>
+        <v>100</v>
       </c>
       <c r="L44" t="n">
         <v>50</v>
       </c>
       <c r="M44" t="n">
-        <v>6.062439935715313</v>
+        <v>5.564298190326248</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.67050187258779</v>
+        <v>9.894042700985699</v>
       </c>
       <c r="P44" t="n">
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5.564298190326248</v>
       </c>
       <c r="R44" t="n">
-        <v>3.458027088468519</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.604412847246794</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>38.27161026000977</v>
+        <v>19810.99221938476</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -3811,87 +3811,87 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C009739</t>
+          <t>C000562</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41.06559688268784</v>
+        <v>59.89577065201719</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Prescription=36.6 | Competition=0.0 | Population=83.0 | Road=75.0</t>
+          <t>Prescription=100.0 | Competition=100.0 | Population=99.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12.81076351994144</v>
+        <v>50</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G45" t="n">
-        <v>20.7548333627464</v>
+        <v>29.89577065201719</v>
       </c>
       <c r="H45" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>36.60218148554698</v>
+        <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
-        <v>83.01933345098558</v>
+        <v>99.6525688400573</v>
       </c>
       <c r="L45" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M45" t="n">
-        <v>5.099699712694632</v>
+        <v>37.99994366855236</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.44479172646265</v>
       </c>
       <c r="O45" t="n">
-        <v>3.613622686501845</v>
+        <v>9.8459310667866</v>
       </c>
       <c r="P45" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>5.099699712694632</v>
+        <v>4.126538382559117</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>33.87340528599324</v>
       </c>
       <c r="T45" t="n">
-        <v>36.10021209716797</v>
+        <v>18880.37124919891</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C009728</t>
+          <t>C002290</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>40.74274441212144</v>
+        <v>59.72320503726518</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3900,74 +3900,74 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Prescription=27.7 | Competition=0.0 | Population=94.2 | Road=75.0</t>
+          <t>Prescription=40.5 | Competition=0.0 | Population=98.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9.697990982384914</v>
+        <v>20.26684901887394</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>23.54475342973653</v>
+        <v>29.45635601839124</v>
       </c>
       <c r="H46" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I46" t="n">
-        <v>27.7085456639569</v>
+        <v>40.53369803774789</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>94.17901371894611</v>
+        <v>98.18785339463746</v>
       </c>
       <c r="L46" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M46" t="n">
-        <v>3.860569414898508</v>
+        <v>5.647469081028808</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.099375487856459</v>
+        <v>9.701213399435666</v>
       </c>
       <c r="P46" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.860569414898508</v>
+        <v>2.382385358838703</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.265083722190105</v>
       </c>
       <c r="T46" t="n">
-        <v>59.30261611938477</v>
+        <v>16336.41899075918</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C000343</t>
+          <t>C004254</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>40.39411103454712</v>
+        <v>59.58766985912721</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3976,56 +3976,56 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Prescription=34.1 | Competition=0.0 | Population=93.8 | Road=50.0</t>
+          <t>Prescription=46.1 | Competition=10.3 | Population=98.8 | Road=50.0</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>11.94543289494654</v>
+        <v>23.03460931790218</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>3.088212433013926</v>
       </c>
       <c r="G47" t="n">
-        <v>23.44867813960058</v>
+        <v>29.64127297423896</v>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I47" t="n">
-        <v>34.12980827127583</v>
+        <v>46.06921863580436</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>10.29404144337975</v>
       </c>
       <c r="K47" t="n">
-        <v>93.79471255840234</v>
+        <v>98.80424324746319</v>
       </c>
       <c r="L47" t="n">
         <v>50</v>
       </c>
       <c r="M47" t="n">
-        <v>4.755229507401785</v>
+        <v>6.418720729368638</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>0.1384342437499836</v>
       </c>
       <c r="O47" t="n">
-        <v>4.08264782534144</v>
+        <v>9.762114308181225</v>
       </c>
       <c r="P47" t="n">
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.022785326912935</v>
       </c>
       <c r="R47" t="n">
-        <v>2.827951706315079</v>
+        <v>2.395935402455703</v>
       </c>
       <c r="S47" t="n">
-        <v>1.927277801086707</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>58.30228424072266</v>
+        <v>17362.30426904932</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -4039,87 +4039,87 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C009010</t>
+          <t>C001535</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>40.20483443779532</v>
+        <v>59.54607531040445</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Prescription=69.3 | Competition=35.6 | Population=86.5 | Road=50.0</t>
+          <t>Prescription=30.4 | Competition=0.0 | Population=97.9 | Road=75.0</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>24.25788075962127</v>
+        <v>15.17720678069678</v>
       </c>
       <c r="F48" t="n">
-        <v>10.6792853241599</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>21.62623900233395</v>
+        <v>29.36886852970768</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I48" t="n">
-        <v>69.30823074177506</v>
+        <v>30.35441356139356</v>
       </c>
       <c r="J48" t="n">
-        <v>35.59761774719968</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>86.50495600933581</v>
+        <v>97.89622843235892</v>
       </c>
       <c r="L48" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M48" t="n">
-        <v>9.656560075272292</v>
+        <v>4.229212244614044</v>
       </c>
       <c r="N48" t="n">
-        <v>2.872300050025061</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.765343065717771</v>
+        <v>9.672400100296763</v>
       </c>
       <c r="P48" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.872794764559936</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.821195878400136</v>
+        <v>2.525406693927321</v>
       </c>
       <c r="S48" t="n">
-        <v>0.9625694323122199</v>
+        <v>1.703805550686723</v>
       </c>
       <c r="T48" t="n">
-        <v>42.17851638793945</v>
+        <v>15872.40109553188</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C001486</t>
+          <t>C001396</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>39.57920744410765</v>
+        <v>59.11323370350171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -4128,74 +4128,74 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Prescription=35.6 | Competition=0.0 | Population=88.5 | Road=50.0</t>
+          <t>Prescription=29.6 | Competition=0.0 | Population=97.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>12.46650123337507</v>
+        <v>14.80379347146088</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>22.11270621073258</v>
+        <v>29.30944023204082</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I49" t="n">
-        <v>35.61857495250022</v>
+        <v>29.60758694292176</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>88.4508248429303</v>
+        <v>97.69813410680275</v>
       </c>
       <c r="L49" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M49" t="n">
-        <v>4.962656024302349</v>
+        <v>4.125158569748727</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.85004183972305</v>
+        <v>9.652827869526897</v>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.740583577744701</v>
+        <v>4.125158569748727</v>
       </c>
       <c r="S49" t="n">
-        <v>2.222072446557649</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>45.99502944946289</v>
+        <v>15564.74381699786</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C013790</t>
+          <t>C001516</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>39.48971452117198</v>
+        <v>58.7085146518535</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -4204,74 +4204,74 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Prescription=30.9 | Competition=0.0 | Population=94.8 | Road=50.0</t>
+          <t>Prescription=27.4 | Competition=0.0 | Population=100.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10.80155672942695</v>
+        <v>13.7085146518535</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>23.68815779174503</v>
+        <v>30</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I50" t="n">
-        <v>30.86159065550558</v>
+        <v>27.417029303707</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>94.75263116698014</v>
+        <v>100</v>
       </c>
       <c r="L50" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M50" t="n">
-        <v>4.299876089662234</v>
+        <v>3.819953095376368</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.124343611996036</v>
+        <v>9.939894145694375</v>
       </c>
       <c r="P50" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>4.299876089662234</v>
+        <v>2.650154762354886</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.169798333021482</v>
       </c>
       <c r="T50" t="n">
-        <v>60.82721328735352</v>
+        <v>20740.54858732224</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C001365</t>
+          <t>C005441</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>39.34963984517759</v>
+        <v>58.51939566970786</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -4280,74 +4280,74 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Prescription=59.8 | Competition=15.4 | Population=92.2 | Road=0.0</t>
+          <t>Prescription=44.8 | Competition=10.4 | Population=97.5 | Road=50.0</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>20.92019089591231</v>
+        <v>22.38284499014633</v>
       </c>
       <c r="F51" t="n">
-        <v>4.619880959531804</v>
+        <v>3.116706617394537</v>
       </c>
       <c r="G51" t="n">
-        <v>23.04932990879709</v>
+        <v>29.25325729695606</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I51" t="n">
-        <v>59.77197398832087</v>
+        <v>44.76568998029266</v>
       </c>
       <c r="J51" t="n">
-        <v>15.39960319843935</v>
+        <v>10.38902205798179</v>
       </c>
       <c r="K51" t="n">
-        <v>92.19731963518835</v>
+        <v>97.51085765652022</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M51" t="n">
-        <v>8.327894846808359</v>
+        <v>6.237103010418305</v>
       </c>
       <c r="N51" t="n">
-        <v>1.242562953267371</v>
+        <v>0.139711542819126</v>
       </c>
       <c r="O51" t="n">
-        <v>4.013117330857386</v>
+        <v>9.634324472761744</v>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.575962790427726</v>
+        <v>6.237103010418305</v>
       </c>
       <c r="S51" t="n">
-        <v>5.751932056380634</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>54.31904983520508</v>
+        <v>15279.37298998237</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C000822</t>
+          <t>C009728</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>39.24357790950415</v>
+        <v>58.31321077413084</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -4356,41 +4356,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Prescription=21.5 | Competition=0.0 | Population=96.9 | Road=75.0</t>
+          <t>Prescription=27.7 | Competition=0.0 | Population=98.2 | Road=75.0</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>7.515472369994811</v>
+        <v>13.85427283195593</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>24.22810553950935</v>
+        <v>29.45893794217491</v>
       </c>
       <c r="H52" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I52" t="n">
-        <v>21.47277819998518</v>
+        <v>27.70854566391186</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>96.91242215803739</v>
+        <v>98.1964598072497</v>
       </c>
       <c r="L52" t="n">
         <v>75</v>
       </c>
       <c r="M52" t="n">
-        <v>2.991753943968063</v>
+        <v>3.860569414897419</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.218353879230892</v>
+        <v>9.702063735220269</v>
       </c>
       <c r="P52" t="n">
         <v>3.5</v>
@@ -4399,13 +4399,13 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.860569414897419</v>
       </c>
       <c r="S52" t="n">
-        <v>2.991753943968063</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>66.92158508300781</v>
+        <v>16350.31719098613</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -4419,11 +4419,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C004503</t>
+          <t>C000421</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>39.02728200866012</v>
+        <v>58.26315755329703</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -4432,74 +4432,74 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Prescription=28.4 | Competition=0.0 | Population=96.3 | Road=50.0</t>
+          <t>Prescription=57.1 | Competition=0.0 | Population=99.1 | Road=0.0</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>9.953769935313051</v>
+        <v>28.54564918342075</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>24.07351207334706</v>
+        <v>29.71750836987628</v>
       </c>
       <c r="H53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>28.43934267232301</v>
+        <v>57.09129836684149</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>96.29404829338826</v>
+        <v>99.05836123292096</v>
       </c>
       <c r="L53" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.962389720201196</v>
+        <v>7.95440233512042</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.191437620895052</v>
+        <v>9.787221821181353</v>
       </c>
       <c r="P53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.530708245784684</v>
+        <v>5.209290742666536</v>
       </c>
       <c r="S53" t="n">
-        <v>1.431681474416512</v>
+        <v>2.745111592453885</v>
       </c>
       <c r="T53" t="n">
-        <v>65.11777496337891</v>
+        <v>17803.77255093679</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C001388</t>
+          <t>C001598</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>39.00021125014148</v>
+        <v>57.88722023537326</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -4508,74 +4508,74 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Prescription=26.5 | Competition=0.0 | Population=98.9 | Road=50.0</t>
+          <t>Prescription=40.9 | Competition=0.0 | Population=74.9 | Road=75.0</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>9.276091828277785</v>
+        <v>20.42890808091994</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>24.72411942186369</v>
+        <v>22.45831215445332</v>
       </c>
       <c r="H54" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I54" t="n">
-        <v>26.5031195093651</v>
+        <v>40.85781616183989</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>98.89647768745476</v>
+        <v>74.86104051484442</v>
       </c>
       <c r="L54" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M54" t="n">
-        <v>3.692620096995865</v>
+        <v>5.692627731066264</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>4.304714824017505</v>
+        <v>7.396464065869566</v>
       </c>
       <c r="P54" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.692620096995865</v>
+        <v>5.692627731066264</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>73.048095703125</v>
+        <v>1629.209911987185</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C005441</t>
+          <t>C001486</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>38.79071834580276</v>
+        <v>57.79514289158504</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -4584,41 +4584,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Prescription=44.8 | Competition=10.4 | Population=85.0 | Road=50.0</t>
+          <t>Prescription=35.6 | Competition=0.0 | Population=100.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>15.66799149311814</v>
+        <v>17.80928747610628</v>
       </c>
       <c r="F55" t="n">
-        <v>3.116706617383964</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>21.23943347006858</v>
+        <v>29.98585541547876</v>
       </c>
       <c r="H55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I55" t="n">
-        <v>44.76568998033756</v>
+        <v>35.61857495221256</v>
       </c>
       <c r="J55" t="n">
-        <v>10.38902205794655</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>84.95773388027432</v>
+        <v>99.9528513849292</v>
       </c>
       <c r="L55" t="n">
         <v>50</v>
       </c>
       <c r="M55" t="n">
-        <v>6.237103010416181</v>
+        <v>4.962656024268938</v>
       </c>
       <c r="N55" t="n">
-        <v>0.8382692569111241</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.697996379660176</v>
+        <v>9.875599757436344</v>
       </c>
       <c r="P55" t="n">
         <v>3</v>
@@ -4627,13 +4627,13 @@
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>6.237103010416181</v>
+        <v>2.740583577726968</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.22207244654197</v>
       </c>
       <c r="T55" t="n">
-        <v>39.3663444519043</v>
+        <v>19448.94959324598</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -4647,11 +4647,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C002569</t>
+          <t>C008905</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>38.64984066377865</v>
+        <v>56.6546532237346</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -4660,56 +4660,56 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Prescription=27.5 | Competition=0.0 | Population=96.1 | Road=50.0</t>
+          <t>Prescription=41.9 | Competition=0.0 | Population=85.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>9.615723239804026</v>
+        <v>20.946221190776</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>24.03411742397462</v>
+        <v>25.70843203295859</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I56" t="n">
-        <v>27.47349497086865</v>
+        <v>41.89244238155201</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>96.13646969589848</v>
+        <v>85.69477344319532</v>
       </c>
       <c r="L56" t="n">
         <v>50</v>
       </c>
       <c r="M56" t="n">
-        <v>3.827820329916125</v>
+        <v>5.836779877776503</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.184578621055787</v>
+        <v>8.466864847807479</v>
       </c>
       <c r="P56" t="n">
         <v>3</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>5.836779877776503</v>
       </c>
       <c r="R56" t="n">
-        <v>3.827820329916125</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>64.66582489013672</v>
+        <v>4753.585728344508</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -4723,87 +4723,87 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C002822</t>
+          <t>C013107</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>38.53216135303814</v>
+        <v>56.53176147549148</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Prescription=69.6 | Competition=41.8 | Population=76.9 | Road=75.0</t>
+          <t>Prescription=49.6 | Competition=12.6 | Population=85.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>24.35476603309433</v>
+        <v>24.81702688055484</v>
       </c>
       <c r="F57" t="n">
-        <v>12.54310385566123</v>
+        <v>3.77480531160157</v>
       </c>
       <c r="G57" t="n">
-        <v>19.22049917560504</v>
+        <v>25.48953990653821</v>
       </c>
       <c r="H57" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I57" t="n">
-        <v>69.58504580884095</v>
+        <v>49.63405376110968</v>
       </c>
       <c r="J57" t="n">
-        <v>41.81034618553743</v>
+        <v>12.58268437200523</v>
       </c>
       <c r="K57" t="n">
-        <v>76.88199670242017</v>
+        <v>84.96513302179402</v>
       </c>
       <c r="L57" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M57" t="n">
-        <v>9.695128096649457</v>
+        <v>6.915401198305339</v>
       </c>
       <c r="N57" t="n">
-        <v>3.373592589625787</v>
+        <v>0.1692119081668849</v>
       </c>
       <c r="O57" t="n">
-        <v>3.346479861000707</v>
+        <v>8.394774490516351</v>
       </c>
       <c r="P57" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>5.961471408471607</v>
+        <v>6.915401198305339</v>
       </c>
       <c r="S57" t="n">
-        <v>3.73365668817785</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>27.4025764465332</v>
+        <v>4422.889168306254</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C002329</t>
+          <t>C002424</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>38.09134938011756</v>
+        <v>56.46909878372492</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4812,47 +4812,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Prescription=35.9 | Competition=0.0 | Population=82.2 | Road=50.0</t>
+          <t>Prescription=40.5 | Competition=14.1 | Population=84.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>12.54873600165587</v>
+        <v>20.26686671617629</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>4.220285479082733</v>
       </c>
       <c r="G58" t="n">
-        <v>20.5426133784617</v>
+        <v>25.42251754663137</v>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I58" t="n">
-        <v>35.85353143330249</v>
+        <v>40.53373343235258</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>14.06761826360911</v>
       </c>
       <c r="K58" t="n">
-        <v>82.17045351384678</v>
+        <v>84.74172515543789</v>
       </c>
       <c r="L58" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M58" t="n">
-        <v>4.995391982898593</v>
+        <v>5.647474012479559</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>0.1891812954511284</v>
       </c>
       <c r="O58" t="n">
-        <v>3.576673078844827</v>
+        <v>8.372701216565424</v>
       </c>
       <c r="P58" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.995391982898593</v>
+        <v>5.647474012479559</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -4861,71 +4861,71 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>34.75439071655273</v>
+        <v>4326.309289178811</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C003299</t>
+          <t>C010158</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>37.81954518677505</v>
+        <v>56.46021424136109</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Prescription=25.3 | Competition=0.0 | Population=95.9 | Road=50.0</t>
+          <t>Prescription=66.3 | Competition=71.5 | Population=99.2 | Road=75.0</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>8.839797733457514</v>
+        <v>33.15490642203208</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>21.45823885203197</v>
       </c>
       <c r="G59" t="n">
-        <v>23.97974745331754</v>
+        <v>29.76354667136097</v>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I59" t="n">
-        <v>25.25656495273575</v>
+        <v>66.30981284406417</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>71.52746284010657</v>
       </c>
       <c r="K59" t="n">
-        <v>95.91898981327014</v>
+        <v>99.2118222378699</v>
       </c>
       <c r="L59" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M59" t="n">
-        <v>3.518940451240022</v>
+        <v>9.238797246106541</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>0.9619011425287426</v>
       </c>
       <c r="O59" t="n">
-        <v>4.175112269001931</v>
+        <v>9.802384164648807</v>
       </c>
       <c r="P59" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4934,28 +4934,28 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>3.518940451240022</v>
+        <v>9.238797246106541</v>
       </c>
       <c r="T59" t="n">
-        <v>64.04714202880859</v>
+        <v>18075.79163980484</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C011102</t>
+          <t>C001987</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>37.80840844228237</v>
+        <v>55.85950952169827</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -4964,74 +4964,74 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Prescription=27.1 | Competition=0.0 | Population=93.3 | Road=50.0</t>
+          <t>Prescription=22.7 | Competition=0.0 | Population=98.4 | Road=75.0</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>9.476269417403149</v>
+        <v>11.3285202836871</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>23.33213902487922</v>
+        <v>29.53098923801117</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I60" t="n">
-        <v>27.07505547829471</v>
+        <v>22.6570405673742</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>93.32855609951687</v>
+        <v>98.43663079337055</v>
       </c>
       <c r="L60" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M60" t="n">
-        <v>3.772306650585076</v>
+        <v>3.156754558952415</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.062357207659206</v>
+        <v>9.725793248680013</v>
       </c>
       <c r="P60" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.772306650585076</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>3.156754558952415</v>
       </c>
       <c r="T60" t="n">
-        <v>57.11112976074219</v>
+        <v>16742.96625340916</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C003004</t>
+          <t>C003455</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>37.64871107569115</v>
+        <v>55.70818370612109</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -5040,56 +5040,56 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Prescription=36.1 | Competition=0.0 | Population=100.0 | Road=0.0</t>
+          <t>Prescription=51.8 | Competition=0.0 | Population=99.4 | Road=0.0</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>12.64871107569115</v>
+        <v>25.88353043767973</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>25</v>
+        <v>29.82465326844135</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>36.13917450197472</v>
+        <v>51.76706087535947</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>100</v>
+        <v>99.41551089480451</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>5.035189989905803</v>
+        <v>7.2125882873324</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4.561027154691065</v>
+        <v>9.82250912980132</v>
       </c>
       <c r="P61" t="n">
         <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.035189989905803</v>
+        <v>5.946306353309759</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.266281934022641</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>94.68170928955078</v>
+        <v>18443.27180154249</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -5103,69 +5103,69 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C008633</t>
+          <t>C005972</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>37.5</v>
+        <v>55.70215727502463</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=100.0 | Population=100.0 | Road=75.0</t>
+          <t>Prescription=23.8 | Competition=0.0 | Population=96.0 | Road=75.0</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>35</v>
+        <v>11.89364993687806</v>
       </c>
       <c r="F62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>25</v>
+        <v>28.80850733814657</v>
       </c>
       <c r="H62" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I62" t="n">
-        <v>100</v>
+        <v>23.78729987375612</v>
       </c>
       <c r="J62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>100</v>
+        <v>96.02835779382191</v>
       </c>
       <c r="L62" t="n">
         <v>75</v>
       </c>
       <c r="M62" t="n">
-        <v>22.19732182271963</v>
+        <v>3.314231048770652</v>
       </c>
       <c r="N62" t="n">
-        <v>10.83004941088425</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.420808983391451</v>
+        <v>9.487849659071031</v>
       </c>
       <c r="P62" t="n">
         <v>3.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>11.49874588567654</v>
+        <v>2.341859880898093</v>
       </c>
       <c r="R62" t="n">
-        <v>5.665547634402373</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>5.033028302640711</v>
+        <v>0.9723711678725593</v>
       </c>
       <c r="T62" t="n">
-        <v>82.16353607177734</v>
+        <v>13197.38376551028</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -5179,87 +5179,87 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C004625</t>
+          <t>C004637</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>37.41435096544772</v>
+        <v>55.6729874345586</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Prescription=35.1 | Competition=0.0 | Population=80.5 | Road=50.0</t>
+          <t>Prescription=57.9 | Competition=0.0 | Population=89.2 | Road=0.0</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>12.29192908381521</v>
+        <v>28.92557192279456</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>20.1224218816325</v>
+        <v>26.74741551176404</v>
       </c>
       <c r="H63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>35.11979738232918</v>
+        <v>57.85114384558913</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>80.48968752653002</v>
+        <v>89.15805170588013</v>
       </c>
       <c r="L63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4.893162466048064</v>
+        <v>8.060269898538653</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.503513564669079</v>
+        <v>8.809045681040432</v>
       </c>
       <c r="P63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>5.260475422696256</v>
       </c>
       <c r="R63" t="n">
-        <v>2.952950685405072</v>
+        <v>2.799794475842398</v>
       </c>
       <c r="S63" t="n">
-        <v>1.940211780642993</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>32.23200988769531</v>
+        <v>6693.527503090911</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C001955</t>
+          <t>C003341</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>36.87377463890948</v>
+        <v>55.41609965891863</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -5268,132 +5268,132 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Prescription=13.7 | Competition=0.0 | Population=98.3 | Road=75.0</t>
+          <t>Prescription=41.1 | Competition=0.0 | Population=82.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4.808251466188355</v>
+        <v>20.56018877317097</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>24.56552317272112</v>
+        <v>24.85591088574767</v>
       </c>
       <c r="H64" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I64" t="n">
-        <v>13.73786133196673</v>
+        <v>41.12037754634193</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>98.26209269088449</v>
+        <v>82.85303628582555</v>
       </c>
       <c r="L64" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M64" t="n">
-        <v>1.914065354692957</v>
+        <v>5.729209818875439</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>4.277101641397385</v>
+        <v>8.186093880364622</v>
       </c>
       <c r="P64" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.528969473397168</v>
       </c>
       <c r="R64" t="n">
-        <v>1.135653399755299</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.7784119549376575</v>
+        <v>1.200240345478271</v>
       </c>
       <c r="T64" t="n">
-        <v>71.03136444091797</v>
+        <v>3589.669234357774</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C005411</t>
+          <t>C002429</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>36.68514102468049</v>
+        <v>55.29829979692706</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=100.0 | Population=96.7 | Road=75.0</t>
+          <t>Prescription=29.4 | Competition=0.0 | Population=85.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>35</v>
+        <v>14.71138051635959</v>
       </c>
       <c r="F65" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>24.18514102468049</v>
+        <v>25.58691928056747</v>
       </c>
       <c r="H65" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I65" t="n">
-        <v>100</v>
+        <v>29.42276103271919</v>
       </c>
       <c r="J65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>96.74056409872196</v>
+        <v>85.2897309352249</v>
       </c>
       <c r="L65" t="n">
         <v>75</v>
       </c>
       <c r="M65" t="n">
-        <v>16.63706737083361</v>
+        <v>4.099407190926346</v>
       </c>
       <c r="N65" t="n">
-        <v>15.15448157485586</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>4.210873330349262</v>
+        <v>8.426845602352843</v>
       </c>
       <c r="P65" t="n">
         <v>3.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>12.0096763342439</v>
+        <v>4.099407190926346</v>
       </c>
       <c r="R65" t="n">
-        <v>2.993790673287788</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>1.633600363301921</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>66.41539001464844</v>
+        <v>4567.067839949392</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -5407,11 +5407,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C010347</t>
+          <t>C001365</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>36.49877042085333</v>
+        <v>55.26610603463652</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -5420,56 +5420,56 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Prescription=35.0 | Competition=0.0 | Population=97.1 | Road=0.0</t>
+          <t>Prescription=59.8 | Competition=15.4 | Population=100.0 | Road=0.0</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12.23578083824733</v>
+        <v>29.88598699414779</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>4.619880959511267</v>
       </c>
       <c r="G66" t="n">
-        <v>24.262989582606</v>
+        <v>30</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>34.95937382356381</v>
+        <v>59.77197398829557</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>15.39960319837089</v>
       </c>
       <c r="K66" t="n">
-        <v>97.05195833042401</v>
+        <v>100</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.870811012026991</v>
+        <v>8.327894846816022</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>0.2070938255438359</v>
       </c>
       <c r="O66" t="n">
-        <v>4.224427537704934</v>
+        <v>9.978464683357261</v>
       </c>
       <c r="P66" t="n">
         <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.262233086451984</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.608577925575007</v>
+        <v>2.575962790423339</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>5.751932056392683</v>
       </c>
       <c r="T66" t="n">
-        <v>67.33537292480469</v>
+        <v>21556.19001682103</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -5483,87 +5483,87 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C013107</t>
+          <t>C007182</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>36.07606685022124</v>
+        <v>55.25560503563615</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Prescription=49.6 | Competition=12.6 | Population=69.9 | Road=50.0</t>
+          <t>Prescription=99.7 | Competition=69.7 | Population=87.7 | Road=0.0</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>17.37191881644968</v>
+        <v>49.87196904187799</v>
       </c>
       <c r="F67" t="n">
-        <v>3.774805311591686</v>
+        <v>20.92171801228825</v>
       </c>
       <c r="G67" t="n">
-        <v>17.47895334536324</v>
+        <v>26.30535400604641</v>
       </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>49.6340537612848</v>
+        <v>99.74393808375598</v>
       </c>
       <c r="J67" t="n">
-        <v>12.58268437197229</v>
+        <v>69.73906004096084</v>
       </c>
       <c r="K67" t="n">
-        <v>69.91581338145298</v>
+        <v>87.68451335348803</v>
       </c>
       <c r="L67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>6.915401198320448</v>
+        <v>13.89709879970679</v>
       </c>
       <c r="N67" t="n">
-        <v>1.015271448997697</v>
+        <v>0.9378507061299934</v>
       </c>
       <c r="O67" t="n">
-        <v>3.043259429800305</v>
+        <v>8.663456287703218</v>
       </c>
       <c r="P67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>10.23535253588912</v>
       </c>
       <c r="R67" t="n">
-        <v>6.915401198320448</v>
+        <v>3.661746263817668</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>19.9734935760498</v>
+        <v>5786.503410625271</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="V67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C000355</t>
+          <t>C013790</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>36.07553761850385</v>
+        <v>55.10724552497056</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -5572,41 +5572,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Prescription=20.8 | Competition=0.0 | Population=95.1 | Road=50.0</t>
+          <t>Prescription=30.9 | Competition=0.0 | Population=98.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>7.290425038973381</v>
+        <v>15.43079532772197</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>23.78511257953047</v>
+        <v>29.67645019724859</v>
       </c>
       <c r="H68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I68" t="n">
-        <v>20.82978582563823</v>
+        <v>30.86159065544394</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>95.14045031812188</v>
+        <v>98.9215006574953</v>
       </c>
       <c r="L68" t="n">
         <v>50</v>
       </c>
       <c r="M68" t="n">
-        <v>2.902167261053638</v>
+        <v>4.299876089659422</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.14122440378959</v>
+        <v>9.773699643006854</v>
       </c>
       <c r="P68" t="n">
         <v>3</v>
@@ -5615,13 +5615,13 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.902167261053638</v>
+        <v>4.299876089659422</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>61.87976455688477</v>
+        <v>17564.63372689299</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -5635,11 +5635,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C002215</t>
+          <t>C004477</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>35.8657147424714</v>
+        <v>54.63415939905781</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -5648,41 +5648,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Prescription=26.0 | Competition=0.0 | Population=87.0 | Road=50.0</t>
+          <t>Prescription=29.7 | Competition=0.0 | Population=99.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>9.117341635512179</v>
+        <v>14.84325545089336</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>21.74837310695922</v>
+        <v>29.79090394816445</v>
       </c>
       <c r="H69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I69" t="n">
-        <v>26.0495475300348</v>
+        <v>29.68651090178671</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>86.99349242783687</v>
+        <v>99.30301316054818</v>
       </c>
       <c r="L69" t="n">
         <v>50</v>
       </c>
       <c r="M69" t="n">
-        <v>3.629424932150556</v>
+        <v>4.136154867619874</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.78660782672817</v>
+        <v>9.811394063230027</v>
       </c>
       <c r="P69" t="n">
         <v>3</v>
@@ -5691,13 +5691,13 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.629424932150556</v>
+        <v>2.737857030775212</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1.398297836844663</v>
       </c>
       <c r="T69" t="n">
-        <v>43.10652923583984</v>
+        <v>18239.39762906916</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -5711,11 +5711,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C000129</t>
+          <t>C008423</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>35.77118919006131</v>
+        <v>54.44666301342273</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -5724,74 +5724,74 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Prescription=18.2 | Competition=0.0 | Population=87.6 | Road=75.0</t>
+          <t>Prescription=20.4 | Competition=0.0 | Population=80.8 | Road=100.0</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6.377408764538267</v>
+        <v>10.20158031496233</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>21.89378042552304</v>
+        <v>24.2450826984604</v>
       </c>
       <c r="H70" t="n">
-        <v>7.5</v>
+        <v>20</v>
       </c>
       <c r="I70" t="n">
-        <v>18.22116789868076</v>
+        <v>20.40316062992466</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>87.57512170209215</v>
+        <v>80.81694232820134</v>
       </c>
       <c r="L70" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M70" t="n">
-        <v>2.538714386041582</v>
+        <v>2.842726531032447</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.811924685503281</v>
+        <v>7.984922540923842</v>
       </c>
       <c r="P70" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2.842726531032447</v>
       </c>
       <c r="R70" t="n">
-        <v>0.5822289040692653</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>1.956485481972317</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>44.23742294311523</v>
+        <v>2935.349848734215</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="V70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C008510</t>
+          <t>C001266</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>35.58240768338413</v>
+        <v>54.14284276064488</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -5800,56 +5800,56 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Prescription=17.0 | Competition=0.0 | Population=98.5 | Road=50.0</t>
+          <t>Prescription=49.5 | Competition=35.3 | Population=100.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5.953172695740633</v>
+        <v>24.7394997362083</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>10.59665697556341</v>
       </c>
       <c r="G71" t="n">
-        <v>24.6292349876435</v>
+        <v>30</v>
       </c>
       <c r="H71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I71" t="n">
-        <v>17.00906484497324</v>
+        <v>49.4789994724166</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>35.32218991854471</v>
       </c>
       <c r="K71" t="n">
-        <v>98.516939950574</v>
+        <v>100</v>
       </c>
       <c r="L71" t="n">
         <v>50</v>
       </c>
       <c r="M71" t="n">
-        <v>2.369834790786054</v>
+        <v>6.893797832620332</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>0.4750127222493101</v>
       </c>
       <c r="O71" t="n">
-        <v>4.288194501348502</v>
+        <v>9.949365992835187</v>
       </c>
       <c r="P71" t="n">
         <v>3</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.655018036553715</v>
       </c>
       <c r="R71" t="n">
-        <v>2.369834790786054</v>
+        <v>1.345701463072373</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1.893078332994244</v>
       </c>
       <c r="T71" t="n">
-        <v>71.83484649658203</v>
+        <v>20937.94273281097</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -5863,11 +5863,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C011062</t>
+          <t>C002569</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>35.25752828262118</v>
+        <v>53.40012772918603</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -5876,74 +5876,74 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Prescription=8.8 | Competition=0.0 | Population=98.7 | Road=75.0</t>
+          <t>Prescription=27.5 | Competition=0.0 | Population=98.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3.09181960209912</v>
+        <v>13.73674748540013</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>24.66570868052206</v>
+        <v>29.6633802437859</v>
       </c>
       <c r="H72" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I72" t="n">
-        <v>8.833770291711772</v>
+        <v>27.47349497080026</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>98.66283472208823</v>
+        <v>98.87793414595301</v>
       </c>
       <c r="L72" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M72" t="n">
-        <v>1.230789368017355</v>
+        <v>3.827820329911738</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.29454493364265</v>
+        <v>9.769395159194156</v>
       </c>
       <c r="P72" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.8709706238756858</v>
+        <v>3.827820329911738</v>
       </c>
       <c r="S72" t="n">
-        <v>0.3598187441416697</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>72.29885101318359</v>
+        <v>17489.18524074554</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C013807</t>
+          <t>C000658</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>35.05509558280933</v>
+        <v>53.33932978578166</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -5952,117 +5952,117 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Prescription=30.3 | Competition=0.0 | Population=97.8 | Road=0.0</t>
+          <t>Prescription=20.5 | Competition=0.0 | Population=93.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>10.59267729672423</v>
+        <v>10.23107042321207</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>24.4624182860851</v>
+        <v>28.1082593625696</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I73" t="n">
-        <v>30.26479227635494</v>
+        <v>20.46214084642413</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>97.8496731443404</v>
+        <v>93.69419787523201</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M73" t="n">
-        <v>4.216725512315009</v>
+        <v>2.850944112087177</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.259150056293074</v>
+        <v>9.257228633192828</v>
       </c>
       <c r="P73" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.216725512315009</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.850944112087177</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>69.74982452392578</v>
+        <v>10479.04899744503</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C005052</t>
+          <t>C011102</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>35</v>
+        <v>53.1432854402842</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=100.0 | Population=100.0 | Road=50.0</t>
+          <t>Prescription=27.1 | Competition=0.0 | Population=98.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>35</v>
+        <v>13.53752773912917</v>
       </c>
       <c r="F74" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>25</v>
+        <v>29.60575770115503</v>
       </c>
       <c r="H74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I74" t="n">
-        <v>100</v>
+        <v>27.07505547825834</v>
       </c>
       <c r="J74" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>100</v>
+        <v>98.68585900385011</v>
       </c>
       <c r="L74" t="n">
         <v>50</v>
       </c>
       <c r="M74" t="n">
-        <v>30.83965299999198</v>
+        <v>3.772306650585076</v>
       </c>
       <c r="N74" t="n">
-        <v>17.90302066526227</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.419745706089935</v>
+        <v>9.750417639288738</v>
       </c>
       <c r="P74" t="n">
         <v>3</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.894869422757747</v>
+        <v>3.772306650585076</v>
       </c>
       <c r="S74" t="n">
-        <v>27.94478357723423</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>82.07515716552734</v>
+        <v>17160.39458546042</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -6091,11 +6091,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C009233</t>
+          <t>C004625</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>34.93626625421695</v>
+        <v>52.96236119238492</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -6104,150 +6104,150 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Prescription=7.0 | Competition=0.0 | Population=99.9 | Road=75.0</t>
+          <t>Prescription=35.1 | Competition=0.0 | Population=84.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2.453654063676462</v>
+        <v>17.55989869109033</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>24.98261219054048</v>
+        <v>25.40246250129459</v>
       </c>
       <c r="H75" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I75" t="n">
-        <v>7.010440181932749</v>
+        <v>35.11979738218066</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>99.93044876216193</v>
+        <v>84.67487500431531</v>
       </c>
       <c r="L75" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M75" t="n">
-        <v>0.9767488802759563</v>
+        <v>4.893162466033944</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.349720983154575</v>
+        <v>8.366096249052609</v>
       </c>
       <c r="P75" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.952950685397501</v>
       </c>
       <c r="S75" t="n">
-        <v>0.9767488802759563</v>
+        <v>1.940211780636443</v>
       </c>
       <c r="T75" t="n">
-        <v>76.45684814453125</v>
+        <v>4297.821735155769</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C007183</t>
+          <t>C009193</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>34.90257162460892</v>
+        <v>52.91702694588842</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Prescription=94.8 | Competition=66.7 | Population=86.9 | Road=0.0</t>
+          <t>Prescription=14.1 | Competition=0.0 | Population=86.2 | Road=100.0</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>33.17548530084602</v>
+        <v>7.047781425300164</v>
       </c>
       <c r="F76" t="n">
-        <v>20.00216058577415</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>21.72924690953706</v>
+        <v>25.86924552058826</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I76" t="n">
-        <v>94.78710085956007</v>
+        <v>14.09556285060033</v>
       </c>
       <c r="J76" t="n">
-        <v>66.67386861924717</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>86.91698763814823</v>
+        <v>86.23081840196086</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M76" t="n">
-        <v>13.20647380570825</v>
+        <v>1.963903103643059</v>
       </c>
       <c r="N76" t="n">
-        <v>5.379780117041485</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>3.783277765739326</v>
+        <v>8.519827473599644</v>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q76" t="n">
-        <v>8.807818466339167</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4.398655339369084</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>1.963903103643059</v>
       </c>
       <c r="T76" t="n">
-        <v>42.95989608764648</v>
+        <v>5012.188774767332</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="V76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C000609</t>
+          <t>C002215</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>34.82037533857539</v>
+        <v>52.38057869885539</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6256,150 +6256,150 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Prescription=19.3 | Competition=0.0 | Population=82.3 | Road=75.0</t>
+          <t>Prescription=26.0 | Competition=0.0 | Population=97.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6.746868980812702</v>
+        <v>13.0247737649999</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>20.57350635776269</v>
+        <v>29.35580493385548</v>
       </c>
       <c r="H77" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I77" t="n">
-        <v>19.27676851660772</v>
+        <v>26.04954752999981</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>82.29402543105076</v>
+        <v>97.85268311285161</v>
       </c>
       <c r="L77" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M77" t="n">
-        <v>2.685788848531968</v>
+        <v>3.629424932150556</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>3.582051853461061</v>
+        <v>9.66809771031183</v>
       </c>
       <c r="P77" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.685788848531968</v>
+        <v>3.629424932150556</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>34.94722366333008</v>
+        <v>15804.25423593447</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C004637</t>
+          <t>C006116</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>34.73396589422817</v>
+        <v>52.28903259509714</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Prescription=57.9 | Competition=0.0 | Population=57.9 | Road=0.0</t>
+          <t>Prescription=16.0 | Competition=0.0 | Population=97.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>20.24790034597755</v>
+        <v>7.990130845013874</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>14.48606554825062</v>
+        <v>29.29890175008326</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I78" t="n">
-        <v>57.85114384565014</v>
+        <v>15.98026169002775</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>57.94426219300248</v>
+        <v>97.66300583361088</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M78" t="n">
-        <v>8.060269898536326</v>
+        <v>2.226493958610325</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>2.522167930158913</v>
+        <v>9.649357105447573</v>
       </c>
       <c r="P78" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q78" t="n">
-        <v>5.260475422682626</v>
+        <v>2.226493958610325</v>
       </c>
       <c r="R78" t="n">
-        <v>2.799794475853701</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>11.45557022094727</v>
+        <v>15510.81243817508</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C000068</t>
+          <t>C000743</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>34.67761350784531</v>
+        <v>52.26559700119078</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6408,74 +6408,74 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Prescription=27.0 | Competition=12.2 | Population=95.6 | Road=50.0</t>
+          <t>Prescription=16.2 | Competition=0.0 | Population=97.3 | Road=75.0</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>9.438623536320801</v>
+        <v>8.081837310687551</v>
       </c>
       <c r="F79" t="n">
-        <v>3.660204967021518</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>23.89919493854602</v>
+        <v>29.18375969050323</v>
       </c>
       <c r="H79" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I79" t="n">
-        <v>26.96749581805943</v>
+        <v>16.1636746213751</v>
       </c>
       <c r="J79" t="n">
-        <v>12.20068322340506</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>95.5967797541841</v>
+        <v>97.27919896834409</v>
       </c>
       <c r="L79" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M79" t="n">
-        <v>3.757320604777506</v>
+        <v>2.252048470263331</v>
       </c>
       <c r="N79" t="n">
-        <v>0.9844485460177469</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.161087275895718</v>
+        <v>9.611435996314485</v>
       </c>
       <c r="P79" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.331433635211078</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.041252395463951</v>
+        <v>1.338890602956456</v>
       </c>
       <c r="S79" t="n">
-        <v>0.3846345741024767</v>
+        <v>0.9131578673068751</v>
       </c>
       <c r="T79" t="n">
-        <v>63.1412239074707</v>
+        <v>14933.60072803311</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C005122</t>
+          <t>C003792</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>34.44192716630756</v>
+        <v>51.56307836348702</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6484,44 +6484,44 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Prescription=12.7 | Competition=0.0 | Population=100.0 | Road=50.0</t>
+          <t>Prescription=13.7 | Competition=0.0 | Population=99.1 | Road=75.0</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4.441927166307563</v>
+        <v>6.826998780677253</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>25</v>
+        <v>29.73607958280977</v>
       </c>
       <c r="H80" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I80" t="n">
-        <v>12.69122047516447</v>
+        <v>13.65399756135451</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>100</v>
+        <v>99.12026527603258</v>
       </c>
       <c r="L80" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M80" t="n">
-        <v>1.768239235590285</v>
+        <v>1.902380803951849</v>
       </c>
       <c r="N80" t="n">
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4.385358651340807</v>
+        <v>9.793338100453699</v>
       </c>
       <c r="P80" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -6530,28 +6530,28 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>1.768239235590285</v>
+        <v>1.902380803951849</v>
       </c>
       <c r="T80" t="n">
-        <v>79.26700592041016</v>
+        <v>17913.00522047281</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C003964</t>
+          <t>C004491</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>34.42202263007693</v>
+        <v>51.02814212478982</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6560,41 +6560,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Prescription=19.1 | Competition=0.0 | Population=91.0 | Road=50.0</t>
+          <t>Prescription=22.5 | Competition=0.0 | Population=99.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6.684446113033752</v>
+        <v>11.24292584402745</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>22.73757651704318</v>
+        <v>29.78521628076236</v>
       </c>
       <c r="H81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I81" t="n">
-        <v>19.09841746581072</v>
+        <v>22.48585168805491</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>90.95030606817271</v>
+        <v>99.28405426920789</v>
       </c>
       <c r="L81" t="n">
         <v>50</v>
       </c>
       <c r="M81" t="n">
-        <v>2.660939597323611</v>
+        <v>3.132903197004849</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.958837968101435</v>
+        <v>9.809520875820892</v>
       </c>
       <c r="P81" t="n">
         <v>3</v>
@@ -6603,13 +6603,13 @@
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.660939597323611</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>3.132903197004849</v>
       </c>
       <c r="T81" t="n">
-        <v>51.39640426635742</v>
+        <v>18205.26192715764</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -6623,11 +6623,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C002593</t>
+          <t>C001039</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>34.41899545307659</v>
+        <v>50.92013636047252</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6636,74 +6636,74 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Prescription=15.3 | Competition=0.0 | Population=96.3 | Road=50.0</t>
+          <t>Prescription=14.2 | Competition=0.0 | Population=96.1 | Road=75.0</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5.351418700948403</v>
+        <v>7.095618068332434</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>24.06757675212818</v>
+        <v>28.82451829214009</v>
       </c>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I82" t="n">
-        <v>15.28976771699544</v>
+        <v>14.19123613666487</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>96.27030700851273</v>
+        <v>96.08172764046697</v>
       </c>
       <c r="L82" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M82" t="n">
-        <v>2.130288984669355</v>
+        <v>1.977233047642413</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.190404222503778</v>
+        <v>9.4931227377004</v>
       </c>
       <c r="P82" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.130288984669355</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>1.977233047642413</v>
       </c>
       <c r="T82" t="n">
-        <v>65.04948425292969</v>
+        <v>13267.16369673051</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C001040</t>
+          <t>C001062</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>34.38334438379486</v>
+        <v>50.77356194553614</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -6712,41 +6712,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Prescription=7.9 | Competition=0.0 | Population=96.4 | Road=75.0</t>
+          <t>Prescription=12.3 | Competition=0.0 | Population=98.8 | Road=75.0</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2.774172752696424</v>
+        <v>6.128520140090682</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>24.10917163109844</v>
+        <v>29.64504180544547</v>
       </c>
       <c r="H83" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I83" t="n">
-        <v>7.926207864846925</v>
+        <v>12.25704028018136</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>96.43668652439378</v>
+        <v>98.81680601815155</v>
       </c>
       <c r="L83" t="n">
         <v>75</v>
       </c>
       <c r="M83" t="n">
-        <v>1.104340734092007</v>
+        <v>1.707745884493074</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.197646304175175</v>
+        <v>9.763355542357576</v>
       </c>
       <c r="P83" t="n">
         <v>3.5</v>
@@ -6755,13 +6755,13 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.248498153885814</v>
       </c>
       <c r="S83" t="n">
-        <v>1.104340734092007</v>
+        <v>0.4592477306072598</v>
       </c>
       <c r="T83" t="n">
-        <v>65.52955627441406</v>
+        <v>17383.86957675219</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -6775,11 +6775,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C001199</t>
+          <t>C000053</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>34.16958807606613</v>
+        <v>50.59973756289124</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -6788,56 +6788,56 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Prescription=7.4 | Competition=0.0 | Population=96.3 | Road=75.0</t>
+          <t>Prescription=13.9 | Competition=0.0 | Population=95.5 | Road=75.0</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2.605156193901499</v>
+        <v>6.946155587435839</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>24.06443188216463</v>
+        <v>28.65358197545541</v>
       </c>
       <c r="H84" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I84" t="n">
-        <v>7.443303411147141</v>
+        <v>13.89231117487168</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>96.25772752865852</v>
+        <v>95.51193991818469</v>
       </c>
       <c r="L84" t="n">
         <v>75</v>
       </c>
       <c r="M84" t="n">
-        <v>1.037058741493719</v>
+        <v>1.935584504306875</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4.189856669399026</v>
+        <v>9.436826239761679</v>
       </c>
       <c r="P84" t="n">
         <v>3.5</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.037058741493719</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1.935584504306875</v>
       </c>
       <c r="T84" t="n">
-        <v>65.01332855224609</v>
+        <v>12540.84885298833</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -6851,11 +6851,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C003443</t>
+          <t>C003299</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>34.07325493750462</v>
+        <v>50.4388448169299</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -6864,74 +6864,74 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Prescription=31.4 | Competition=0.0 | Population=92.4 | Road=0.0</t>
+          <t>Prescription=25.3 | Competition=0.0 | Population=92.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>10.97326245270559</v>
+        <v>12.62828247638798</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>23.09999248479903</v>
+        <v>27.81056234054192</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I85" t="n">
-        <v>31.35217843630168</v>
+        <v>25.25656495277596</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>92.39996993919614</v>
+        <v>92.70187446847306</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M85" t="n">
-        <v>4.368228582962812</v>
+        <v>3.518940451250351</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>4.021938188669036</v>
+        <v>9.159184518799863</v>
       </c>
       <c r="P85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.228691694388785</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>1.139536888574027</v>
+        <v>3.518940451250351</v>
       </c>
       <c r="T85" t="n">
-        <v>54.80916976928711</v>
+        <v>9500.305781238712</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C007721</t>
+          <t>C003219</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>34.0066654418853</v>
+        <v>49.92228075615876</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -6940,74 +6940,74 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Prescription=42.7 | Competition=0.0 | Population=76.3 | Road=0.0</t>
+          <t>Prescription=38.3 | Competition=23.6 | Population=92.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>14.94388384971127</v>
+        <v>19.13483596173829</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>7.076384231398707</v>
       </c>
       <c r="G86" t="n">
-        <v>19.06278159217402</v>
+        <v>27.86382902581918</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I86" t="n">
-        <v>42.69681099917506</v>
+        <v>38.26967192347659</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>23.58794743799569</v>
       </c>
       <c r="K86" t="n">
-        <v>76.25112636869609</v>
+        <v>92.87943008606392</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M86" t="n">
-        <v>5.948850750096658</v>
+        <v>5.332027409087558</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>0.3172106585303589</v>
       </c>
       <c r="O86" t="n">
-        <v>3.319019662810459</v>
+        <v>9.17672747219955</v>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.948850750096658</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.835560469593693</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>1.496466939493864</v>
       </c>
       <c r="T86" t="n">
-        <v>26.63324737548828</v>
+        <v>9668.457371109165</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C003792</t>
+          <t>C005980</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>33.9931675008067</v>
+        <v>49.77824373985452</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7016,41 +7016,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Prescription=13.7 | Competition=0.0 | Population=86.9 | Road=75.0</t>
+          <t>Prescription=13.7 | Competition=0.0 | Population=93.1 | Road=75.0</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.778899146474155</v>
+        <v>6.846944378936001</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>21.71426835433255</v>
+        <v>27.93129936091851</v>
       </c>
       <c r="H87" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="I87" t="n">
-        <v>13.65399756135473</v>
+        <v>13.693888757872</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>86.85707341733018</v>
+        <v>93.1043312030617</v>
       </c>
       <c r="L87" t="n">
         <v>75</v>
       </c>
       <c r="M87" t="n">
-        <v>1.902380803949324</v>
+        <v>1.907938754739562</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>3.780669850467156</v>
+        <v>9.198948283168885</v>
       </c>
       <c r="P87" t="n">
         <v>3.5</v>
@@ -7059,13 +7059,13 @@
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.907938754739562</v>
       </c>
       <c r="S87" t="n">
-        <v>1.902380803949324</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>42.84540176391602</v>
+        <v>9885.725553262979</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -7079,11 +7079,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C012221</t>
+          <t>C001218</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>33.97632242009587</v>
+        <v>49.51722802929469</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7092,56 +7092,56 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Prescription=14.7 | Competition=0.0 | Population=95.3 | Road=50.0</t>
+          <t>Prescription=19.6 | Competition=0.0 | Population=99.1 | Road=50.0</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5.156454675057673</v>
+        <v>9.778207231929336</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>23.8198677450382</v>
+        <v>29.73902079736535</v>
       </c>
       <c r="H88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I88" t="n">
-        <v>14.73272764302192</v>
+        <v>19.55641446385867</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>95.27947098015279</v>
+        <v>99.13006932455116</v>
       </c>
       <c r="L88" t="n">
         <v>50</v>
       </c>
       <c r="M88" t="n">
-        <v>2.052677842657946</v>
+        <v>2.724751290088874</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4.147275623395008</v>
+        <v>9.794306765757693</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>0.9384203657469457</v>
       </c>
       <c r="R88" t="n">
-        <v>1.429588059991767</v>
+        <v>1.465485907048629</v>
       </c>
       <c r="S88" t="n">
-        <v>0.623089782666179</v>
+        <v>0.3208450172932996</v>
       </c>
       <c r="T88" t="n">
-        <v>62.26141738891602</v>
+        <v>17930.36630296707</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -7155,87 +7155,87 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C002520</t>
+          <t>C008680</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>33.82401498136188</v>
+        <v>49.50704874044831</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Prescription=18.5 | Competition=0.0 | Population=89.4 | Road=50.0</t>
+          <t>Prescription=51.3 | Competition=0.0 | Population=79.5 | Road=0.0</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6.464564958091114</v>
+        <v>25.66505473120245</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>22.35945002327077</v>
+        <v>23.84199400924586</v>
       </c>
       <c r="H89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>18.47018559454604</v>
+        <v>51.33010946240491</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>89.43780009308308</v>
+        <v>79.47331336415286</v>
       </c>
       <c r="L89" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2.57340946214139</v>
+        <v>7.15170882865891</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.893002388871203</v>
+        <v>7.852168530532077</v>
       </c>
       <c r="P89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>5.388515065030845</v>
       </c>
       <c r="R89" t="n">
-        <v>2.57340946214139</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>1.763193763628065</v>
       </c>
       <c r="T89" t="n">
-        <v>48.05795669555664</v>
+        <v>2570.304227115586</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="V89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C000053</t>
+          <t>C009013</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>33.77182585156439</v>
+        <v>49.4712612685909</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7244,44 +7244,44 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Prescription=13.9 | Competition=0.0 | Population=85.6 | Road=75.0</t>
+          <t>Prescription=19.3 | Competition=0.0 | Population=99.3 | Road=50.0</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4.862308911231528</v>
+        <v>9.668464239264205</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>21.40951694033286</v>
+        <v>29.80279702932669</v>
       </c>
       <c r="H90" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I90" t="n">
-        <v>13.89231117494722</v>
+        <v>19.33692847852841</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>85.63806776133146</v>
+        <v>99.34265676442232</v>
       </c>
       <c r="L90" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M90" t="n">
-        <v>1.9355845043148</v>
+        <v>2.694170800869325</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>3.727609601602453</v>
+        <v>9.815310953637642</v>
       </c>
       <c r="P90" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -7290,28 +7290,28 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>1.9355845043148</v>
+        <v>2.694170800869325</v>
       </c>
       <c r="T90" t="n">
-        <v>40.57959747314453</v>
+        <v>18310.9833728075</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C012690</t>
+          <t>C008509</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>33.67147761373074</v>
+        <v>49.42719928648053</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7320,150 +7320,150 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Prescription=42.4 | Competition=0.0 | Population=75.4 | Road=0.0</t>
+          <t>Prescription=21.2 | Competition=0.0 | Population=96.1 | Road=50.0</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>14.82350132934223</v>
+        <v>10.60925048190143</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>18.8479762843885</v>
+        <v>28.8179488045791</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I91" t="n">
-        <v>42.35286094097781</v>
+        <v>21.21850096380286</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>75.39190513755402</v>
+        <v>96.05982934859702</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M91" t="n">
-        <v>5.900928961236548</v>
+        <v>2.9563260679364</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.281619924646912</v>
+        <v>9.490959129930511</v>
       </c>
       <c r="P91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.900928961236548</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>2.9563260679364</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>25.61885833740234</v>
+        <v>13238.4876277335</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C002501</t>
+          <t>C003233</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>33.47132247768859</v>
+        <v>49.30304415771374</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Prescription=28.4 | Competition=0.0 | Population=94.2 | Road=0.0</t>
+          <t>Prescription=63.1 | Competition=58.5 | Population=84.2 | Road=50.0</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>9.924656437901096</v>
+        <v>31.56590915535433</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>17.53727381472914</v>
       </c>
       <c r="G92" t="n">
-        <v>23.5466660397875</v>
+        <v>25.27440881708856</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I92" t="n">
-        <v>28.35616125114599</v>
+        <v>63.13181831070865</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>58.45757938243048</v>
       </c>
       <c r="K92" t="n">
-        <v>94.18666415914998</v>
+        <v>84.24802939029522</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M92" t="n">
-        <v>3.950800239671313</v>
+        <v>8.796014407736113</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>0.7861373822684408</v>
       </c>
       <c r="O92" t="n">
-        <v>4.099708492268002</v>
+        <v>8.323922800432859</v>
       </c>
       <c r="P92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4.898343315095299</v>
       </c>
       <c r="R92" t="n">
-        <v>3.950800239671313</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>3.897671092640813</v>
       </c>
       <c r="T92" t="n">
-        <v>59.32270050048828</v>
+        <v>4120.29535892047</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C001680</t>
+          <t>C001808</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>33.21047402725125</v>
+        <v>49.17072030655128</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7472,41 +7472,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Prescription=21.1 | Competition=0.0 | Population=83.3 | Road=50.0</t>
+          <t>Prescription=20.4 | Competition=0.0 | Population=96.6 | Road=50.0</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>7.37872737817603</v>
+        <v>10.18407562956502</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>20.83174664907522</v>
+        <v>28.98664467698627</v>
       </c>
       <c r="H93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I93" t="n">
-        <v>21.08207822336009</v>
+        <v>20.36815125913003</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>83.32698659630088</v>
+        <v>96.62214892328755</v>
       </c>
       <c r="L93" t="n">
         <v>50</v>
       </c>
       <c r="M93" t="n">
-        <v>2.937318594005888</v>
+        <v>2.837848754054762</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>3.627014053780666</v>
+        <v>9.546517755607224</v>
       </c>
       <c r="P93" t="n">
         <v>3</v>
@@ -7515,13 +7515,13 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.937318594005888</v>
+        <v>2.837848754054762</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>36.60037612915039</v>
+        <v>13994.8726666458</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -7535,11 +7535,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C005040</t>
+          <t>C010151</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>33.1480001060946</v>
+        <v>49.15946444110203</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7548,74 +7548,74 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Prescription=17.5 | Competition=0.0 | Population=88.0 | Road=50.0</t>
+          <t>Prescription=8.8 | Competition=0.0 | Population=99.2 | Road=75.0</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6.139337391707823</v>
+        <v>4.400997864297702</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>22.00866271438678</v>
+        <v>29.75846657680433</v>
       </c>
       <c r="H94" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I94" t="n">
-        <v>17.54096397630807</v>
+        <v>8.801995728595404</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>88.03465085754712</v>
+        <v>99.19488858934777</v>
       </c>
       <c r="L94" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M94" t="n">
-        <v>2.443943101743472</v>
+        <v>1.226362289527533</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.831926833343236</v>
+        <v>9.800711076458521</v>
       </c>
       <c r="P94" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1.516331421446902</v>
+        <v>1.226362289527533</v>
       </c>
       <c r="S94" t="n">
-        <v>0.9276116802965699</v>
+        <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>45.1513786315918</v>
+        <v>18045.57285958529</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C004255</t>
+          <t>C003442</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>33.11488600682182</v>
+        <v>49.04565204813061</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -7624,74 +7624,74 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Prescription=49.9 | Competition=36.4 | Population=86.3 | Road=50.0</t>
+          <t>Prescription=39.0 | Competition=0.0 | Population=98.5 | Road=0.0</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>17.4594253679512</v>
+        <v>19.50929186168302</v>
       </c>
       <c r="F95" t="n">
-        <v>10.91142307098628</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>21.5668837098569</v>
+        <v>29.53636018644758</v>
       </c>
       <c r="H95" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>49.88407247986057</v>
+        <v>39.01858372336605</v>
       </c>
       <c r="J95" t="n">
-        <v>36.37141023662092</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>86.26753483942761</v>
+        <v>98.45453395482528</v>
       </c>
       <c r="L95" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>6.950235744665522</v>
+        <v>5.436371607595046</v>
       </c>
       <c r="N95" t="n">
-        <v>2.934735806874224</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.75500871960618</v>
+        <v>9.727562127250957</v>
       </c>
       <c r="P95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.911019114987763</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>1.039216629677759</v>
+        <v>3.825468315911813</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>1.610903291683232</v>
       </c>
       <c r="T95" t="n">
-        <v>41.73459243774414</v>
+        <v>16772.61050732061</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="V95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C002093</t>
+          <t>C002934</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>33.11390436402692</v>
+        <v>48.56306272130901</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7700,74 +7700,74 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Prescription=21.6 | Competition=0.0 | Population=82.3 | Road=50.0</t>
+          <t>Prescription=7.3 | Competition=0.0 | Population=99.7 | Road=75.0</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>7.550034300721182</v>
+        <v>3.663140195215731</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>20.56387006330574</v>
+        <v>29.89992252609328</v>
       </c>
       <c r="H96" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I96" t="n">
-        <v>21.57152657348909</v>
+        <v>7.326280390431463</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>82.25548025322296</v>
+        <v>99.66640842031094</v>
       </c>
       <c r="L96" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M96" t="n">
-        <v>3.005512332991565</v>
+        <v>1.020754186933006</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3.580374078860088</v>
+        <v>9.847298453044241</v>
       </c>
       <c r="P96" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.005512332991565</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>1.020754186933006</v>
       </c>
       <c r="T96" t="n">
-        <v>34.886962890625</v>
+        <v>18906.20703649521</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C010661</t>
+          <t>C003307</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>32.92057656131267</v>
+        <v>48.54662079507821</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -7776,150 +7776,150 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Prescription=5.2 | Competition=0.0 | Population=94.4 | Road=75.0</t>
+          <t>Prescription=17.7 | Competition=0.0 | Population=99.0 | Road=50.0</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.825915689046522</v>
+        <v>8.844791832423269</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>23.59466087226615</v>
+        <v>29.70182896265495</v>
       </c>
       <c r="H97" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I97" t="n">
-        <v>5.21690196870435</v>
+        <v>17.68958366484654</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>94.37864348906459</v>
+        <v>99.00609654218316</v>
       </c>
       <c r="L97" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M97" t="n">
-        <v>0.7268592305478555</v>
+        <v>2.464649949048758</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>4.10806486942837</v>
+        <v>9.782057934808718</v>
       </c>
       <c r="P97" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>1.342751112903287</v>
       </c>
       <c r="R97" t="n">
-        <v>0.7268592305478555</v>
+        <v>0.6733907766220355</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>0.4485080595234353</v>
       </c>
       <c r="T97" t="n">
-        <v>59.82889175415039</v>
+        <v>17712.06770906597</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C000566</t>
+          <t>C002068</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>32.78057148689416</v>
+        <v>48.32885399871516</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>population</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Prescription=100.0 | Competition=100.0 | Population=91.1 | Road=50.0</t>
+          <t>Prescription=8.7 | Competition=0.0 | Population=96.6 | Road=75.0</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>35</v>
+        <v>4.334921387209121</v>
       </c>
       <c r="F98" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>22.78057148689416</v>
+        <v>28.99393261150604</v>
       </c>
       <c r="H98" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I98" t="n">
-        <v>100</v>
+        <v>8.669842774418242</v>
       </c>
       <c r="J98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>91.12228594757664</v>
+        <v>96.64644203835347</v>
       </c>
       <c r="L98" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M98" t="n">
-        <v>96.95707514290143</v>
+        <v>1.207949715328478</v>
       </c>
       <c r="N98" t="n">
-        <v>30.80745044097855</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.966323819504986</v>
+        <v>9.548917978091408</v>
       </c>
       <c r="P98" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q98" t="n">
-        <v>6.967140901460901</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>38.78516257146202</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>51.20477166997851</v>
+        <v>1.207949715328478</v>
       </c>
       <c r="T98" t="n">
-        <v>51.79010772705078</v>
+        <v>14028.50622276776</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="V98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C000078</t>
+          <t>C001892</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>32.55230263012822</v>
+        <v>48.24004654736563</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -7928,74 +7928,74 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Prescription=12.5 | Competition=0.0 | Population=82.7 | Road=75.0</t>
+          <t>Prescription=18.8 | Competition=0.0 | Population=96.1 | Road=50.0</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4.378264108616531</v>
+        <v>9.419859685936014</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>20.67403852151169</v>
+        <v>28.82018686142962</v>
       </c>
       <c r="H99" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I99" t="n">
-        <v>12.50932602461866</v>
+        <v>18.83971937187203</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>82.69615408604677</v>
+        <v>96.06728953809872</v>
       </c>
       <c r="L99" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M99" t="n">
-        <v>1.74289629045584</v>
+        <v>2.624895773112596</v>
       </c>
       <c r="N99" t="n">
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.599555501950892</v>
+        <v>9.491696215912677</v>
       </c>
       <c r="P99" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.624895773112596</v>
       </c>
       <c r="S99" t="n">
-        <v>1.74289629045584</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>35.58197021484375</v>
+        <v>13248.2498658374</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C003503</t>
+          <t>C011362</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>32.27825157050953</v>
+        <v>48.15804215280909</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -8004,74 +8004,74 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Prescription=20.8 | Competition=0.0 | Population=100.0 | Road=0.0</t>
+          <t>Prescription=38.0 | Competition=0.0 | Population=63.9 | Road=50.0</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>7.278251570509533</v>
+        <v>19.00073748587126</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>25</v>
+        <v>19.15730466693783</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I100" t="n">
-        <v>20.7950044871701</v>
+        <v>38.00147497174251</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>100</v>
+        <v>63.85768222312611</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M100" t="n">
-        <v>2.897321255307693</v>
+        <v>5.294660130357306</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>4.516137085628762</v>
+        <v>6.309303860122169</v>
       </c>
       <c r="P100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.897321255307693</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>5.294660130357306</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>90.48152923583984</v>
+        <v>548.662173836492</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="V100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C005118</t>
+          <t>C005098</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>32.25753739358888</v>
+        <v>48.13080025698646</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -8080,41 +8080,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Prescription=11.2 | Competition=0.0 | Population=93.3 | Road=50.0</t>
+          <t>Prescription=17.7 | Competition=0.0 | Population=97.7 | Road=50.0</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3.930562245514911</v>
+        <v>8.830115128424836</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>23.32697514807397</v>
+        <v>29.30068512856162</v>
       </c>
       <c r="H101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I101" t="n">
-        <v>11.23017784432832</v>
+        <v>17.66023025684967</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>93.30790059229587</v>
+        <v>97.66895042853875</v>
       </c>
       <c r="L101" t="n">
         <v>50</v>
       </c>
       <c r="M101" t="n">
-        <v>1.564675448343019</v>
+        <v>2.460560204660502</v>
       </c>
       <c r="N101" t="n">
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>4.0614581254046</v>
+        <v>9.64994444677315</v>
       </c>
       <c r="P101" t="n">
         <v>3</v>
@@ -8123,13 +8123,13 @@
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.11372039787528</v>
       </c>
       <c r="S101" t="n">
-        <v>1.564675448343019</v>
+        <v>1.346839806785223</v>
       </c>
       <c r="T101" t="n">
-        <v>57.05890655517578</v>
+        <v>15519.92584273219</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
